--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="117">
   <si>
     <t>nspp</t>
   </si>
@@ -364,13 +364,19 @@
   </si>
   <si>
     <t>NOTE: Most objects are ordered by species code if not specified</t>
+  </si>
+  <si>
+    <t>weight1_Numbers2</t>
+  </si>
+  <si>
+    <t>Is the observation in weight (kg) set as 1, if the observation is in numbers caught, set as 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -501,6 +507,13 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -847,9 +860,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1456,6 +1470,12 @@
       <c r="D14" t="s">
         <v>12</v>
       </c>
+      <c r="F14" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G14" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="117">
   <si>
     <t>nspp</t>
   </si>
@@ -364,6 +364,12 @@
   </si>
   <si>
     <t>NOTE: Most objects are ordered by species code if not specified</t>
+  </si>
+  <si>
+    <t>minage</t>
+  </si>
+  <si>
+    <t>Minimum age of each species included in the hindcast</t>
   </si>
 </sst>
 </file>
@@ -1171,7 +1177,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -1288,10 +1294,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>115</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
         <v>60</v>
@@ -1308,10 +1314,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
         <v>60</v>
@@ -1328,10 +1334,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
         <v>60</v>
@@ -1348,10 +1354,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
         <v>60</v>
@@ -1368,10 +1374,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
         <v>60</v>
@@ -1388,13 +1394,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
         <v>93</v>
@@ -1408,13 +1414,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
         <v>94</v>
@@ -1428,13 +1434,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>95</v>
@@ -1448,13 +1454,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1462,13 +1468,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1476,237 +1482,237 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="F20" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D31" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D32" t="s">
         <v>68</v>
@@ -1717,7 +1723,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C33" t="s">
         <v>72</v>
@@ -1731,7 +1737,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C34" t="s">
         <v>72</v>
@@ -1745,7 +1751,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C35" t="s">
         <v>72</v>
@@ -1759,7 +1765,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C36" t="s">
         <v>72</v>
@@ -1773,7 +1779,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C37" t="s">
         <v>72</v>
@@ -1787,13 +1793,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D38" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1801,10 +1807,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D39" t="s">
         <v>77</v>
@@ -1815,13 +1821,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C40" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D40" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1829,13 +1835,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D41" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1843,13 +1849,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1857,13 +1863,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C43" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D43" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1871,12 +1877,26 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C44" t="s">
+        <v>84</v>
+      </c>
+      <c r="D44" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
         <v>81</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C45" t="s">
         <v>85</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D45" t="s">
         <v>81</v>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="133">
   <si>
     <t>nspp</t>
   </si>
@@ -150,9 +150,6 @@
     <t>Start year of the hindcast</t>
   </si>
   <si>
-    <t>Number of ages of each species included in the hindcast</t>
-  </si>
-  <si>
     <t>Number of lengths of each species included in the hindcast</t>
   </si>
   <si>
@@ -321,9 +318,6 @@
     <t>Selectivity to use for the species: 0 = empirical selectivity provided in srv_emp_sel; 1 = logistic selectivity; 2 = non-parametric selecitivty sensu Ianelli et al 2018; 3 = double logistic</t>
   </si>
   <si>
-    <t>Number of ages to estimate non-parametric selectivity for Selectivity = 2. Not used otherwise</t>
-  </si>
-  <si>
     <t>Units used for survey: 1 = kg; 2 = numbers</t>
   </si>
   <si>
@@ -370,13 +364,67 @@
   </si>
   <si>
     <t>Minimum age of each species included in the hindcast</t>
+  </si>
+  <si>
+    <t>weight1_Numbers2</t>
+  </si>
+  <si>
+    <t>Is the observation in weight (kg) set as 1, if the observation is in numbers caught, set as 2</t>
+  </si>
+  <si>
+    <t>Number of ages of each species included in the hindcast. Includes age 0 if minage = 0</t>
+  </si>
+  <si>
+    <t>Number of ages (starting from minage) to estimate non-parametric selectivity for Selectivity = 2. Not used otherwise</t>
+  </si>
+  <si>
+    <t>Estimate_sigma_catch</t>
+  </si>
+  <si>
+    <t>Estimate_sigma_index</t>
+  </si>
+  <si>
+    <t>Should CEATTLE estimate the variance associated with the catch time series (yes = 1; no = 0). If 0, uses the CV from fsh_biom.</t>
+  </si>
+  <si>
+    <t>Should CEATTLE estimate the variance associated with the survey index time series (yes = 1; no = 0). If 0, uses the CV from srv_biom.</t>
+  </si>
+  <si>
+    <t>Sigma_catch_prior</t>
+  </si>
+  <si>
+    <t>Prior for sigma_catch to be used if Estimate_sigma_catch = 1</t>
+  </si>
+  <si>
+    <t>Sigma_index_prior</t>
+  </si>
+  <si>
+    <t>Prior for sigma_catch to be used if Estimate_sigma_index = 1</t>
+  </si>
+  <si>
+    <t>sigma_rec_prior</t>
+  </si>
+  <si>
+    <t>Prior to be used for estimating the standard deviation around recruitment deviates. Is the starting value if random_rec = TRUE when using fit_mod.</t>
+  </si>
+  <si>
+    <t>projyr</t>
+  </si>
+  <si>
+    <t>End year of the forecast</t>
+  </si>
+  <si>
+    <t>proj_F</t>
+  </si>
+  <si>
+    <t>Projected F rate for forecast of each fishery</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -507,6 +555,19 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -853,9 +914,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1177,13 +1242,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="119.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="17.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="119.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="2"/>
+    <col min="6" max="6" width="23.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1191,713 +1259,777 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G3" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="C4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
         <v>42</v>
       </c>
-      <c r="D3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B43" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
         <v>45</v>
       </c>
-      <c r="D4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" t="s">
-        <v>111</v>
-      </c>
-      <c r="G5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" t="s">
-        <v>88</v>
-      </c>
-      <c r="G6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" t="s">
-        <v>89</v>
-      </c>
-      <c r="G7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B46" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
         <v>46</v>
       </c>
-      <c r="D8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" t="s">
-        <v>91</v>
-      </c>
-      <c r="G9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" t="s">
-        <v>93</v>
-      </c>
-      <c r="G11" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>94</v>
-      </c>
-      <c r="G12" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>95</v>
-      </c>
-      <c r="G13" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28" t="s">
-        <v>75</v>
-      </c>
-      <c r="D28" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" t="s">
-        <v>69</v>
-      </c>
-      <c r="D29" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" t="s">
-        <v>107</v>
-      </c>
-      <c r="D30" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" t="s">
-        <v>70</v>
-      </c>
-      <c r="D31" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" t="s">
-        <v>71</v>
-      </c>
-      <c r="D32" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>30</v>
-      </c>
-      <c r="C33" t="s">
-        <v>72</v>
-      </c>
-      <c r="D33" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" t="s">
-        <v>72</v>
-      </c>
-      <c r="D34" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" t="s">
-        <v>72</v>
-      </c>
-      <c r="D35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" t="s">
-        <v>72</v>
-      </c>
-      <c r="D37" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>35</v>
-      </c>
-      <c r="C38" t="s">
-        <v>72</v>
-      </c>
-      <c r="D38" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="s">
-        <v>36</v>
-      </c>
-      <c r="C39" t="s">
-        <v>73</v>
-      </c>
-      <c r="D39" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="s">
-        <v>37</v>
-      </c>
-      <c r="C40" t="s">
-        <v>74</v>
-      </c>
-      <c r="D40" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="s">
-        <v>38</v>
-      </c>
-      <c r="C41" t="s">
-        <v>76</v>
-      </c>
-      <c r="D41" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" t="s">
-        <v>82</v>
-      </c>
-      <c r="D42" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="s">
-        <v>79</v>
-      </c>
-      <c r="C43" t="s">
-        <v>83</v>
-      </c>
-      <c r="D43" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="B47" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C47" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D47" s="2" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
-        <v>81</v>
-      </c>
-      <c r="C45" t="s">
-        <v>85</v>
-      </c>
-      <c r="D45" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="127">
   <si>
     <t>nspp</t>
   </si>
@@ -336,9 +336,6 @@
     <t>Age transition matrix (e.g. Age Length Key or ALK) index to use for derived quantitied</t>
   </si>
   <si>
-    <t>Estimate catchability? (0 = no; 1 = yes)</t>
-  </si>
-  <si>
     <t>Starting value or fixed value for catchability</t>
   </si>
   <si>
@@ -370,6 +367,39 @@
   </si>
   <si>
     <t>Is the observation in weight (kg) set as 1, if the observation is in numbers caught, set as 2</t>
+  </si>
+  <si>
+    <t>Estimate catchability? (0 = no; 1 = yes, 2 = analytical from Ludwig and Walters 1994)</t>
+  </si>
+  <si>
+    <t>Estimate_sigma_index</t>
+  </si>
+  <si>
+    <t>Estimate survey variance (0 = use CV from srv_biom, 1 = yes, 2 = analytically estimate following (Ludwig and Walters 1994)</t>
+  </si>
+  <si>
+    <t>Sigma_index_prior</t>
+  </si>
+  <si>
+    <t>Starting value to be used if Estimate_sigma_index = 1</t>
+  </si>
+  <si>
+    <t>Estimate_sigma_catch</t>
+  </si>
+  <si>
+    <t>Estimate fishery variance (0 = use CV from srv_biom, 1 = yes, 2 = analytically estimate following (Ludwig and Walters 1994)</t>
+  </si>
+  <si>
+    <t>Sigma_catch_prior</t>
+  </si>
+  <si>
+    <t>Starting value to be used if Estimate_sigma_catch = 1</t>
+  </si>
+  <si>
+    <t>NOTE: Lengths are index 1 through nlenths</t>
+  </si>
+  <si>
+    <t>NOTE: Columns for ages are index by 1 trhough nages</t>
   </si>
 </sst>
 </file>
@@ -860,10 +890,18 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1208,10 +1246,10 @@
         <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>40</v>
@@ -1271,10 +1309,10 @@
         <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1291,10 +1329,10 @@
         <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1434,7 +1472,7 @@
         <v>94</v>
       </c>
       <c r="G12" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1450,11 +1488,11 @@
       <c r="D13" t="s">
         <v>11</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="2" t="s">
         <v>95</v>
       </c>
       <c r="G13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1470,11 +1508,11 @@
       <c r="D14" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G14" t="s">
         <v>115</v>
-      </c>
-      <c r="G14" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1490,6 +1528,12 @@
       <c r="D15" t="s">
         <v>13</v>
       </c>
+      <c r="F15" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G15" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
@@ -1504,11 +1548,14 @@
       <c r="D16" t="s">
         <v>14</v>
       </c>
-      <c r="F16" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F16" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1521,8 +1568,14 @@
       <c r="D17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F17" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1535,8 +1588,14 @@
       <c r="D18" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F18" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G18" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1550,7 +1609,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1564,7 +1623,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1578,7 +1637,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1592,7 +1651,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1606,7 +1665,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1620,7 +1679,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1633,8 +1692,11 @@
       <c r="D25" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F25" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1647,8 +1709,11 @@
       <c r="D26" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1661,8 +1726,11 @@
       <c r="D27" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F27" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1676,7 +1744,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1684,13 +1752,13 @@
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D29" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1704,7 +1772,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1718,7 +1786,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10309"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grant Adams\Documents\GitHub\Rceattle\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grantadams/Documents/GitHub/Rceattle/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F15347-0179-E14B-9092-1C6EA2FC6A68}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="12340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data_names" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="139">
   <si>
     <t>nspp</t>
   </si>
@@ -400,13 +401,49 @@
   </si>
   <si>
     <t>NOTE: Columns for ages are index by 1 trhough nages</t>
+  </si>
+  <si>
+    <t>Time_varying_sel</t>
+  </si>
+  <si>
+    <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity. 0 = no, 1 = random walk from mean selectivity following Dorn 2018, 2 = random effect.</t>
+  </si>
+  <si>
+    <t>Sel_sd_prior</t>
+  </si>
+  <si>
+    <t>The sd to use for the random walk of time varying selectivity if set to 1</t>
+  </si>
+  <si>
+    <t>Time_varying_q</t>
+  </si>
+  <si>
+    <t>Q_sd_prior</t>
+  </si>
+  <si>
+    <t>The sd to use for the random walk of time varying q if set to 1</t>
+  </si>
+  <si>
+    <t>Wether a time-varying q should be estimated. 0 = no, 1 = random walk from mean selectivity following Dorn 2018, 2 = random effect.</t>
+  </si>
+  <si>
+    <t>Selectivity_index</t>
+  </si>
+  <si>
+    <t>index to use if selectivitys of different surveys are to be the same</t>
+  </si>
+  <si>
+    <t>Q_index</t>
+  </si>
+  <si>
+    <t>index to use if catchability coefficients are to be set the same</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="19" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1222,17 +1259,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="119.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="119.5" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -1255,7 +1292,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1275,7 +1312,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1295,7 +1332,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1315,7 +1352,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1335,7 +1372,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1355,7 +1392,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1375,7 +1412,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1395,7 +1432,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1415,7 +1452,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1435,7 +1472,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1455,7 +1492,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1475,7 +1512,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1495,7 +1532,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1515,7 +1552,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1535,7 +1572,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1555,7 +1592,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1575,7 +1612,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1595,7 +1632,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1608,8 +1645,14 @@
       <c r="D19" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F19" t="s">
+        <v>127</v>
+      </c>
+      <c r="G19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1622,8 +1665,14 @@
       <c r="D20" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F20" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1636,8 +1685,14 @@
       <c r="D21" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F21" t="s">
+        <v>131</v>
+      </c>
+      <c r="G21" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1650,8 +1705,14 @@
       <c r="D22" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F22" t="s">
+        <v>132</v>
+      </c>
+      <c r="G22" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1664,8 +1725,14 @@
       <c r="D23" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F23" t="s">
+        <v>135</v>
+      </c>
+      <c r="G23" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1678,8 +1745,14 @@
       <c r="D24" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F24" t="s">
+        <v>137</v>
+      </c>
+      <c r="G24" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1696,7 +1769,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1713,7 +1786,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1730,7 +1803,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1744,7 +1817,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1758,7 +1831,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1772,7 +1845,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1786,7 +1859,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1800,7 +1873,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1814,7 +1887,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1828,7 +1901,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1842,7 +1915,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1856,7 +1929,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1870,7 +1943,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1884,7 +1957,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1898,7 +1971,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1912,7 +1985,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1926,7 +1999,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1940,7 +2013,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1954,7 +2027,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4">
       <c r="A44">
         <v>43</v>
       </c>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grantadams/Documents/GitHub/Rceattle/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F15347-0179-E14B-9092-1C6EA2FC6A68}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3E6C21-7787-2F40-8A10-10FEFA542231}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="12340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -373,15 +373,9 @@
     <t>Estimate catchability? (0 = no; 1 = yes, 2 = analytical from Ludwig and Walters 1994)</t>
   </si>
   <si>
-    <t>Estimate_sigma_index</t>
-  </si>
-  <si>
     <t>Estimate survey variance (0 = use CV from srv_biom, 1 = yes, 2 = analytically estimate following (Ludwig and Walters 1994)</t>
   </si>
   <si>
-    <t>Sigma_index_prior</t>
-  </si>
-  <si>
     <t>Starting value to be used if Estimate_sigma_index = 1</t>
   </si>
   <si>
@@ -400,9 +394,6 @@
     <t>NOTE: Lengths are index 1 through nlenths</t>
   </si>
   <si>
-    <t>NOTE: Columns for ages are index by 1 trhough nages</t>
-  </si>
-  <si>
     <t>Time_varying_sel</t>
   </si>
   <si>
@@ -437,6 +428,15 @@
   </si>
   <si>
     <t>index to use if catchability coefficients are to be set the same</t>
+  </si>
+  <si>
+    <t>Sigma_survey_prior</t>
+  </si>
+  <si>
+    <t>Estimate_sigma_survey</t>
+  </si>
+  <si>
+    <t>NOTE: Columns for ages are index by 1 trhough nages, but are place holders.</t>
   </si>
 </sst>
 </file>
@@ -1566,10 +1566,10 @@
         <v>13</v>
       </c>
       <c r="F15" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G15" t="s">
         <v>117</v>
-      </c>
-      <c r="G15" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1586,10 +1586,10 @@
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="G16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1606,10 +1606,10 @@
         <v>15</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1626,10 +1626,10 @@
         <v>16</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G18" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1646,10 +1646,10 @@
         <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1666,10 +1666,10 @@
         <v>18</v>
       </c>
       <c r="F20" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G20" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1686,10 +1686,10 @@
         <v>19</v>
       </c>
       <c r="F21" t="s">
+        <v>128</v>
+      </c>
+      <c r="G21" t="s">
         <v>131</v>
-      </c>
-      <c r="G21" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1706,10 +1706,10 @@
         <v>20</v>
       </c>
       <c r="F22" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G22" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1726,10 +1726,10 @@
         <v>21</v>
       </c>
       <c r="F23" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G23" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1746,10 +1746,10 @@
         <v>22</v>
       </c>
       <c r="F24" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G24" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1765,9 +1765,6 @@
       <c r="D25" t="s">
         <v>23</v>
       </c>
-      <c r="F25" t="s">
-        <v>113</v>
-      </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
@@ -1782,9 +1779,6 @@
       <c r="D26" t="s">
         <v>24</v>
       </c>
-      <c r="F26" t="s">
-        <v>125</v>
-      </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
@@ -1799,9 +1793,6 @@
       <c r="D27" t="s">
         <v>68</v>
       </c>
-      <c r="F27" t="s">
-        <v>126</v>
-      </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
@@ -1830,6 +1821,9 @@
       <c r="D29" t="s">
         <v>68</v>
       </c>
+      <c r="F29" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
@@ -1844,6 +1838,9 @@
       <c r="D30" t="s">
         <v>68</v>
       </c>
+      <c r="F30" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
@@ -1857,6 +1854,9 @@
       </c>
       <c r="D31" t="s">
         <v>68</v>
+      </c>
+      <c r="F31" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="32" spans="1:7">

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10309"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grantadams/Documents/GitHub/Rceattle/inst/extdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grant Adams\Documents\GitHub\Rceattle\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3E6C21-7787-2F40-8A10-10FEFA542231}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="12340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="465" windowWidth="25605" windowHeight="12345"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data_names" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="139">
   <si>
     <t>nspp</t>
   </si>
@@ -397,9 +396,6 @@
     <t>Time_varying_sel</t>
   </si>
   <si>
-    <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity. 0 = no, 1 = random walk from mean selectivity following Dorn 2018, 2 = random effect.</t>
-  </si>
-  <si>
     <t>Sel_sd_prior</t>
   </si>
   <si>
@@ -415,9 +411,6 @@
     <t>The sd to use for the random walk of time varying q if set to 1</t>
   </si>
   <si>
-    <t>Wether a time-varying q should be estimated. 0 = no, 1 = random walk from mean selectivity following Dorn 2018, 2 = random effect.</t>
-  </si>
-  <si>
     <t>Selectivity_index</t>
   </si>
   <si>
@@ -437,13 +430,19 @@
   </si>
   <si>
     <t>NOTE: Columns for ages are index by 1 trhough nages, but are place holders.</t>
+  </si>
+  <si>
+    <t>Wether a time-varying q should be estimated. 0 = no, 1 = random walk from mean selectivity following Dorn 2018, 2 = random effect, 3 = time blocks with no penalty</t>
+  </si>
+  <si>
+    <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity. 0 = no, 1 = random walk from mean selectivity following Dorn 2018, 2 = random effect, 3 = time blocks with no penality</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1259,17 +1258,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="119.5" customWidth="1"/>
-    <col min="4" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="119.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -1292,7 +1291,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1312,7 +1311,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1332,7 +1331,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1352,7 +1351,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1372,7 +1371,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1392,7 +1391,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1412,7 +1411,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1432,7 +1431,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1452,7 +1451,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1472,7 +1471,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1492,7 +1491,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1512,7 +1511,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1532,7 +1531,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1552,7 +1551,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1566,13 +1565,13 @@
         <v>13</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G15" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1586,13 +1585,13 @@
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G16" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1612,7 +1611,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1632,7 +1631,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1649,10 +1648,10 @@
         <v>124</v>
       </c>
       <c r="G19" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1666,13 +1665,13 @@
         <v>18</v>
       </c>
       <c r="F20" t="s">
+        <v>125</v>
+      </c>
+      <c r="G20" t="s">
         <v>126</v>
       </c>
-      <c r="G20" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1686,13 +1685,13 @@
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G21" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1706,13 +1705,13 @@
         <v>20</v>
       </c>
       <c r="F22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G22" t="s">
         <v>129</v>
       </c>
-      <c r="G22" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1726,13 +1725,13 @@
         <v>21</v>
       </c>
       <c r="F23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G23" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1746,13 +1745,13 @@
         <v>22</v>
       </c>
       <c r="F24" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1766,7 +1765,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1780,7 +1779,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1794,7 +1793,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1808,7 +1807,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1825,7 +1824,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1842,7 +1841,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1856,10 +1855,10 @@
         <v>68</v>
       </c>
       <c r="F31" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1873,7 +1872,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1887,7 +1886,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1901,7 +1900,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1915,7 +1914,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1929,7 +1928,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1943,7 +1942,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1957,7 +1956,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1971,7 +1970,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1985,7 +1984,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1999,7 +1998,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2013,7 +2012,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2027,7 +2026,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="0" yWindow="465" windowWidth="25605" windowHeight="12345"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data_names" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="139">
   <si>
     <t>nspp</t>
   </si>
@@ -372,15 +372,9 @@
     <t>Estimate catchability? (0 = no; 1 = yes, 2 = analytical from Ludwig and Walters 1994)</t>
   </si>
   <si>
-    <t>Estimate_sigma_index</t>
-  </si>
-  <si>
     <t>Estimate survey variance (0 = use CV from srv_biom, 1 = yes, 2 = analytically estimate following (Ludwig and Walters 1994)</t>
   </si>
   <si>
-    <t>Sigma_index_prior</t>
-  </si>
-  <si>
     <t>Starting value to be used if Estimate_sigma_index = 1</t>
   </si>
   <si>
@@ -399,7 +393,49 @@
     <t>NOTE: Lengths are index 1 through nlenths</t>
   </si>
   <si>
-    <t>NOTE: Columns for ages are index by 1 trhough nages</t>
+    <t>Time_varying_sel</t>
+  </si>
+  <si>
+    <t>Sel_sd_prior</t>
+  </si>
+  <si>
+    <t>The sd to use for the random walk of time varying selectivity if set to 1</t>
+  </si>
+  <si>
+    <t>Time_varying_q</t>
+  </si>
+  <si>
+    <t>Q_sd_prior</t>
+  </si>
+  <si>
+    <t>The sd to use for the random walk of time varying q if set to 1</t>
+  </si>
+  <si>
+    <t>Selectivity_index</t>
+  </si>
+  <si>
+    <t>index to use if selectivitys of different surveys are to be the same</t>
+  </si>
+  <si>
+    <t>Q_index</t>
+  </si>
+  <si>
+    <t>index to use if catchability coefficients are to be set the same</t>
+  </si>
+  <si>
+    <t>Sigma_survey_prior</t>
+  </si>
+  <si>
+    <t>Estimate_sigma_survey</t>
+  </si>
+  <si>
+    <t>NOTE: Columns for ages are index by 1 trhough nages, but are place holders.</t>
+  </si>
+  <si>
+    <t>Wether a time-varying q should be estimated. 0 = no, 1 = random walk from mean selectivity following Dorn 2018, 2 = random effect, 3 = time blocks with no penalty</t>
+  </si>
+  <si>
+    <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity. 0 = no, 1 = random walk from mean selectivity following Dorn 2018, 2 = random effect, 3 = time blocks with no penality</t>
   </si>
 </sst>
 </file>
@@ -1224,10 +1260,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="119.5703125" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="119.42578125" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -1529,10 +1565,10 @@
         <v>13</v>
       </c>
       <c r="F15" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G15" t="s">
         <v>117</v>
-      </c>
-      <c r="G15" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1549,10 +1585,10 @@
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="G16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1569,10 +1605,10 @@
         <v>15</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1589,10 +1625,10 @@
         <v>16</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G18" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1608,6 +1644,12 @@
       <c r="D19" t="s">
         <v>17</v>
       </c>
+      <c r="F19" t="s">
+        <v>124</v>
+      </c>
+      <c r="G19" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
@@ -1622,6 +1664,12 @@
       <c r="D20" t="s">
         <v>18</v>
       </c>
+      <c r="F20" t="s">
+        <v>125</v>
+      </c>
+      <c r="G20" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
@@ -1636,6 +1684,12 @@
       <c r="D21" t="s">
         <v>19</v>
       </c>
+      <c r="F21" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
@@ -1650,6 +1704,12 @@
       <c r="D22" t="s">
         <v>20</v>
       </c>
+      <c r="F22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G22" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
@@ -1664,6 +1724,12 @@
       <c r="D23" t="s">
         <v>21</v>
       </c>
+      <c r="F23" t="s">
+        <v>130</v>
+      </c>
+      <c r="G23" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
@@ -1678,6 +1744,12 @@
       <c r="D24" t="s">
         <v>22</v>
       </c>
+      <c r="F24" t="s">
+        <v>132</v>
+      </c>
+      <c r="G24" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
@@ -1692,9 +1764,6 @@
       <c r="D25" t="s">
         <v>23</v>
       </c>
-      <c r="F25" t="s">
-        <v>113</v>
-      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
@@ -1709,9 +1778,6 @@
       <c r="D26" t="s">
         <v>24</v>
       </c>
-      <c r="F26" t="s">
-        <v>125</v>
-      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
@@ -1726,9 +1792,6 @@
       <c r="D27" t="s">
         <v>68</v>
       </c>
-      <c r="F27" t="s">
-        <v>126</v>
-      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
@@ -1757,6 +1820,9 @@
       <c r="D29" t="s">
         <v>68</v>
       </c>
+      <c r="F29" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
@@ -1771,6 +1837,9 @@
       <c r="D30" t="s">
         <v>68</v>
       </c>
+      <c r="F30" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
@@ -1784,6 +1853,9 @@
       </c>
       <c r="D31" t="s">
         <v>68</v>
+      </c>
+      <c r="F31" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="139">
   <si>
     <t>nspp</t>
   </si>
@@ -294,9 +294,6 @@
     <t>Nselages</t>
   </si>
   <si>
-    <t>Catch_units</t>
-  </si>
-  <si>
     <t>Weight_index</t>
   </si>
   <si>
@@ -324,9 +321,6 @@
     <t>Number of ages to estimate non-parametric selectivity for Selectivity = 2. Not used otherwise</t>
   </si>
   <si>
-    <t>Units used for survey: 1 = kg; 2 = numbers</t>
-  </si>
-  <si>
     <t>Weight-at-age (wt) index to use for calculation of derived quantities</t>
   </si>
   <si>
@@ -436,6 +430,12 @@
   </si>
   <si>
     <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity. 0 = no, 1 = random walk from mean selectivity following Dorn 2018, 2 = random effect, 3 = time blocks with no penality</t>
+  </si>
+  <si>
+    <t>Fit_0no_1yes</t>
+  </si>
+  <si>
+    <t>Index of wether data should be included in the likelihood and associated parameters estimated.</t>
   </si>
 </sst>
 </file>
@@ -1282,10 +1282,10 @@
         <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>40</v>
@@ -1308,7 +1308,7 @@
         <v>86</v>
       </c>
       <c r="G2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1328,7 +1328,7 @@
         <v>87</v>
       </c>
       <c r="G3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1345,10 +1345,10 @@
         <v>60</v>
       </c>
       <c r="F4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G4" t="s">
         <v>109</v>
-      </c>
-      <c r="G4" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1365,10 +1365,10 @@
         <v>60</v>
       </c>
       <c r="F5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5" t="s">
         <v>110</v>
-      </c>
-      <c r="G5" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1388,7 +1388,7 @@
         <v>88</v>
       </c>
       <c r="G6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1405,10 +1405,10 @@
         <v>60</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="G7" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1419,16 +1419,16 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
         <v>60</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>60</v>
       </c>
       <c r="F9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1464,11 +1464,11 @@
       <c r="D10" t="s">
         <v>60</v>
       </c>
-      <c r="F10" t="s">
-        <v>92</v>
+      <c r="F10" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="G10" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1485,10 +1485,10 @@
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1505,10 +1505,10 @@
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G12" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1524,11 +1524,11 @@
       <c r="D13" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>95</v>
+      <c r="F13" t="s">
+        <v>93</v>
       </c>
       <c r="G13" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1544,11 +1544,11 @@
       <c r="D14" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>114</v>
+      <c r="F14" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="G14" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1565,10 +1565,10 @@
         <v>13</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1585,10 +1585,10 @@
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G16" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1605,10 +1605,10 @@
         <v>15</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1625,10 +1625,10 @@
         <v>16</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1645,10 +1645,10 @@
         <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G19" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1665,10 +1665,10 @@
         <v>18</v>
       </c>
       <c r="F20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G20" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1685,10 +1685,10 @@
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1705,10 +1705,10 @@
         <v>20</v>
       </c>
       <c r="F22" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1725,10 +1725,10 @@
         <v>21</v>
       </c>
       <c r="F23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1745,10 +1745,10 @@
         <v>22</v>
       </c>
       <c r="F24" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G24" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1815,13 +1815,13 @@
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s">
         <v>68</v>
       </c>
       <c r="F29" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1838,7 +1838,7 @@
         <v>68</v>
       </c>
       <c r="F30" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1855,7 +1855,7 @@
         <v>68</v>
       </c>
       <c r="F31" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="153">
   <si>
     <t>nspp</t>
   </si>
@@ -436,6 +436,48 @@
   </si>
   <si>
     <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity. 0 = no, 1 = random walk from mean selectivity following Dorn 2018, 2 = random effect, 3 = time blocks with no penality</t>
+  </si>
+  <si>
+    <t>projyr</t>
+  </si>
+  <si>
+    <t>End year of the forecast</t>
+  </si>
+  <si>
+    <t>nsex</t>
+  </si>
+  <si>
+    <t>spawn_month</t>
+  </si>
+  <si>
+    <t>Spawning month of the population to adjust the numbers spawning</t>
+  </si>
+  <si>
+    <t>R_sexr</t>
+  </si>
+  <si>
+    <t>Percent of recruitment that is female (ignored if nsex = 1)</t>
+  </si>
+  <si>
+    <t>Number of sexes to model in the population (1 = combined/1sex, 2 = models both female/male)</t>
+  </si>
+  <si>
+    <t>minage</t>
+  </si>
+  <si>
+    <t>Minimum age for each population (i.e.does recruitment correspond to age 0, 1, 2?)</t>
+  </si>
+  <si>
+    <t>ssb_wt_index</t>
+  </si>
+  <si>
+    <t>Weight-at-age (wt) index to use for calculation of each species spawning biomass</t>
+  </si>
+  <si>
+    <t>sigma_rec_prior</t>
+  </si>
+  <si>
+    <t>Standard deviation to use for recruitment</t>
   </si>
 </sst>
 </file>
@@ -1259,7 +1301,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
@@ -1356,10 +1398,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>139</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="D5" t="s">
         <v>60</v>
@@ -1376,10 +1418,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>146</v>
       </c>
       <c r="D6" t="s">
         <v>60</v>
@@ -1396,10 +1438,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>142</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>143</v>
       </c>
       <c r="D7" t="s">
         <v>60</v>
@@ -1416,10 +1458,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>144</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
         <v>60</v>
@@ -1436,10 +1478,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
         <v>60</v>
@@ -1456,10 +1498,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>147</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>148</v>
       </c>
       <c r="D10" t="s">
         <v>60</v>
@@ -1476,13 +1518,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
         <v>93</v>
@@ -1496,13 +1538,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F12" t="s">
         <v>94</v>
@@ -1516,13 +1558,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>149</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="D13" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>95</v>
@@ -1536,13 +1578,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>114</v>
@@ -1556,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>152</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>135</v>
@@ -1576,13 +1618,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>134</v>
@@ -1596,13 +1638,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>119</v>
@@ -1613,16 +1655,16 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>121</v>
@@ -1633,16 +1675,16 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
         <v>124</v>
@@ -1653,16 +1695,16 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F20" t="s">
         <v>125</v>
@@ -1673,16 +1715,16 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F21" t="s">
         <v>127</v>
@@ -1693,16 +1735,16 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F22" t="s">
         <v>128</v>
@@ -1713,16 +1755,16 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F23" t="s">
         <v>130</v>
@@ -1733,16 +1775,16 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D24" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F24" t="s">
         <v>132</v>
@@ -1753,72 +1795,72 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D27" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D28" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="D29" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="F29" t="s">
         <v>113</v>
@@ -1826,16 +1868,16 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D30" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="F30" t="s">
         <v>123</v>
@@ -1843,16 +1885,16 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D31" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="F31" t="s">
         <v>136</v>
@@ -1860,41 +1902,41 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D32" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C33" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D33" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D34" t="s">
         <v>68</v>
@@ -1902,13 +1944,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D35" t="s">
         <v>68</v>
@@ -1916,13 +1958,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="D36" t="s">
         <v>68</v>
@@ -1930,13 +1972,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D37" t="s">
         <v>68</v>
@@ -1944,99 +1986,197 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C38" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D38" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C39" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D39" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C40" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D40" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D41" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="C42" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D42" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C43" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D43" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
+        <v>36</v>
+      </c>
+      <c r="B44" t="s">
+        <v>35</v>
+      </c>
+      <c r="C44" t="s">
+        <v>72</v>
+      </c>
+      <c r="D44" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>37</v>
+      </c>
+      <c r="B45" t="s">
+        <v>36</v>
+      </c>
+      <c r="C45" t="s">
+        <v>73</v>
+      </c>
+      <c r="D45" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>38</v>
+      </c>
+      <c r="B46" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46" t="s">
+        <v>74</v>
+      </c>
+      <c r="D46" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>39</v>
+      </c>
+      <c r="B47" t="s">
+        <v>38</v>
+      </c>
+      <c r="C47" t="s">
+        <v>76</v>
+      </c>
+      <c r="D47" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>40</v>
+      </c>
+      <c r="B48" t="s">
+        <v>78</v>
+      </c>
+      <c r="C48" t="s">
+        <v>82</v>
+      </c>
+      <c r="D48" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>41</v>
+      </c>
+      <c r="B49" t="s">
+        <v>79</v>
+      </c>
+      <c r="C49" t="s">
+        <v>83</v>
+      </c>
+      <c r="D49" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>42</v>
+      </c>
+      <c r="B50" t="s">
+        <v>80</v>
+      </c>
+      <c r="C50" t="s">
+        <v>84</v>
+      </c>
+      <c r="D50" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B51" t="s">
         <v>81</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C51" t="s">
         <v>85</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D51" t="s">
         <v>81</v>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="155">
   <si>
     <t>nspp</t>
   </si>
@@ -478,6 +478,12 @@
   </si>
   <si>
     <t>Standard deviation to use for recruitment</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>sex codes: 0=combined; 1=use female only; 2=use male only</t>
   </si>
 </sst>
 </file>
@@ -1447,10 +1453,10 @@
         <v>60</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>153</v>
       </c>
       <c r="G7" t="s">
-        <v>99</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1467,10 +1473,10 @@
         <v>60</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1487,10 +1493,10 @@
         <v>60</v>
       </c>
       <c r="F9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1507,10 +1513,10 @@
         <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1527,10 +1533,10 @@
         <v>60</v>
       </c>
       <c r="F11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1547,10 +1553,10 @@
         <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G12" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1566,11 +1572,11 @@
       <c r="D13" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>95</v>
+      <c r="F13" t="s">
+        <v>94</v>
       </c>
       <c r="G13" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1586,11 +1592,11 @@
       <c r="D14" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>114</v>
+      <c r="F14" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="G14" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1606,11 +1612,11 @@
       <c r="D15" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>135</v>
+      <c r="F15" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="G15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1626,11 +1632,11 @@
       <c r="D16" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>134</v>
+      <c r="F16" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="G16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1646,11 +1652,11 @@
       <c r="D17" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>119</v>
+      <c r="F17" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="G17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1667,10 +1673,10 @@
         <v>9</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1686,11 +1692,11 @@
       <c r="D19" t="s">
         <v>10</v>
       </c>
-      <c r="F19" t="s">
-        <v>124</v>
+      <c r="F19" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="G19" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1707,10 +1713,10 @@
         <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G20" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1727,10 +1733,10 @@
         <v>12</v>
       </c>
       <c r="F21" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G21" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1747,10 +1753,10 @@
         <v>13</v>
       </c>
       <c r="F22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G22" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1767,10 +1773,10 @@
         <v>14</v>
       </c>
       <c r="F23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1787,10 +1793,10 @@
         <v>15</v>
       </c>
       <c r="F24" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G24" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1805,6 +1811,12 @@
       </c>
       <c r="D25" t="s">
         <v>16</v>
+      </c>
+      <c r="F25" t="s">
+        <v>132</v>
+      </c>
+      <c r="G25" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10810"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grant Adams\Documents\GitHub\Rceattle\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grantadams/Documents/GitHub/Rceattle/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0BF229-F42D-1249-8354-90EAE7EBF434}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="465" windowWidth="25605" windowHeight="12345"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="12340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data_names" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="161">
   <si>
     <t>nspp</t>
   </si>
@@ -201,9 +202,6 @@
     <t>Weight-at-age (wt) to use for calculation of derived quantities (SSB, Consumption/Ration, Suitability, Total Catch, Survey Biomass, etc). Can have multiple weight-at-age data-sets for each species, but must be full for all years of the hindcast.</t>
   </si>
   <si>
-    <t>control</t>
-  </si>
-  <si>
     <t>Sheet location</t>
   </si>
   <si>
@@ -225,9 +223,6 @@
     <t>data_list Object name</t>
   </si>
   <si>
-    <t>bioenergetics_control</t>
-  </si>
-  <si>
     <t>This scales the maximum consumption used for ration for each species; Pvalue is in Cmax*fT*Pvalue*Page</t>
   </si>
   <si>
@@ -252,9 +247,6 @@
     <t>Annual relative foraging rate by age</t>
   </si>
   <si>
-    <t>Temp_data</t>
-  </si>
-  <si>
     <t>UobsAge</t>
   </si>
   <si>
@@ -279,12 +271,6 @@
     <t>Stomach proportion by weight for each predator, prey, predator length prey length combination. Can also be year specific by including the column, "Year"</t>
   </si>
   <si>
-    <t>Survey_name</t>
-  </si>
-  <si>
-    <t>Survey_code</t>
-  </si>
-  <si>
     <t>Species</t>
   </si>
   <si>
@@ -306,15 +292,6 @@
     <t>Estimate_q</t>
   </si>
   <si>
-    <t>log_q_start</t>
-  </si>
-  <si>
-    <t>Name of survey</t>
-  </si>
-  <si>
-    <t>Index of survey ACROSS species</t>
-  </si>
-  <si>
     <t>Species number</t>
   </si>
   <si>
@@ -348,18 +325,6 @@
     <t>Column names</t>
   </si>
   <si>
-    <t>Fishery_name</t>
-  </si>
-  <si>
-    <t>Fishery_code</t>
-  </si>
-  <si>
-    <t>Name of fishery</t>
-  </si>
-  <si>
-    <t>Index of fishery ACROSS species</t>
-  </si>
-  <si>
     <t>NOTE: Most objects are ordered by species code if not specified</t>
   </si>
   <si>
@@ -378,15 +343,9 @@
     <t>Starting value to be used if Estimate_sigma_index = 1</t>
   </si>
   <si>
-    <t>Estimate_sigma_catch</t>
-  </si>
-  <si>
     <t>Estimate fishery variance (0 = use CV from srv_biom, 1 = yes, 2 = analytically estimate following (Ludwig and Walters 1994)</t>
   </si>
   <si>
-    <t>Sigma_catch_prior</t>
-  </si>
-  <si>
     <t>Starting value to be used if Estimate_sigma_catch = 1</t>
   </si>
   <si>
@@ -399,9 +358,6 @@
     <t>Sel_sd_prior</t>
   </si>
   <si>
-    <t>The sd to use for the random walk of time varying selectivity if set to 1</t>
-  </si>
-  <si>
     <t>Time_varying_q</t>
   </si>
   <si>
@@ -423,21 +379,12 @@
     <t>index to use if catchability coefficients are to be set the same</t>
   </si>
   <si>
-    <t>Sigma_survey_prior</t>
-  </si>
-  <si>
-    <t>Estimate_sigma_survey</t>
-  </si>
-  <si>
     <t>NOTE: Columns for ages are index by 1 trhough nages, but are place holders.</t>
   </si>
   <si>
     <t>Wether a time-varying q should be estimated. 0 = no, 1 = random walk from mean selectivity following Dorn 2018, 2 = random effect, 3 = time blocks with no penalty</t>
   </si>
   <si>
-    <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity. 0 = no, 1 = random walk from mean selectivity following Dorn 2018, 2 = random effect, 3 = time blocks with no penality</t>
-  </si>
-  <si>
     <t>projyr</t>
   </si>
   <si>
@@ -483,13 +430,85 @@
     <t>Sex</t>
   </si>
   <si>
-    <t>sex codes: 0=combined; 1=use female only; 2=use male only</t>
+    <t>fleet_control</t>
+  </si>
+  <si>
+    <t>Fleet_name</t>
+  </si>
+  <si>
+    <t>Fleet_code</t>
+  </si>
+  <si>
+    <t>Name of survey or fishery</t>
+  </si>
+  <si>
+    <t>Index of survey/fishery ACROSS species</t>
+  </si>
+  <si>
+    <t>Fleet_type</t>
+  </si>
+  <si>
+    <t>0 = Do not estimate; 1 = Fishery; 2 = Survey</t>
+  </si>
+  <si>
+    <t>The sd to use for the random walk of time varying selectivity if set to 1. If selectivity is set to type = 2 (non-parametric) this value will be the 2nd penalty on selectivity.</t>
+  </si>
+  <si>
+    <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity. 0 = no, 1 = random walk from mean selectivity following Dorn 2018, 2 = random effect, 3 = time blocks with no penality. If selectivity is set to type = 2 (non-parametric) this value will be the 1st penalty on selectivity.</t>
+  </si>
+  <si>
+    <t>Age_first_selected</t>
+  </si>
+  <si>
+    <t>Age at which selectivity is non-zero</t>
+  </si>
+  <si>
+    <t>Acuumulation_age_lower</t>
+  </si>
+  <si>
+    <t>Ages below this will be grouped to this age for composition data. For example, if set to 2, comp data for age 2 will include 1 and 2 year olds.</t>
+  </si>
+  <si>
+    <t>Acuumulation_age_upper</t>
+  </si>
+  <si>
+    <t>Ages above this will be grouped to this age for composition data. For example, if set to 9 for a species with 10 ages, comp data for age 9 will include 9 and 10 year olds.</t>
+  </si>
+  <si>
+    <t>Log_q_prior</t>
+  </si>
+  <si>
+    <t>Survey_sd_prior</t>
+  </si>
+  <si>
+    <t>Estimate_survey_sd</t>
+  </si>
+  <si>
+    <t>Estimate_catch_sd</t>
+  </si>
+  <si>
+    <t>Catch_sd_prior</t>
+  </si>
+  <si>
+    <t>Comp_weights</t>
+  </si>
+  <si>
+    <t>Composition weights to be used for multinomial likelihood. These are multiplied. After running model, these will update to McAllister &amp; Ianelli 1997 weights using the harmonic mean.</t>
+  </si>
+  <si>
+    <t>proj_F_prop</t>
+  </si>
+  <si>
+    <t>The proportion of future fishing mortality assigned to this fleet</t>
+  </si>
+  <si>
+    <t>sex codes: 0=combined; 1=use female only; 2=use male only; 3 = joint female and male</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1306,40 +1325,40 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G51"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="119.42578125" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="119.5" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1350,16 +1369,16 @@
         <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="F2" t="s">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="G2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1370,16 +1389,16 @@
         <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="F3" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="G3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1390,96 +1409,96 @@
         <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="F4" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="G4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="C5" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="F5" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C6" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="G6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="C7" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="F7" t="s">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="G7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="C8" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1490,36 +1509,36 @@
         <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="F9" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="F10" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="G10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1530,16 +1549,16 @@
         <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="F11" t="s">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="G11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1550,36 +1569,36 @@
         <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="F12" t="s">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="G12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" t="s">
+        <v>132</v>
+      </c>
+      <c r="D13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" t="s">
         <v>149</v>
       </c>
-      <c r="C13" t="s">
+      <c r="G13" t="s">
         <v>150</v>
       </c>
-      <c r="D13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F13" t="s">
-        <v>94</v>
-      </c>
-      <c r="G13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1587,39 +1606,39 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" t="s">
+        <v>136</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G14" t="s">
         <v>103</v>
       </c>
-      <c r="D14" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="C15" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>136</v>
+      </c>
+      <c r="F15" t="s">
+        <v>87</v>
       </c>
       <c r="G15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1630,16 +1649,16 @@
         <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
+      </c>
+      <c r="F16" t="s">
+        <v>88</v>
       </c>
       <c r="G16" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1650,16 +1669,16 @@
         <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
+      </c>
+      <c r="F17" t="s">
+        <v>117</v>
       </c>
       <c r="G17" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>10</v>
       </c>
@@ -1670,16 +1689,16 @@
         <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>119</v>
+        <v>136</v>
+      </c>
+      <c r="F18" t="s">
+        <v>89</v>
       </c>
       <c r="G18" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>11</v>
       </c>
@@ -1690,16 +1709,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>121</v>
+        <v>136</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="G19" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>12</v>
       </c>
@@ -1710,16 +1729,16 @@
         <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c r="F20" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="G20" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>13</v>
       </c>
@@ -1730,16 +1749,16 @@
         <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>12</v>
+        <v>136</v>
       </c>
       <c r="F21" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="G21" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>14</v>
       </c>
@@ -1750,16 +1769,16 @@
         <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" t="s">
-        <v>127</v>
+        <v>136</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>153</v>
       </c>
       <c r="G22" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>15</v>
       </c>
@@ -1770,16 +1789,16 @@
         <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" t="s">
-        <v>128</v>
+        <v>136</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="G23" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>16</v>
       </c>
@@ -1790,16 +1809,16 @@
         <v>55</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" t="s">
-        <v>130</v>
+        <v>136</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>154</v>
       </c>
       <c r="G24" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>17</v>
       </c>
@@ -1810,16 +1829,16 @@
         <v>56</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" t="s">
-        <v>132</v>
+        <v>136</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="G25" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>18</v>
       </c>
@@ -1830,10 +1849,16 @@
         <v>57</v>
       </c>
       <c r="D26" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G26" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>19</v>
       </c>
@@ -1844,10 +1869,16 @@
         <v>58</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="F27" t="s">
+        <v>86</v>
+      </c>
+      <c r="G27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>20</v>
       </c>
@@ -1858,10 +1889,16 @@
         <v>59</v>
       </c>
       <c r="D28" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G28" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>21</v>
       </c>
@@ -1869,16 +1906,10 @@
         <v>20</v>
       </c>
       <c r="C29" t="s">
-        <v>62</v>
-      </c>
-      <c r="D29" t="s">
-        <v>20</v>
-      </c>
-      <c r="F29" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>22</v>
       </c>
@@ -1886,16 +1917,16 @@
         <v>21</v>
       </c>
       <c r="C30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="F30" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+      <c r="G30" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>23</v>
       </c>
@@ -1903,16 +1934,10 @@
         <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>64</v>
-      </c>
-      <c r="D31" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>24</v>
       </c>
@@ -1920,13 +1945,10 @@
         <v>23</v>
       </c>
       <c r="C32" t="s">
-        <v>65</v>
-      </c>
-      <c r="D32" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>25</v>
       </c>
@@ -1934,13 +1956,13 @@
         <v>24</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="F33" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>26</v>
       </c>
@@ -1948,13 +1970,13 @@
         <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>75</v>
-      </c>
-      <c r="D34" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="F34" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>27</v>
       </c>
@@ -1962,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
-      </c>
-      <c r="D35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="F35" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>28</v>
       </c>
@@ -1976,13 +1998,11 @@
         <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D36" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>29</v>
       </c>
@@ -1990,13 +2010,10 @@
         <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>70</v>
-      </c>
-      <c r="D37" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>30</v>
       </c>
@@ -2004,13 +2021,10 @@
         <v>29</v>
       </c>
       <c r="C38" t="s">
-        <v>71</v>
-      </c>
-      <c r="D38" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>31</v>
       </c>
@@ -2018,13 +2032,10 @@
         <v>30</v>
       </c>
       <c r="C39" t="s">
-        <v>72</v>
-      </c>
-      <c r="D39" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>32</v>
       </c>
@@ -2032,13 +2043,10 @@
         <v>31</v>
       </c>
       <c r="C40" t="s">
-        <v>72</v>
-      </c>
-      <c r="D40" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>33</v>
       </c>
@@ -2046,13 +2054,10 @@
         <v>32</v>
       </c>
       <c r="C41" t="s">
-        <v>72</v>
-      </c>
-      <c r="D41" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>34</v>
       </c>
@@ -2060,13 +2065,10 @@
         <v>33</v>
       </c>
       <c r="C42" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>35</v>
       </c>
@@ -2074,13 +2076,10 @@
         <v>34</v>
       </c>
       <c r="C43" t="s">
-        <v>72</v>
-      </c>
-      <c r="D43" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>36</v>
       </c>
@@ -2088,13 +2087,10 @@
         <v>35</v>
       </c>
       <c r="C44" t="s">
-        <v>72</v>
-      </c>
-      <c r="D44" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>37</v>
       </c>
@@ -2102,13 +2098,10 @@
         <v>36</v>
       </c>
       <c r="C45" t="s">
-        <v>73</v>
-      </c>
-      <c r="D45" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>38</v>
       </c>
@@ -2116,13 +2109,10 @@
         <v>37</v>
       </c>
       <c r="C46" t="s">
-        <v>74</v>
-      </c>
-      <c r="D46" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>39</v>
       </c>
@@ -2130,66 +2120,51 @@
         <v>38</v>
       </c>
       <c r="C47" t="s">
-        <v>76</v>
-      </c>
-      <c r="D47" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C48" t="s">
-        <v>82</v>
-      </c>
-      <c r="D48" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>41</v>
       </c>
       <c r="B49" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>83</v>
-      </c>
-      <c r="D49" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>42</v>
       </c>
       <c r="B50" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C50" t="s">
-        <v>84</v>
-      </c>
-      <c r="D50" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>43</v>
       </c>
       <c r="B51" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C51" t="s">
-        <v>85</v>
-      </c>
-      <c r="D51" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10810"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grantadams/Documents/GitHub/Rceattle/inst/extdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grant Adams\Documents\GitHub\Rceattle\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0BF229-F42D-1249-8354-90EAE7EBF434}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="12340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="465" windowWidth="25605" windowHeight="12345"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data_names" sheetId="1" r:id="rId1"/>
@@ -295,9 +294,6 @@
     <t>Species number</t>
   </si>
   <si>
-    <t>Selectivity to use for the species: 0 = empirical selectivity provided in srv_emp_sel; 1 = logistic selectivity; 2 = non-parametric selecitivty sensu Ianelli et al 2018; 3 = double logistic</t>
-  </si>
-  <si>
     <t>Number of ages to estimate non-parametric selectivity for Selectivity = 2. Not used otherwise</t>
   </si>
   <si>
@@ -503,12 +499,15 @@
   </si>
   <si>
     <t>sex codes: 0=combined; 1=use female only; 2=use male only; 3 = joint female and male</t>
+  </si>
+  <si>
+    <t>Selectivity to use for the species: 0 = empirical selectivity provided in srv_emp_sel; 1 = logistic selectivity; 2 = non-parametric selecitivty sensu Ianelli et al 2018; 3 = double logistic; 4 = descending logistic</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1325,17 +1324,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="119.5" customWidth="1"/>
-    <col min="4" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="119.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -1349,16 +1348,16 @@
         <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1369,16 +1368,16 @@
         <v>41</v>
       </c>
       <c r="D2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2" t="s">
         <v>136</v>
       </c>
-      <c r="F2" t="s">
-        <v>137</v>
-      </c>
       <c r="G2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1389,16 +1388,16 @@
         <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1409,27 +1408,27 @@
         <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G4" t="s">
         <v>141</v>
       </c>
-      <c r="G4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" t="s">
         <v>121</v>
       </c>
-      <c r="C5" t="s">
-        <v>122</v>
-      </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F5" t="s">
         <v>83</v>
@@ -1438,67 +1437,67 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G6" t="s">
         <v>115</v>
       </c>
-      <c r="G6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" t="s">
         <v>124</v>
       </c>
-      <c r="C7" t="s">
-        <v>125</v>
-      </c>
       <c r="D7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F7" t="s">
         <v>84</v>
       </c>
       <c r="G7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" t="s">
         <v>126</v>
       </c>
-      <c r="C8" t="s">
-        <v>127</v>
-      </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F8" t="s">
         <v>85</v>
       </c>
       <c r="G8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1509,36 +1508,36 @@
         <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G9" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" t="s">
         <v>129</v>
       </c>
-      <c r="C10" t="s">
-        <v>130</v>
-      </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G10" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1549,16 +1548,16 @@
         <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F11" t="s">
+        <v>144</v>
+      </c>
+      <c r="G11" t="s">
         <v>145</v>
       </c>
-      <c r="G11" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1569,36 +1568,36 @@
         <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F12" t="s">
+        <v>146</v>
+      </c>
+      <c r="G12" t="s">
         <v>147</v>
       </c>
-      <c r="G12" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" t="s">
         <v>131</v>
       </c>
-      <c r="C13" t="s">
-        <v>132</v>
-      </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F13" t="s">
+        <v>148</v>
+      </c>
+      <c r="G13" t="s">
         <v>149</v>
       </c>
-      <c r="G13" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1606,39 +1605,39 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" t="s">
         <v>102</v>
       </c>
-      <c r="G14" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" t="s">
         <v>133</v>
       </c>
-      <c r="C15" t="s">
-        <v>134</v>
-      </c>
       <c r="D15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F15" t="s">
         <v>87</v>
       </c>
       <c r="G15" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1649,16 +1648,16 @@
         <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F16" t="s">
         <v>88</v>
       </c>
       <c r="G16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1669,16 +1668,16 @@
         <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F17" t="s">
+        <v>116</v>
+      </c>
+      <c r="G17" t="s">
         <v>117</v>
       </c>
-      <c r="G17" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>10</v>
       </c>
@@ -1689,16 +1688,16 @@
         <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F18" t="s">
         <v>89</v>
       </c>
       <c r="G18" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>11</v>
       </c>
@@ -1709,16 +1708,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G19" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>12</v>
       </c>
@@ -1729,16 +1728,16 @@
         <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G20" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>13</v>
       </c>
@@ -1749,16 +1748,16 @@
         <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F21" t="s">
+        <v>112</v>
+      </c>
+      <c r="G21" t="s">
         <v>113</v>
       </c>
-      <c r="G21" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>14</v>
       </c>
@@ -1769,16 +1768,16 @@
         <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G22" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>15</v>
       </c>
@@ -1789,16 +1788,16 @@
         <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G23" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>16</v>
       </c>
@@ -1809,16 +1808,16 @@
         <v>55</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G24" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>17</v>
       </c>
@@ -1829,16 +1828,16 @@
         <v>56</v>
       </c>
       <c r="D25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G25" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>18</v>
       </c>
@@ -1849,16 +1848,16 @@
         <v>57</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F26" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G26" t="s">
         <v>156</v>
       </c>
-      <c r="G26" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>19</v>
       </c>
@@ -1869,16 +1868,16 @@
         <v>58</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F27" t="s">
         <v>86</v>
       </c>
       <c r="G27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>20</v>
       </c>
@@ -1889,16 +1888,16 @@
         <v>59</v>
       </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F28" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="G28" t="s">
         <v>158</v>
       </c>
-      <c r="G28" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>21</v>
       </c>
@@ -1909,7 +1908,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>22</v>
       </c>
@@ -1920,13 +1919,13 @@
         <v>62</v>
       </c>
       <c r="F30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G30" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>23</v>
       </c>
@@ -1937,7 +1936,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>24</v>
       </c>
@@ -1948,7 +1947,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>25</v>
       </c>
@@ -1959,10 +1958,10 @@
         <v>65</v>
       </c>
       <c r="F33" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26</v>
       </c>
@@ -1973,10 +1972,10 @@
         <v>73</v>
       </c>
       <c r="F34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>27</v>
       </c>
@@ -1987,10 +1986,10 @@
         <v>67</v>
       </c>
       <c r="F35" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>28</v>
       </c>
@@ -1998,11 +1997,11 @@
         <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F36" s="4"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>29</v>
       </c>
@@ -2013,7 +2012,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>30</v>
       </c>
@@ -2024,7 +2023,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>31</v>
       </c>
@@ -2035,7 +2034,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>32</v>
       </c>
@@ -2046,7 +2045,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>33</v>
       </c>
@@ -2057,7 +2056,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>34</v>
       </c>
@@ -2068,7 +2067,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>35</v>
       </c>
@@ -2079,7 +2078,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>36</v>
       </c>
@@ -2090,7 +2089,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>37</v>
       </c>
@@ -2101,7 +2100,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>38</v>
       </c>
@@ -2112,7 +2111,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>39</v>
       </c>
@@ -2123,7 +2122,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>40</v>
       </c>
@@ -2134,7 +2133,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>41</v>
       </c>
@@ -2145,7 +2144,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>42</v>
       </c>
@@ -2156,7 +2155,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>43</v>
       </c>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -450,9 +450,6 @@
     <t>The sd to use for the random walk of time varying selectivity if set to 1. If selectivity is set to type = 2 (non-parametric) this value will be the 2nd penalty on selectivity.</t>
   </si>
   <si>
-    <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity. 0 = no, 1 = random walk from mean selectivity following Dorn 2018, 2 = random effect, 3 = time blocks with no penality. If selectivity is set to type = 2 (non-parametric) this value will be the 1st penalty on selectivity.</t>
-  </si>
-  <si>
     <t>Age_first_selected</t>
   </si>
   <si>
@@ -502,6 +499,9 @@
   </si>
   <si>
     <t>Selectivity to use for the species: 0 = empirical selectivity provided in srv_emp_sel; 1 = logistic selectivity; 2 = non-parametric selecitivty sensu Ianelli et al 2018; 3 = double logistic; 4 = descending logistic</t>
+  </si>
+  <si>
+    <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity, or descending logistic. 0 = no, 1 = penalized deviates given sel_sd_prior, 2 = random effect, 3 = time blocks with no penality, 4 = random walk following Dorn, 5 = random walk on ascending portion of double logistic. If selectivity is set to type = 2 (non-parametric) this value will be the 1st penalty on selectivity.</t>
   </si>
 </sst>
 </file>
@@ -1474,7 +1474,7 @@
         <v>84</v>
       </c>
       <c r="G7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1514,7 +1514,7 @@
         <v>109</v>
       </c>
       <c r="G9" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1551,10 +1551,10 @@
         <v>135</v>
       </c>
       <c r="F11" t="s">
+        <v>143</v>
+      </c>
+      <c r="G11" t="s">
         <v>144</v>
-      </c>
-      <c r="G11" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1571,10 +1571,10 @@
         <v>135</v>
       </c>
       <c r="F12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G12" t="s">
         <v>146</v>
-      </c>
-      <c r="G12" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1591,10 +1591,10 @@
         <v>135</v>
       </c>
       <c r="F13" t="s">
+        <v>147</v>
+      </c>
+      <c r="G13" t="s">
         <v>148</v>
-      </c>
-      <c r="G13" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1711,7 +1711,7 @@
         <v>135</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G19" t="s">
         <v>96</v>
@@ -1771,7 +1771,7 @@
         <v>135</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G22" t="s">
         <v>104</v>
@@ -1791,7 +1791,7 @@
         <v>135</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G23" t="s">
         <v>105</v>
@@ -1811,7 +1811,7 @@
         <v>135</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G24" t="s">
         <v>106</v>
@@ -1831,7 +1831,7 @@
         <v>135</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G25" t="s">
         <v>107</v>
@@ -1851,10 +1851,10 @@
         <v>135</v>
       </c>
       <c r="F26" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" t="s">
         <v>155</v>
-      </c>
-      <c r="G26" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1891,10 +1891,10 @@
         <v>135</v>
       </c>
       <c r="F28" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G28" t="s">
         <v>157</v>
-      </c>
-      <c r="G28" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1922,7 +1922,7 @@
         <v>134</v>
       </c>
       <c r="G30" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="160">
   <si>
     <t>nspp</t>
   </si>
@@ -48,30 +48,18 @@
     <t>stom_sample_size</t>
   </si>
   <si>
-    <t>srv_control</t>
-  </si>
-  <si>
     <t>srv_biom</t>
   </si>
   <si>
     <t>srv_emp_sel</t>
   </si>
   <si>
-    <t>srv_comp</t>
-  </si>
-  <si>
-    <t>fsh_control</t>
-  </si>
-  <si>
     <t>fsh_biom</t>
   </si>
   <si>
     <t>fsh_emp_sel</t>
   </si>
   <si>
-    <t>fsh_comp</t>
-  </si>
-  <si>
     <t>age_trans_matrix</t>
   </si>
   <si>
@@ -168,18 +156,9 @@
     <t>Sample size of diet data for each species (used when suitMode &gt; 0)</t>
   </si>
   <si>
-    <t>Survey data specifications</t>
-  </si>
-  <si>
     <t>Empirical selectivity for surveys (leave empty if not used)</t>
   </si>
   <si>
-    <t>Survey age or length composition data</t>
-  </si>
-  <si>
-    <t>Fishery data specifications</t>
-  </si>
-  <si>
     <t>Total catch in weight (kg) or numbers data</t>
   </si>
   <si>
@@ -189,9 +168,6 @@
     <t>Empirical selectivity for fisheries (leave empty if not used)</t>
   </si>
   <si>
-    <t>Fishery age or length composition data</t>
-  </si>
-  <si>
     <t>Age transition matrix (e.g. Age Length Key or ALK) used to convert age to length for length comp data. Can have multiple ALKs for a species specified by ALK_index.</t>
   </si>
   <si>
@@ -502,6 +478,27 @@
   </si>
   <si>
     <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity, or descending logistic. 0 = no, 1 = penalized deviates given sel_sd_prior, 2 = random effect, 3 = time blocks with no penality, 4 = random walk following Dorn, 5 = random walk on ascending portion of double logistic. If selectivity is set to type = 2 (non-parametric) this value will be the 1st penalty on selectivity.</t>
+  </si>
+  <si>
+    <t>Survey and fishery data specifications</t>
+  </si>
+  <si>
+    <t>comp</t>
+  </si>
+  <si>
+    <t>Survey/fishery age or length composition data</t>
+  </si>
+  <si>
+    <t>est_propF</t>
+  </si>
+  <si>
+    <t>propF_sigma</t>
+  </si>
+  <si>
+    <t>Is sex ration F/(M+F) to be included in the likelihood (assumed normal); 0 = no, 1 = use annual average across ages (uses 2nd age in propF data), 2 = age, and year specific (TBD)</t>
+  </si>
+  <si>
+    <t>Initial value or fixed value for sd of normal likelihood for sex ration. Not yet able to estimate.</t>
   </si>
 </sst>
 </file>
@@ -1336,25 +1333,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1365,16 +1362,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="G2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1385,16 +1382,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F3" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="G3" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1405,16 +1402,16 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F4" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G4" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1422,19 +1419,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G5" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1442,19 +1439,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F6" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G6" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1462,19 +1459,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C7" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G7" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1482,19 +1479,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F8" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1505,16 +1502,16 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F9" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="G9" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1522,19 +1519,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F10" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="G10" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1545,16 +1542,16 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" t="s">
         <v>135</v>
       </c>
-      <c r="F11" t="s">
-        <v>143</v>
-      </c>
       <c r="G11" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1565,16 +1562,16 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F12" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="G12" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1582,19 +1579,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C13" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F13" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="G13" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1605,16 +1602,16 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" t="s">
+        <v>127</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" t="s">
         <v>94</v>
-      </c>
-      <c r="D14" t="s">
-        <v>135</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="G14" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1622,19 +1619,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C15" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F15" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1645,16 +1642,16 @@
         <v>7</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D16" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F16" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1665,16 +1662,16 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F17" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G17" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1682,19 +1679,19 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>156</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>158</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F18" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G18" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1702,19 +1699,19 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>157</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>159</v>
       </c>
       <c r="D19" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="G19" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1722,19 +1719,19 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>153</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F20" t="s">
+        <v>103</v>
+      </c>
+      <c r="G20" t="s">
         <v>111</v>
-      </c>
-      <c r="G20" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1742,19 +1739,19 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F21" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G21" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1762,19 +1759,19 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G22" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1782,19 +1779,19 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>155</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="G23" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1802,19 +1799,19 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="G24" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1822,19 +1819,19 @@
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G25" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1842,19 +1839,19 @@
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G26" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1862,19 +1859,19 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1882,19 +1879,19 @@
         <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D28" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="G28" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1902,10 +1899,10 @@
         <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1913,16 +1910,16 @@
         <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="F30" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="G30" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1930,10 +1927,10 @@
         <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1941,10 +1938,10 @@
         <v>24</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C32" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1952,13 +1949,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F33" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1966,13 +1963,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C34" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F34" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1980,13 +1977,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F35" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1994,10 +1991,10 @@
         <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C36" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F36" s="4"/>
     </row>
@@ -2006,10 +2003,10 @@
         <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2017,10 +2014,10 @@
         <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2028,10 +2025,10 @@
         <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2039,10 +2036,10 @@
         <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C40" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2050,10 +2047,10 @@
         <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C41" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2061,10 +2058,10 @@
         <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C42" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2072,10 +2069,10 @@
         <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C43" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2083,10 +2080,10 @@
         <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C44" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2094,10 +2091,10 @@
         <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C45" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2105,10 +2102,10 @@
         <v>38</v>
       </c>
       <c r="B46" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C46" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2116,10 +2113,10 @@
         <v>39</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C47" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2127,10 +2124,10 @@
         <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C48" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -2138,10 +2135,10 @@
         <v>41</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2149,10 +2146,10 @@
         <v>42</v>
       </c>
       <c r="B50" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C50" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2160,10 +2157,10 @@
         <v>43</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C51" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="162">
   <si>
     <t>nspp</t>
   </si>
@@ -117,12 +117,6 @@
     <t>CK4</t>
   </si>
   <si>
-    <t>Tyrs</t>
-  </si>
-  <si>
-    <t>BTempC</t>
-  </si>
-  <si>
     <t>Pyrs</t>
   </si>
   <si>
@@ -210,12 +204,6 @@
     <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
   </si>
   <si>
-    <t xml:space="preserve">Years of bottom temperature data to incorporate into ft specificed by Ceq. </t>
-  </si>
-  <si>
-    <t>Bottom temperature data to incorporate into ft specificed by Ceq. Will use the mean for missing years.</t>
-  </si>
-  <si>
     <t>Which bioenergetics equation to use for each species for ft to scale max consumtion: 1 = Exponential (Stewart et al 1983), 2 = Temperature-dependendence for warm-water species (Kitchell et al 1977; sensu Holsman et al 2015), 3 = temperature dependence for cool and cold-water species (Thornton and Lessem 1979)</t>
   </si>
   <si>
@@ -306,9 +294,6 @@
     <t>Is the observation in weight (kg) set as 1, if the observation is in numbers caught, set as 2</t>
   </si>
   <si>
-    <t>Estimate catchability? (0 = no; 1 = yes, 2 = analytical from Ludwig and Walters 1994)</t>
-  </si>
-  <si>
     <t>Estimate survey variance (0 = use CV from srv_biom, 1 = yes, 2 = analytically estimate following (Ludwig and Walters 1994)</t>
   </si>
   <si>
@@ -354,9 +339,6 @@
     <t>NOTE: Columns for ages are index by 1 trhough nages, but are place holders.</t>
   </si>
   <si>
-    <t>Wether a time-varying q should be estimated. 0 = no, 1 = random walk from mean selectivity following Dorn 2018, 2 = random effect, 3 = time blocks with no penalty</t>
-  </si>
-  <si>
     <t>projyr</t>
   </si>
   <si>
@@ -444,9 +426,6 @@
     <t>Ages above this will be grouped to this age for composition data. For example, if set to 9 for a species with 10 ages, comp data for age 9 will include 9 and 10 year olds.</t>
   </si>
   <si>
-    <t>Log_q_prior</t>
-  </si>
-  <si>
     <t>Survey_sd_prior</t>
   </si>
   <si>
@@ -477,9 +456,6 @@
     <t>Selectivity to use for the species: 0 = empirical selectivity provided in srv_emp_sel; 1 = logistic selectivity; 2 = non-parametric selecitivty sensu Ianelli et al 2018; 3 = double logistic; 4 = descending logistic</t>
   </si>
   <si>
-    <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity, or descending logistic. 0 = no, 1 = penalized deviates given sel_sd_prior, 2 = random effect, 3 = time blocks with no penality, 4 = random walk following Dorn, 5 = random walk on ascending portion of double logistic. If selectivity is set to type = 2 (non-parametric) this value will be the 1st penalty on selectivity.</t>
-  </si>
-  <si>
     <t>Survey and fishery data specifications</t>
   </si>
   <si>
@@ -499,6 +475,36 @@
   </si>
   <si>
     <t>Initial value or fixed value for sd of normal likelihood for sex ration. Not yet able to estimate.</t>
+  </si>
+  <si>
+    <t>Q_prior</t>
+  </si>
+  <si>
+    <t>Time_varying_q_sd_prior</t>
+  </si>
+  <si>
+    <t>Variance of q prior: dnorm (log_q, log_q_prior, q_sd_prior)</t>
+  </si>
+  <si>
+    <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity, or descending logistic. 0 = no, 1 = penalized deviates given sel_sd_prior, 2 = random effect, 3 = time blocks with no penality, 4 = random walk following Dorn, 5 = random walk on ascending portion of double logistic only. If selectivity is set to type = 2 (non-parametric) this value will be the 1st penalty on selectivity.</t>
+  </si>
+  <si>
+    <t>Wether a time-varying q should be estimated. 0 = no, 1 = penalized deviate, 2 = random effect, 3 = time blocks with no penalty; 4 = random walk from mean following Dorn 2018 (dnorm(q_y - q_y-1, 0, sigma). If Estimate_q = 5, this determines the environmental index to be used in the equation log(q_y) = q_mu + beta * index_y</t>
+  </si>
+  <si>
+    <t>Estimate catchability? (0 = fixed at prior; - 1 = Estimate single parameter; - 2 = Estimate single parameter with prior; - 3 = Estimate analytical q  from Ludwig and Walters 1994;  - 4 = Estimate power equation; - 5 - Linear equation log(q_y) = q_mu + beta * index_y)</t>
+  </si>
+  <si>
+    <t>Cindex</t>
+  </si>
+  <si>
+    <t>Which environmental index in env_data to use to drive bioenergetics</t>
+  </si>
+  <si>
+    <t>env_data</t>
+  </si>
+  <si>
+    <t>Environmental indices such as bottom temperature data to incorporate into ration equation specificed by Ceq and Cindex. Also used to drive catchability if Estimate_q = 5. Will use the mean for missing years. Temperature should be in celcius.</t>
   </si>
 </sst>
 </file>
@@ -1333,25 +1339,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1362,16 +1368,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="G2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1382,16 +1388,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1402,16 +1408,16 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G4" t="s">
         <v>127</v>
-      </c>
-      <c r="F4" t="s">
-        <v>132</v>
-      </c>
-      <c r="G4" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1419,19 +1425,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1439,19 +1445,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F6" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1459,19 +1465,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1479,19 +1485,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1502,16 +1508,16 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F9" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G9" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1519,19 +1525,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F10" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G10" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1542,16 +1548,16 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F11" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="G11" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1562,16 +1568,16 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F12" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G12" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1579,19 +1585,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F13" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G13" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1602,16 +1608,16 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1619,19 +1625,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D15" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G15" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1642,16 +1648,16 @@
         <v>7</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F16" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1662,16 +1668,16 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F17" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G17" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1679,19 +1685,19 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C18" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D18" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F18" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s">
-        <v>95</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1699,19 +1705,19 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C19" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D19" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="G19" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1719,19 +1725,19 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C20" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D20" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F20" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G20" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1742,16 +1748,16 @@
         <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D21" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F21" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G21" t="s">
-        <v>105</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1762,16 +1768,16 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D22" t="s">
-        <v>127</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>143</v>
+        <v>121</v>
+      </c>
+      <c r="F22" t="s">
+        <v>153</v>
       </c>
       <c r="G22" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1779,19 +1785,19 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C23" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D23" t="s">
-        <v>127</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>142</v>
+        <v>121</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>136</v>
       </c>
       <c r="G23" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1802,16 +1808,16 @@
         <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>127</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>144</v>
+        <v>121</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="G24" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1822,16 +1828,16 @@
         <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>127</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>145</v>
+        <v>121</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="G25" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1842,16 +1848,16 @@
         <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="G26" t="s">
-        <v>147</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1862,16 +1868,16 @@
         <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D27" t="s">
-        <v>127</v>
-      </c>
-      <c r="F27" t="s">
-        <v>78</v>
+        <v>121</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="G27" t="s">
-        <v>84</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1882,16 +1888,16 @@
         <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>148</v>
+        <v>121</v>
+      </c>
+      <c r="F28" t="s">
+        <v>74</v>
       </c>
       <c r="G28" t="s">
-        <v>149</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1902,7 +1908,13 @@
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>51</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G29" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1913,13 +1925,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F30" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="G30" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1930,7 +1942,7 @@
         <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1941,7 +1953,7 @@
         <v>19</v>
       </c>
       <c r="C32" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1952,10 +1964,10 @@
         <v>20</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F33" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1966,10 +1978,10 @@
         <v>21</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F34" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1977,13 +1989,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>158</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>159</v>
       </c>
       <c r="F35" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1991,33 +2003,33 @@
         <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>89</v>
-      </c>
-      <c r="F36" s="4"/>
+        <v>57</v>
+      </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="F37" s="4"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2025,10 +2037,10 @@
         <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C39" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2036,10 +2048,10 @@
         <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2047,10 +2059,10 @@
         <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2058,10 +2070,10 @@
         <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2069,10 +2081,10 @@
         <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C43" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2080,10 +2092,10 @@
         <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C44" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2091,10 +2103,10 @@
         <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C45" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2102,10 +2114,10 @@
         <v>38</v>
       </c>
       <c r="B46" t="s">
-        <v>33</v>
+        <v>160</v>
       </c>
       <c r="C46" t="s">
-        <v>64</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2113,10 +2125,10 @@
         <v>39</v>
       </c>
       <c r="B47" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C47" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2124,10 +2136,10 @@
         <v>40</v>
       </c>
       <c r="B48" t="s">
+        <v>63</v>
+      </c>
+      <c r="C48" t="s">
         <v>67</v>
-      </c>
-      <c r="C48" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -2135,10 +2147,10 @@
         <v>41</v>
       </c>
       <c r="B49" t="s">
+        <v>64</v>
+      </c>
+      <c r="C49" t="s">
         <v>68</v>
-      </c>
-      <c r="C49" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2146,10 +2158,10 @@
         <v>42</v>
       </c>
       <c r="B50" t="s">
+        <v>65</v>
+      </c>
+      <c r="C50" t="s">
         <v>69</v>
-      </c>
-      <c r="C50" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2157,10 +2169,10 @@
         <v>43</v>
       </c>
       <c r="B51" t="s">
+        <v>66</v>
+      </c>
+      <c r="C51" t="s">
         <v>70</v>
-      </c>
-      <c r="C51" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="156">
   <si>
     <t>nspp</t>
   </si>
@@ -51,15 +51,9 @@
     <t>srv_biom</t>
   </si>
   <si>
-    <t>srv_emp_sel</t>
-  </si>
-  <si>
     <t>fsh_biom</t>
   </si>
   <si>
-    <t>fsh_emp_sel</t>
-  </si>
-  <si>
     <t>age_trans_matrix</t>
   </si>
   <si>
@@ -150,18 +144,12 @@
     <t>Sample size of diet data for each species (used when suitMode &gt; 0)</t>
   </si>
   <si>
-    <t>Empirical selectivity for surveys (leave empty if not used)</t>
-  </si>
-  <si>
     <t>Total catch in weight (kg) or numbers data</t>
   </si>
   <si>
     <t>Survey index in weight (kg) or numbers data</t>
   </si>
   <si>
-    <t>Empirical selectivity for fisheries (leave empty if not used)</t>
-  </si>
-  <si>
     <t>Age transition matrix (e.g. Age Length Key or ALK) used to convert age to length for length comp data. Can have multiple ALKs for a species specified by ALK_index.</t>
   </si>
   <si>
@@ -189,12 +177,6 @@
     <t>Parameters for weight-at-length power function for each species. . Used when estimating time-variant length-based gamma suitability (suitMode = 2) or time-variant length-based lognormal suitability (suitMode = 5)</t>
   </si>
   <si>
-    <t>data_list Object name</t>
-  </si>
-  <si>
-    <t>This scales the maximum consumption used for ration for each species; Pvalue is in Cmax*fT*Pvalue*Page</t>
-  </si>
-  <si>
     <t>Intercept of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
   </si>
   <si>
@@ -207,33 +189,18 @@
     <t>Which bioenergetics equation to use for each species for ft to scale max consumtion: 1 = Exponential (Stewart et al 1983), 2 = Temperature-dependendence for warm-water species (Kitchell et al 1977; sensu Holsman et al 2015), 3 = temperature dependence for cool and cold-water species (Thornton and Lessem 1979)</t>
   </si>
   <si>
-    <t>Annual relative foraging rate by age</t>
-  </si>
-  <si>
     <t>UobsAge</t>
   </si>
   <si>
     <t>UobsWtAge</t>
   </si>
   <si>
-    <t>Uobs</t>
-  </si>
-  <si>
-    <t>UobsWt</t>
-  </si>
-  <si>
     <t>Stomach proportion by numbers for each predator, prey, predator age, prey age combination. Can also be year specific by including the column, "Year"</t>
   </si>
   <si>
     <t>Stomach proportion by weight for each predator, prey, predator age, prey age combination. Can also be year specific by including the column, "Year"</t>
   </si>
   <si>
-    <t>Stomach proportion by numbers for each predator, prey, predator length, prey length combination. Can also be year specific by including the column, "Year"</t>
-  </si>
-  <si>
-    <t>Stomach proportion by weight for each predator, prey, predator length prey length combination. Can also be year specific by including the column, "Year"</t>
-  </si>
-  <si>
     <t>Species</t>
   </si>
   <si>
@@ -276,9 +243,6 @@
     <t>Starting value or fixed value for catchability</t>
   </si>
   <si>
-    <t>Percent of foraging days per year for each species</t>
-  </si>
-  <si>
     <t>Blank</t>
   </si>
   <si>
@@ -327,9 +291,6 @@
     <t>Selectivity_index</t>
   </si>
   <si>
-    <t>index to use if selectivitys of different surveys are to be the same</t>
-  </si>
-  <si>
     <t>Q_index</t>
   </si>
   <si>
@@ -459,12 +420,6 @@
     <t>Survey and fishery data specifications</t>
   </si>
   <si>
-    <t>comp</t>
-  </si>
-  <si>
-    <t>Survey/fishery age or length composition data</t>
-  </si>
-  <si>
     <t>est_propF</t>
   </si>
   <si>
@@ -505,6 +460,33 @@
   </si>
   <si>
     <t>Environmental indices such as bottom temperature data to incorporate into ration equation specificed by Ceq and Cindex. Also used to drive catchability if Estimate_q = 5. Will use the mean for missing years. Temperature should be in celcius.</t>
+  </si>
+  <si>
+    <t>emp_sel</t>
+  </si>
+  <si>
+    <t>Empirical/fixed selectivity for surveys and fisheries (leave empty if not used)</t>
+  </si>
+  <si>
+    <t>comp_data</t>
+  </si>
+  <si>
+    <t>Survey/fishery age or length composition data. Note if sex is 3, put female composition data then male composition data (similar to SS).</t>
+  </si>
+  <si>
+    <t>Object name</t>
+  </si>
+  <si>
+    <t>index to use if selectivities of different surveys are to be the same</t>
+  </si>
+  <si>
+    <t>Number of foraging days per year for each species</t>
+  </si>
+  <si>
+    <t>This scales the maximum consumption used for ration for each species; Pvalue is in Cmax*fT*Pvalue*Pyrs</t>
+  </si>
+  <si>
+    <t>Annual relative foraging rate by age. Multiplied by pvalue and fday to scale maximum consumption to the number of days in a year that foraging occurs.</t>
   </si>
 </sst>
 </file>
@@ -1328,7 +1310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
@@ -1339,25 +1321,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1368,16 +1350,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F2" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="G2" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1388,16 +1370,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F3" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="G3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1408,16 +1390,16 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F4" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="G4" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1425,19 +1407,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F5" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G5" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1445,19 +1427,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F6" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G6" t="s">
-        <v>102</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1465,19 +1447,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F7" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="G7" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1485,19 +1467,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="G8" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1508,16 +1490,16 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F9" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="G9" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1525,19 +1507,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="C10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" t="s">
         <v>115</v>
-      </c>
-      <c r="D10" t="s">
-        <v>121</v>
-      </c>
-      <c r="F10" t="s">
-        <v>97</v>
-      </c>
-      <c r="G10" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1548,16 +1530,16 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F11" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="G11" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1568,16 +1550,16 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F12" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="G12" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1585,19 +1567,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G13" t="s">
         <v>121</v>
-      </c>
-      <c r="F13" t="s">
-        <v>133</v>
-      </c>
-      <c r="G13" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1608,16 +1590,16 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1625,19 +1607,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="C15" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F15" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G15" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1648,16 +1630,16 @@
         <v>7</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="G16" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1668,16 +1650,16 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F17" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1685,19 +1667,19 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C18" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F18" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="G18" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1705,19 +1687,19 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C19" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="G19" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1725,19 +1707,19 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C20" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F20" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1748,16 +1730,16 @@
         <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F21" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="G21" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1768,16 +1750,16 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F22" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="G22" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1785,19 +1767,19 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C23" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="G23" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1805,19 +1787,19 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>148</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="G24" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1825,19 +1807,19 @@
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="G25" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1845,19 +1827,19 @@
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="G26" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1865,19 +1847,19 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="G27" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1885,19 +1867,19 @@
         <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D28" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F28" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G28" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1905,16 +1887,16 @@
         <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G29" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1922,16 +1904,16 @@
         <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F30" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="G30" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1939,10 +1921,10 @@
         <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1950,10 +1932,10 @@
         <v>24</v>
       </c>
       <c r="B32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1961,13 +1943,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C33" t="s">
         <v>55</v>
       </c>
       <c r="F33" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1975,13 +1957,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="C34" t="s">
-        <v>61</v>
+        <v>144</v>
       </c>
       <c r="F34" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1989,13 +1971,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="C35" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F35" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2003,10 +1985,10 @@
         <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>57</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2014,10 +1996,10 @@
         <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="F37" s="4"/>
     </row>
@@ -2026,10 +2008,10 @@
         <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C38" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2037,10 +2019,10 @@
         <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2048,10 +2030,10 @@
         <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C40" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2059,10 +2041,10 @@
         <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C41" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2070,10 +2052,10 @@
         <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2081,10 +2063,10 @@
         <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C43" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2092,10 +2074,10 @@
         <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C44" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2103,10 +2085,10 @@
         <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="C45" t="s">
-        <v>60</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2114,10 +2096,10 @@
         <v>38</v>
       </c>
       <c r="B46" t="s">
-        <v>160</v>
+        <v>30</v>
       </c>
       <c r="C46" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2125,10 +2107,10 @@
         <v>39</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C47" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2136,43 +2118,10 @@
         <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C48" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>41</v>
-      </c>
-      <c r="B49" t="s">
-        <v>64</v>
-      </c>
-      <c r="C49" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>42</v>
-      </c>
-      <c r="B50" t="s">
-        <v>65</v>
-      </c>
-      <c r="C50" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>43</v>
-      </c>
-      <c r="B51" t="s">
-        <v>66</v>
-      </c>
-      <c r="C51" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -39,9 +39,6 @@
     <t>pop_wt_index</t>
   </si>
   <si>
-    <t>pop_alk_index</t>
-  </si>
-  <si>
     <t>other_food</t>
   </si>
   <si>
@@ -150,9 +147,6 @@
     <t>Survey index in weight (kg) or numbers data</t>
   </si>
   <si>
-    <t>Age transition matrix (e.g. Age Length Key or ALK) used to convert age to length for length comp data. Can have multiple ALKs for a species specified by ALK_index.</t>
-  </si>
-  <si>
     <t>Aging error matrices. Can have only one per species.</t>
   </si>
   <si>
@@ -216,9 +210,6 @@
     <t>Weight_index</t>
   </si>
   <si>
-    <t>ALK_index</t>
-  </si>
-  <si>
     <t>Estimate_q</t>
   </si>
   <si>
@@ -234,12 +225,6 @@
     <t>Weight-at-age (wt) index to use for calculation of derived quantities</t>
   </si>
   <si>
-    <t>Age transition matrix (e.g. Age Length Key or ALK) index to use for derived quantities of the population (used in length-based predation estimation)</t>
-  </si>
-  <si>
-    <t>Age transition matrix (e.g. Age Length Key or ALK) index to use for derived quantitied</t>
-  </si>
-  <si>
     <t>Starting value or fixed value for catchability</t>
   </si>
   <si>
@@ -487,6 +472,21 @@
   </si>
   <si>
     <t>Annual relative foraging rate by age. Multiplied by pvalue and fday to scale maximum consumption to the number of days in a year that foraging occurs.</t>
+  </si>
+  <si>
+    <t>pop_age_transition_index</t>
+  </si>
+  <si>
+    <t>Age transition matrix (e.g. growth trajectory) index to use for derived quantities of the population to convert age to length (also used in length-based predation estimation)</t>
+  </si>
+  <si>
+    <t>Age_transition_index</t>
+  </si>
+  <si>
+    <t>Age transition matrix (e.g. growth trajectory) index to use for derived quantities to convert age to length</t>
+  </si>
+  <si>
+    <t>Age transition matrix (e.g. growth trajectory) used to convert age to length for length comp data. Can have multiple matrices for a species specified by Age_transition_index.</t>
   </si>
 </sst>
 </file>
@@ -1321,25 +1321,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1350,16 +1350,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1370,16 +1370,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1390,16 +1390,16 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F4" t="s">
         <v>108</v>
       </c>
-      <c r="F4" t="s">
-        <v>113</v>
-      </c>
       <c r="G4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1407,19 +1407,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1427,19 +1427,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" t="s">
         <v>95</v>
       </c>
-      <c r="C6" t="s">
-        <v>100</v>
-      </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G6" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1447,19 +1447,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G7" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1467,19 +1467,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1490,16 +1490,16 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F9" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G9" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1507,19 +1507,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F10" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G10" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1530,16 +1530,16 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F11" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G11" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1550,16 +1550,16 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F12" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G12" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1567,19 +1567,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F13" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G13" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1587,19 +1587,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>151</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G14" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1607,19 +1607,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1627,19 +1627,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>153</v>
       </c>
       <c r="G16" t="s">
-        <v>72</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1647,19 +1647,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F17" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G17" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1667,19 +1667,19 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C18" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G18" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1687,19 +1687,19 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C19" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G19" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1707,19 +1707,19 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F20" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G20" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1727,19 +1727,19 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F21" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1747,19 +1747,19 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F22" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G22" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1767,19 +1767,19 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C23" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D23" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G23" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1787,19 +1787,19 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C24" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D24" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G24" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1807,19 +1807,19 @@
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>155</v>
       </c>
       <c r="D25" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G25" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1827,19 +1827,19 @@
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G26" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1847,19 +1847,19 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G27" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1867,19 +1867,19 @@
         <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D28" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F28" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G28" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1887,16 +1887,16 @@
         <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G29" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1904,16 +1904,16 @@
         <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F30" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G30" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1921,10 +1921,10 @@
         <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1932,10 +1932,10 @@
         <v>24</v>
       </c>
       <c r="B32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1943,13 +1943,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F33" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1957,13 +1957,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C34" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F34" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1971,13 +1971,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C35" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F35" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1985,10 +1985,10 @@
         <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C36" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1996,10 +1996,10 @@
         <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F37" s="4"/>
     </row>
@@ -2008,10 +2008,10 @@
         <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2019,10 +2019,10 @@
         <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2030,10 +2030,10 @@
         <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2041,10 +2041,10 @@
         <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C41" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2052,10 +2052,10 @@
         <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2063,10 +2063,10 @@
         <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2074,10 +2074,10 @@
         <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2085,10 +2085,10 @@
         <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C45" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2096,10 +2096,10 @@
         <v>38</v>
       </c>
       <c r="B46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C46" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2107,10 +2107,10 @@
         <v>39</v>
       </c>
       <c r="B47" t="s">
+        <v>54</v>
+      </c>
+      <c r="C47" t="s">
         <v>56</v>
-      </c>
-      <c r="C47" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2118,10 +2118,10 @@
         <v>40</v>
       </c>
       <c r="B48" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" t="s">
         <v>57</v>
-      </c>
-      <c r="C48" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="meta_data_names" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="156">
   <si>
     <t>nspp</t>
   </si>
@@ -1892,6 +1892,9 @@
       <c r="C29" t="s">
         <v>46</v>
       </c>
+      <c r="D29" t="s">
+        <v>103</v>
+      </c>
       <c r="F29" s="2" t="s">
         <v>123</v>
       </c>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="161">
   <si>
     <t>nspp</t>
   </si>
@@ -42,9 +42,6 @@
     <t>other_food</t>
   </si>
   <si>
-    <t>stom_sample_size</t>
-  </si>
-  <si>
     <t>srv_biom</t>
   </si>
   <si>
@@ -138,9 +135,6 @@
     <t>Other food in the ecosystem for each species</t>
   </si>
   <si>
-    <t>Sample size of diet data for each species (used when suitMode &gt; 0)</t>
-  </si>
-  <si>
     <t>Total catch in weight (kg) or numbers data</t>
   </si>
   <si>
@@ -228,9 +222,6 @@
     <t>Starting value or fixed value for catchability</t>
   </si>
   <si>
-    <t>Blank</t>
-  </si>
-  <si>
     <t>Column names</t>
   </si>
   <si>
@@ -405,12 +396,6 @@
     <t>Survey and fishery data specifications</t>
   </si>
   <si>
-    <t>est_propF</t>
-  </si>
-  <si>
-    <t>propF_sigma</t>
-  </si>
-  <si>
     <t>Is sex ration F/(M+F) to be included in the likelihood (assumed normal); 0 = no, 1 = use annual average across ages (uses 2nd age in propF data), 2 = age, and year specific (TBD)</t>
   </si>
   <si>
@@ -487,6 +472,36 @@
   </si>
   <si>
     <t>Age transition matrix (e.g. growth trajectory) used to convert age to length for length comp data. Can have multiple matrices for a species specified by Age_transition_index.</t>
+  </si>
+  <si>
+    <t>est_M1</t>
+  </si>
+  <si>
+    <t>est_sex_ratio</t>
+  </si>
+  <si>
+    <t>sex_ratio_sigma</t>
+  </si>
+  <si>
+    <t>Estimate residual (multi-species mode) or total natural mortality (single-species mode). 0 = use fixed natural mortality from M1_base, 1 = estimate sex- and age-invariant M1, 2 = sex-specific (two-sex model), age-invariant M1, 3 =   estimate sex- and age-specific M1.</t>
+  </si>
+  <si>
+    <t>estDynamics</t>
+  </si>
+  <si>
+    <t>Estimate or fix numbers-at-age: 0 = estimate dynamics, 1 = use input numbers-at-age in NbyageFixed, 2 = multiply input numbers-at-age (NbyageFixed) by a single scaling coefficient, 3 = multiply input numbers-at-age (NbyageFixed) by age specific scaling coefficient.</t>
+  </si>
+  <si>
+    <t>proj_F</t>
+  </si>
+  <si>
+    <t>Unused</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>bioenergetics_control</t>
   </si>
 </sst>
 </file>
@@ -1310,36 +1325,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="119.42578125" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="119.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1347,19 +1363,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
-        <v>32</v>
-      </c>
       <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G2" t="s">
         <v>103</v>
-      </c>
-      <c r="F2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G2" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1367,19 +1386,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
-        <v>33</v>
-      </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>100</v>
       </c>
       <c r="F3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1387,19 +1409,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" t="s">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>100</v>
       </c>
       <c r="F4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1407,19 +1432,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>86</v>
+      </c>
+      <c r="E5" t="s">
+        <v>100</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1427,19 +1455,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>92</v>
+      </c>
+      <c r="E6" t="s">
+        <v>100</v>
       </c>
       <c r="F6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1447,19 +1478,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>89</v>
+      </c>
+      <c r="E7" t="s">
+        <v>100</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1467,19 +1501,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>159</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>91</v>
+      </c>
+      <c r="E8" t="s">
+        <v>100</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1487,19 +1524,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" t="s">
         <v>3</v>
       </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>33</v>
+      </c>
+      <c r="E9" t="s">
+        <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1507,19 +1547,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>94</v>
+      </c>
+      <c r="E10" t="s">
+        <v>100</v>
       </c>
       <c r="F10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1527,19 +1570,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" t="s">
         <v>4</v>
       </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>100</v>
       </c>
       <c r="F11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G11" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1547,19 +1593,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12" t="s">
         <v>5</v>
       </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>100</v>
       </c>
       <c r="F12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1567,19 +1616,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>96</v>
+      </c>
+      <c r="E13" t="s">
+        <v>100</v>
       </c>
       <c r="F13" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G13" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1587,19 +1639,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C14" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>147</v>
+      </c>
+      <c r="E14" t="s">
+        <v>100</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1607,19 +1662,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>103</v>
+        <v>98</v>
+      </c>
+      <c r="E15" t="s">
+        <v>100</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1627,19 +1685,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16" t="s">
         <v>6</v>
       </c>
-      <c r="C16" t="s">
-        <v>38</v>
-      </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>100</v>
       </c>
       <c r="F16" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G16" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1647,19 +1708,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>159</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>155</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>156</v>
+      </c>
+      <c r="E17" t="s">
+        <v>100</v>
       </c>
       <c r="F17" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G17" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1667,19 +1731,22 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="C18" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="D18" t="s">
-        <v>103</v>
+        <v>158</v>
+      </c>
+      <c r="E18" t="s">
+        <v>100</v>
       </c>
       <c r="F18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G18" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1687,19 +1754,22 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="C19" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="D19" t="s">
-        <v>103</v>
+        <v>125</v>
+      </c>
+      <c r="E19" t="s">
+        <v>100</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1707,19 +1777,22 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>159</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>126</v>
+      </c>
+      <c r="E20" t="s">
+        <v>100</v>
       </c>
       <c r="F20" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1727,246 +1800,249 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>159</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>151</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>154</v>
+      </c>
+      <c r="E21" t="s">
+        <v>100</v>
       </c>
       <c r="F21" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>14</v>
       </c>
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>124</v>
+      </c>
+      <c r="E22" t="s">
+        <v>100</v>
       </c>
       <c r="F22" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G22" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>15</v>
       </c>
-      <c r="B23" t="s">
-        <v>144</v>
-      </c>
       <c r="C23" t="s">
-        <v>145</v>
+        <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>103</v>
+        <v>39</v>
+      </c>
+      <c r="E23" t="s">
+        <v>100</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G23" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>16</v>
       </c>
-      <c r="B24" t="s">
-        <v>142</v>
-      </c>
       <c r="C24" t="s">
-        <v>143</v>
+        <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>103</v>
+        <v>38</v>
+      </c>
+      <c r="E24" t="s">
+        <v>100</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>17</v>
       </c>
-      <c r="B25" t="s">
-        <v>10</v>
-      </c>
       <c r="C25" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="D25" t="s">
-        <v>103</v>
+        <v>140</v>
+      </c>
+      <c r="E25" t="s">
+        <v>100</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G25" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>18</v>
       </c>
-      <c r="B26" t="s">
-        <v>11</v>
-      </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="D26" t="s">
-        <v>103</v>
+        <v>138</v>
+      </c>
+      <c r="E26" t="s">
+        <v>100</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G26" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>19</v>
       </c>
-      <c r="B27" t="s">
-        <v>12</v>
-      </c>
       <c r="C27" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>103</v>
+        <v>150</v>
+      </c>
+      <c r="E27" t="s">
+        <v>100</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G27" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>20</v>
       </c>
-      <c r="B28" t="s">
-        <v>13</v>
-      </c>
       <c r="C28" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="D28" t="s">
-        <v>103</v>
+        <v>40</v>
+      </c>
+      <c r="E28" t="s">
+        <v>100</v>
       </c>
       <c r="F28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G28" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>21</v>
       </c>
-      <c r="B29" t="s">
-        <v>14</v>
-      </c>
       <c r="C29" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>103</v>
+        <v>41</v>
+      </c>
+      <c r="E29" t="s">
+        <v>100</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G29" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>22</v>
       </c>
-      <c r="B30" t="s">
-        <v>15</v>
-      </c>
       <c r="C30" t="s">
-        <v>47</v>
+        <v>12</v>
+      </c>
+      <c r="D30" t="s">
+        <v>43</v>
       </c>
       <c r="F30" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G30" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>23</v>
       </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
       <c r="C31" t="s">
-        <v>48</v>
+        <v>13</v>
+      </c>
+      <c r="D31" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>24</v>
       </c>
-      <c r="B32" t="s">
-        <v>17</v>
-      </c>
       <c r="C32" t="s">
-        <v>49</v>
+        <v>14</v>
+      </c>
+      <c r="D32" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>25</v>
       </c>
-      <c r="B33" t="s">
-        <v>18</v>
-      </c>
       <c r="C33" t="s">
-        <v>53</v>
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>46</v>
       </c>
       <c r="F33" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26</v>
       </c>
-      <c r="B34" t="s">
-        <v>138</v>
-      </c>
       <c r="C34" t="s">
-        <v>139</v>
+        <v>16</v>
+      </c>
+      <c r="D34" t="s">
+        <v>47</v>
       </c>
       <c r="F34" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1974,13 +2050,16 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>19</v>
+        <v>160</v>
       </c>
       <c r="C35" t="s">
-        <v>149</v>
+        <v>17</v>
+      </c>
+      <c r="D35" t="s">
+        <v>51</v>
       </c>
       <c r="F35" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1988,10 +2067,13 @@
         <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="C36" t="s">
-        <v>148</v>
+        <v>133</v>
+      </c>
+      <c r="D36" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1999,10 +2081,13 @@
         <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="C37" t="s">
-        <v>50</v>
+        <v>18</v>
+      </c>
+      <c r="D37" t="s">
+        <v>144</v>
       </c>
       <c r="F37" s="4"/>
     </row>
@@ -2011,10 +2096,13 @@
         <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="C38" t="s">
-        <v>51</v>
+        <v>19</v>
+      </c>
+      <c r="D38" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2022,10 +2110,13 @@
         <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="C39" t="s">
-        <v>52</v>
+        <v>20</v>
+      </c>
+      <c r="D39" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2033,10 +2124,13 @@
         <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="C40" t="s">
-        <v>52</v>
+        <v>21</v>
+      </c>
+      <c r="D40" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2044,10 +2138,13 @@
         <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>160</v>
       </c>
       <c r="C41" t="s">
-        <v>52</v>
+        <v>22</v>
+      </c>
+      <c r="D41" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2055,10 +2152,13 @@
         <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>160</v>
       </c>
       <c r="C42" t="s">
-        <v>52</v>
+        <v>23</v>
+      </c>
+      <c r="D42" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2066,10 +2166,13 @@
         <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>160</v>
       </c>
       <c r="C43" t="s">
-        <v>52</v>
+        <v>24</v>
+      </c>
+      <c r="D43" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2077,10 +2180,13 @@
         <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>28</v>
+        <v>160</v>
       </c>
       <c r="C44" t="s">
-        <v>52</v>
+        <v>25</v>
+      </c>
+      <c r="D44" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2088,10 +2194,13 @@
         <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C45" t="s">
-        <v>141</v>
+        <v>26</v>
+      </c>
+      <c r="D45" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2099,32 +2208,57 @@
         <v>38</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>160</v>
       </c>
       <c r="C46" t="s">
-        <v>150</v>
+        <v>27</v>
+      </c>
+      <c r="D46" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>39</v>
       </c>
-      <c r="B47" t="s">
-        <v>54</v>
-      </c>
       <c r="C47" t="s">
-        <v>56</v>
+        <v>135</v>
+      </c>
+      <c r="D47" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>40</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>41</v>
+      </c>
+      <c r="C49" t="s">
+        <v>52</v>
+      </c>
+      <c r="D49" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>42</v>
+      </c>
+      <c r="C50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D50" t="s">
         <v>55</v>
-      </c>
-      <c r="C48" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -114,27 +114,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Number of species included in CEATTLE</t>
-  </si>
-  <si>
-    <t>Start year of the hindcast</t>
-  </si>
-  <si>
-    <t>Number of ages of each species included in the hindcast</t>
-  </si>
-  <si>
-    <t>Number of lengths of each species included in the hindcast</t>
-  </si>
-  <si>
-    <t>End year of the hindcast</t>
-  </si>
-  <si>
-    <t>Weight-at-age (wt) index to use for calculation of each species population derived quantities (SSB, Consumption/Ration, Suitability, etc)</t>
-  </si>
-  <si>
-    <t>Other food in the ecosystem for each species</t>
-  </si>
-  <si>
     <t>Total catch in weight (kg) or numbers data</t>
   </si>
   <si>
@@ -174,9 +153,6 @@
     <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
   </si>
   <si>
-    <t>Which bioenergetics equation to use for each species for ft to scale max consumtion: 1 = Exponential (Stewart et al 1983), 2 = Temperature-dependendence for warm-water species (Kitchell et al 1977; sensu Holsman et al 2015), 3 = temperature dependence for cool and cold-water species (Thornton and Lessem 1979)</t>
-  </si>
-  <si>
     <t>UobsAge</t>
   </si>
   <si>
@@ -279,45 +255,24 @@
     <t>projyr</t>
   </si>
   <si>
-    <t>End year of the forecast</t>
-  </si>
-  <si>
     <t>nsex</t>
   </si>
   <si>
     <t>spawn_month</t>
   </si>
   <si>
-    <t>Spawning month of the population to adjust the numbers spawning</t>
-  </si>
-  <si>
     <t>R_sexr</t>
   </si>
   <si>
-    <t>Percent of recruitment that is female (ignored if nsex = 1)</t>
-  </si>
-  <si>
-    <t>Number of sexes to model in the population (1 = combined/1sex, 2 = models both female/male)</t>
-  </si>
-  <si>
     <t>minage</t>
   </si>
   <si>
-    <t>Minimum age for each population (i.e.does recruitment correspond to age 0, 1, 2?)</t>
-  </si>
-  <si>
     <t>ssb_wt_index</t>
   </si>
   <si>
-    <t>Weight-at-age (wt) index to use for calculation of each species spawning biomass</t>
-  </si>
-  <si>
     <t>sigma_rec_prior</t>
   </si>
   <si>
-    <t>Standard deviation to use for recruitment</t>
-  </si>
-  <si>
     <t>Sex</t>
   </si>
   <si>
@@ -396,12 +351,6 @@
     <t>Survey and fishery data specifications</t>
   </si>
   <si>
-    <t>Is sex ration F/(M+F) to be included in the likelihood (assumed normal); 0 = no, 1 = use annual average across ages (uses 2nd age in propF data), 2 = age, and year specific (TBD)</t>
-  </si>
-  <si>
-    <t>Initial value or fixed value for sd of normal likelihood for sex ration. Not yet able to estimate.</t>
-  </si>
-  <si>
     <t>Q_prior</t>
   </si>
   <si>
@@ -423,9 +372,6 @@
     <t>Cindex</t>
   </si>
   <si>
-    <t>Which environmental index in env_data to use to drive bioenergetics</t>
-  </si>
-  <si>
     <t>env_data</t>
   </si>
   <si>
@@ -450,21 +396,12 @@
     <t>index to use if selectivities of different surveys are to be the same</t>
   </si>
   <si>
-    <t>Number of foraging days per year for each species</t>
-  </si>
-  <si>
-    <t>This scales the maximum consumption used for ration for each species; Pvalue is in Cmax*fT*Pvalue*Pyrs</t>
-  </si>
-  <si>
     <t>Annual relative foraging rate by age. Multiplied by pvalue and fday to scale maximum consumption to the number of days in a year that foraging occurs.</t>
   </si>
   <si>
     <t>pop_age_transition_index</t>
   </si>
   <si>
-    <t>Age transition matrix (e.g. growth trajectory) index to use for derived quantities of the population to convert age to length (also used in length-based predation estimation)</t>
-  </si>
-  <si>
     <t>Age_transition_index</t>
   </si>
   <si>
@@ -483,15 +420,9 @@
     <t>sex_ratio_sigma</t>
   </si>
   <si>
-    <t>Estimate residual (multi-species mode) or total natural mortality (single-species mode). 0 = use fixed natural mortality from M1_base, 1 = estimate sex- and age-invariant M1, 2 = sex-specific (two-sex model), age-invariant M1, 3 =   estimate sex- and age-specific M1.</t>
-  </si>
-  <si>
     <t>estDynamics</t>
   </si>
   <si>
-    <t>Estimate or fix numbers-at-age: 0 = estimate dynamics, 1 = use input numbers-at-age in NbyageFixed, 2 = multiply input numbers-at-age (NbyageFixed) by a single scaling coefficient, 3 = multiply input numbers-at-age (NbyageFixed) by age specific scaling coefficient.</t>
-  </si>
-  <si>
     <t>proj_F</t>
   </si>
   <si>
@@ -502,6 +433,75 @@
   </si>
   <si>
     <t>bioenergetics_control</t>
+  </si>
+  <si>
+    <t>Integer: end year of the forecast</t>
+  </si>
+  <si>
+    <t>Integer: number of sexes to model in the population (1 = combined/1sex, 2 = models both female/male)</t>
+  </si>
+  <si>
+    <t>Numeric: spawning month of the population to adjust the numbers at spawning</t>
+  </si>
+  <si>
+    <t>Numeric: percent of recruitment that is female (ignored if nsex = 1)</t>
+  </si>
+  <si>
+    <t>Integer: end year of the hindcast</t>
+  </si>
+  <si>
+    <t>Integer: start year of the hindcast</t>
+  </si>
+  <si>
+    <t>Integer: number of species included in CEATTLE</t>
+  </si>
+  <si>
+    <t>Integer: number of ages of each species included in the hindcast</t>
+  </si>
+  <si>
+    <t>Numeric: minimum age for each population (i.e.does recruitment correspond to age 0, 1, 2?)</t>
+  </si>
+  <si>
+    <t>Integer: number of lengths of each species included in the hindcast</t>
+  </si>
+  <si>
+    <t>Integer: weight-at-age (wt) index to use for calculation of each species population derived quantities (SSB, Consumption/Ration, Suitability, etc)</t>
+  </si>
+  <si>
+    <t>Integer: weight-at-age (wt) index to use for calculation of each species spawning biomass</t>
+  </si>
+  <si>
+    <t>Integer: age transition matrix (e.g. growth trajectory) index to use for derived quantities of the population to convert age to length (also used in length-based predation estimation)</t>
+  </si>
+  <si>
+    <t>Numeric: fixed or initial value of standard deviation for recruitment deviates</t>
+  </si>
+  <si>
+    <t>Numeric: other food in the ecosystem for each species (kg)</t>
+  </si>
+  <si>
+    <t>Integer: is sex ration F/(M+F) to be included in the likelihood (assumed normal); 0 = no, 1 = use annual average across ages (uses 2nd age in propF data), 2 = age, and year specific (TBD)</t>
+  </si>
+  <si>
+    <t>Numeric: initial value or fixed value for sd of normal likelihood for sex ration. Not yet able to estimate.</t>
+  </si>
+  <si>
+    <t>Integer: switch to estimate residual (multi-species mode) or total natural mortality (single-species mode). 0 = use fixed natural mortality from M1_base, 1 = estimate sex- and age-invariant M1, 2 = sex-specific (two-sex model), age-invariant M1, 3 =   estimate sex- and age-specific M1.</t>
+  </si>
+  <si>
+    <t>Integer: switch to estimate or fix numbers-at-age: 0 = estimate dynamics, 1 = use input numbers-at-age in NbyageFixed, 2 = multiply input numbers-at-age (NbyageFixed) by a single scaling coefficient, 3 = multiply input numbers-at-age (NbyageFixed) by age specific scaling coefficient.</t>
+  </si>
+  <si>
+    <t>Integer: switch for which bioenergetics equation to use for each species for ft to scale max consumtion: 1 = Exponential (Stewart et al 1983), 2 = Temperature-dependendence for warm-water species (Kitchell et al 1977; sensu Holsman et al 2015), 3 = temperature dependence for cool and cold-water species (Thornton and Lessem 1979)</t>
+  </si>
+  <si>
+    <t>Integer: which environmental index in env_data to use to drive bioenergetics</t>
+  </si>
+  <si>
+    <t>Numeric: this scales the maximum consumption used for ration for each species; Pvalue is in Cmax*fT*Pvalue*Pyrs</t>
+  </si>
+  <si>
+    <t>Numeric: number of foraging days per year for each species</t>
   </si>
 </sst>
 </file>
@@ -1340,19 +1340,19 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>30</v>
@@ -1363,22 +1363,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>144</v>
       </c>
       <c r="E2" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F2" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="G2" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1386,22 +1386,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>143</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="G3" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1409,22 +1409,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>142</v>
       </c>
       <c r="E4" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F4" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="G4" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1432,22 +1432,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="E5" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G5" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1455,22 +1455,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>139</v>
       </c>
       <c r="E6" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="G6" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1478,22 +1478,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="E7" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G7" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1501,22 +1501,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>141</v>
       </c>
       <c r="E8" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1524,22 +1524,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>145</v>
       </c>
       <c r="E9" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F9" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G9" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1547,22 +1547,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="E10" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F10" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="G10" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1570,22 +1570,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>147</v>
       </c>
       <c r="E11" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F11" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="G11" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1593,22 +1593,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
       <c r="E12" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F12" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="G12" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1616,22 +1616,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>149</v>
       </c>
       <c r="E13" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F13" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="G13" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1639,22 +1639,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C14" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="D14" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E14" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="G14" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1662,22 +1662,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c r="E15" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G15" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1685,22 +1685,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C16" t="s">
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>152</v>
       </c>
       <c r="E16" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F16" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="G16" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1708,22 +1708,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C17" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="D17" t="s">
         <v>156</v>
       </c>
       <c r="E17" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1731,22 +1731,22 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C18" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="D18" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="E18" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F18" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G18" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1754,22 +1754,22 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C19" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="D19" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="E19" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="G19" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1777,22 +1777,22 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C20" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="E20" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F20" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G20" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1800,22 +1800,22 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C21" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="D21" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E21" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F21" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G21" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1823,19 +1823,19 @@
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D22" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="E22" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F22" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="G22" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1846,16 +1846,16 @@
         <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E23" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="G23" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1866,16 +1866,16 @@
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E24" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="G24" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1883,19 +1883,19 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="D25" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E25" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="G25" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1903,19 +1903,19 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="E26" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="G26" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1926,16 +1926,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="E27" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G27" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1946,16 +1946,16 @@
         <v>10</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E28" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F28" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="G28" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1966,16 +1966,16 @@
         <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E29" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="G29" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1986,13 +1986,13 @@
         <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F30" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="G30" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2003,7 +2003,7 @@
         <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2014,7 +2014,7 @@
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2025,10 +2025,10 @@
         <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F33" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2039,10 +2039,10 @@
         <v>16</v>
       </c>
       <c r="D34" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F34" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2050,16 +2050,16 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="C35" t="s">
         <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>51</v>
+        <v>157</v>
       </c>
       <c r="F35" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2067,13 +2067,13 @@
         <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="D36" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2081,13 +2081,13 @@
         <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="C37" t="s">
         <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="F37" s="4"/>
     </row>
@@ -2096,13 +2096,13 @@
         <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="C38" t="s">
         <v>19</v>
       </c>
       <c r="D38" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2110,13 +2110,13 @@
         <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="C39" t="s">
         <v>20</v>
       </c>
       <c r="D39" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2124,13 +2124,13 @@
         <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="C40" t="s">
         <v>21</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2138,13 +2138,13 @@
         <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="C41" t="s">
         <v>22</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2152,13 +2152,13 @@
         <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="C42" t="s">
         <v>23</v>
       </c>
       <c r="D42" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2166,13 +2166,13 @@
         <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="C43" t="s">
         <v>24</v>
       </c>
       <c r="D43" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2180,13 +2180,13 @@
         <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="C44" t="s">
         <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2194,13 +2194,13 @@
         <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="C45" t="s">
         <v>26</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2208,13 +2208,13 @@
         <v>38</v>
       </c>
       <c r="B46" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="C46" t="s">
         <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2222,10 +2222,10 @@
         <v>39</v>
       </c>
       <c r="C47" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="D47" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2236,7 +2236,7 @@
         <v>28</v>
       </c>
       <c r="D48" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2244,10 +2244,10 @@
         <v>41</v>
       </c>
       <c r="C49" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2255,10 +2255,10 @@
         <v>42</v>
       </c>
       <c r="C50" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D50" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -345,9 +345,6 @@
     <t>sex codes: 0=combined; 1=use female only; 2=use male only; 3 = joint female and male</t>
   </si>
   <si>
-    <t>Selectivity to use for the species: 0 = empirical selectivity provided in srv_emp_sel; 1 = logistic selectivity; 2 = non-parametric selecitivty sensu Ianelli et al 2018; 3 = double logistic; 4 = descending logistic</t>
-  </si>
-  <si>
     <t>Survey and fishery data specifications</t>
   </si>
   <si>
@@ -502,6 +499,9 @@
   </si>
   <si>
     <t>Numeric: number of foraging days per year for each species</t>
+  </si>
+  <si>
+    <t>Selectivity to use for the species: 0 = empirical selectivity provided in srv_emp_sel; 1 = logistic selectivity; 2 = non-parametric selecitivty sensu Ianelli et al 2018; 3 = double logistic; 4 = descending logistic; 5 = non-parametric selectivity sensu Taylor et al 2014 (Hake)</t>
   </si>
 </sst>
 </file>
@@ -1343,7 +1343,7 @@
         <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>30</v>
@@ -1363,13 +1363,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
         <v>85</v>
@@ -1386,13 +1386,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E3" t="s">
         <v>85</v>
@@ -1409,13 +1409,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E4" t="s">
         <v>85</v>
@@ -1432,13 +1432,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C5" t="s">
         <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
         <v>85</v>
@@ -1455,13 +1455,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C6" t="s">
         <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E6" t="s">
         <v>85</v>
@@ -1470,7 +1470,7 @@
         <v>73</v>
       </c>
       <c r="G6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1478,13 +1478,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C7" t="s">
         <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E7" t="s">
         <v>85</v>
@@ -1493,7 +1493,7 @@
         <v>49</v>
       </c>
       <c r="G7" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1501,13 +1501,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C8" t="s">
         <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E8" t="s">
         <v>85</v>
@@ -1524,13 +1524,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E9" t="s">
         <v>85</v>
@@ -1539,7 +1539,7 @@
         <v>68</v>
       </c>
       <c r="G9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1547,13 +1547,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C10" t="s">
         <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E10" t="s">
         <v>85</v>
@@ -1570,13 +1570,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E11" t="s">
         <v>85</v>
@@ -1593,13 +1593,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E12" t="s">
         <v>85</v>
@@ -1616,13 +1616,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C13" t="s">
         <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E13" t="s">
         <v>85</v>
@@ -1639,13 +1639,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E14" t="s">
         <v>85</v>
@@ -1662,13 +1662,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C15" t="s">
         <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E15" t="s">
         <v>85</v>
@@ -1685,22 +1685,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C16" t="s">
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E16" t="s">
         <v>85</v>
       </c>
       <c r="F16" t="s">
+        <v>126</v>
+      </c>
+      <c r="G16" t="s">
         <v>127</v>
-      </c>
-      <c r="G16" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1708,13 +1708,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E17" t="s">
         <v>85</v>
@@ -1731,13 +1731,13 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C18" t="s">
+        <v>133</v>
+      </c>
+      <c r="D18" t="s">
         <v>134</v>
-      </c>
-      <c r="D18" t="s">
-        <v>135</v>
       </c>
       <c r="E18" t="s">
         <v>85</v>
@@ -1746,7 +1746,7 @@
         <v>53</v>
       </c>
       <c r="G18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1754,19 +1754,19 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E19" t="s">
         <v>85</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G19" t="s">
         <v>58</v>
@@ -1777,13 +1777,13 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E20" t="s">
         <v>85</v>
@@ -1792,7 +1792,7 @@
         <v>71</v>
       </c>
       <c r="G20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1800,13 +1800,13 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D21" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E21" t="s">
         <v>85</v>
@@ -1815,7 +1815,7 @@
         <v>70</v>
       </c>
       <c r="G21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1826,13 +1826,13 @@
         <v>85</v>
       </c>
       <c r="D22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E22" t="s">
         <v>85</v>
       </c>
       <c r="F22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G22" t="s">
         <v>72</v>
@@ -1883,10 +1883,10 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" t="s">
         <v>121</v>
-      </c>
-      <c r="D25" t="s">
-        <v>122</v>
       </c>
       <c r="E25" t="s">
         <v>85</v>
@@ -1903,10 +1903,10 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" t="s">
         <v>119</v>
-      </c>
-      <c r="D26" t="s">
-        <v>120</v>
       </c>
       <c r="E26" t="s">
         <v>85</v>
@@ -1926,7 +1926,7 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E27" t="s">
         <v>85</v>
@@ -2050,13 +2050,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C35" t="s">
         <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F35" t="s">
         <v>76</v>
@@ -2067,13 +2067,13 @@
         <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2081,13 +2081,13 @@
         <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C37" t="s">
         <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F37" s="4"/>
     </row>
@@ -2096,13 +2096,13 @@
         <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C38" t="s">
         <v>19</v>
       </c>
       <c r="D38" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2110,7 +2110,7 @@
         <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C39" t="s">
         <v>20</v>
@@ -2124,7 +2124,7 @@
         <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C40" t="s">
         <v>21</v>
@@ -2138,7 +2138,7 @@
         <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C41" t="s">
         <v>22</v>
@@ -2152,7 +2152,7 @@
         <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C42" t="s">
         <v>23</v>
@@ -2166,7 +2166,7 @@
         <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C43" t="s">
         <v>24</v>
@@ -2180,7 +2180,7 @@
         <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C44" t="s">
         <v>25</v>
@@ -2194,7 +2194,7 @@
         <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C45" t="s">
         <v>26</v>
@@ -2208,7 +2208,7 @@
         <v>38</v>
       </c>
       <c r="B46" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C46" t="s">
         <v>27</v>
@@ -2222,10 +2222,10 @@
         <v>39</v>
       </c>
       <c r="C47" t="s">
+        <v>116</v>
+      </c>
+      <c r="D47" t="s">
         <v>117</v>
-      </c>
-      <c r="D47" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2236,7 +2236,7 @@
         <v>28</v>
       </c>
       <c r="D48" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -186,9 +186,6 @@
     <t>Species number</t>
   </si>
   <si>
-    <t>Number of ages to estimate non-parametric selectivity for Selectivity = 2. Not used otherwise</t>
-  </si>
-  <si>
     <t>Units used for survey: 1 = kg; 2 = numbers</t>
   </si>
   <si>
@@ -357,9 +354,6 @@
     <t>Variance of q prior: dnorm (log_q, log_q_prior, q_sd_prior)</t>
   </si>
   <si>
-    <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity, or descending logistic. 0 = no, 1 = penalized deviates given sel_sd_prior, 2 = random effect, 3 = time blocks with no penality, 4 = random walk following Dorn, 5 = random walk on ascending portion of double logistic only. If selectivity is set to type = 2 (non-parametric) this value will be the 1st penalty on selectivity.</t>
-  </si>
-  <si>
     <t>Wether a time-varying q should be estimated. 0 = no, 1 = penalized deviate, 2 = random effect, 3 = time blocks with no penalty; 4 = random walk from mean following Dorn 2018 (dnorm(q_y - q_y-1, 0, sigma). If Estimate_q = 5, this determines the environmental index to be used in the equation log(q_y) = q_mu + beta * index_y</t>
   </si>
   <si>
@@ -502,6 +496,12 @@
   </si>
   <si>
     <t>Selectivity to use for the species: 0 = empirical selectivity provided in srv_emp_sel; 1 = logistic selectivity; 2 = non-parametric selecitivty sensu Ianelli et al 2018; 3 = double logistic; 4 = descending logistic; 5 = non-parametric selectivity sensu Taylor et al 2014 (Hake)</t>
+  </si>
+  <si>
+    <t>Number of ages to estimate non-parametric selectivity for Selectivity = 2 &amp; 5. Not used otherwise</t>
+  </si>
+  <si>
+    <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity,  descending logistic , or non-parametric (Selectivity = 5). 0 = no, 1 = penalized deviates given sel_sd_prior, 2 = random effect, 3 = time blocks with no penality, 4 = random walk following Dorn, 5 = random walk on ascending portion of double logistic only. If selectivity is set to type = 2 (non-parametric) this value will be the 1st penalty on selectivity.</t>
   </si>
 </sst>
 </file>
@@ -1343,7 +1343,7 @@
         <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>30</v>
@@ -1352,7 +1352,7 @@
         <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>30</v>
@@ -1363,22 +1363,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" t="s">
         <v>85</v>
       </c>
-      <c r="F2" t="s">
-        <v>86</v>
-      </c>
       <c r="G2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1386,22 +1386,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1409,22 +1409,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G4" t="s">
         <v>90</v>
-      </c>
-      <c r="G4" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1432,16 +1432,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" t="s">
         <v>135</v>
       </c>
-      <c r="C5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" t="s">
-        <v>137</v>
-      </c>
       <c r="E5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F5" t="s">
         <v>48</v>
@@ -1455,22 +1455,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1478,22 +1478,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F7" t="s">
         <v>49</v>
       </c>
       <c r="G7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1501,22 +1501,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F8" t="s">
         <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>55</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1524,22 +1524,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G9" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1547,22 +1547,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1570,22 +1570,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F11" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" t="s">
         <v>93</v>
-      </c>
-      <c r="G11" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1593,22 +1593,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F12" t="s">
+        <v>94</v>
+      </c>
+      <c r="G12" t="s">
         <v>95</v>
-      </c>
-      <c r="G12" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1616,22 +1616,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F13" t="s">
+        <v>96</v>
+      </c>
+      <c r="G13" t="s">
         <v>97</v>
-      </c>
-      <c r="G13" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1639,22 +1639,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C14" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" t="s">
         <v>61</v>
-      </c>
-      <c r="G14" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1662,22 +1662,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F15" t="s">
         <v>52</v>
       </c>
       <c r="G15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1685,22 +1685,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C16" t="s">
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G16" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1708,22 +1708,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D17" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" t="s">
         <v>74</v>
-      </c>
-      <c r="G17" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1731,22 +1731,22 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C18" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F18" t="s">
         <v>53</v>
       </c>
       <c r="G18" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1754,22 +1754,22 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C19" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1777,22 +1777,22 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D20" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1800,22 +1800,22 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1823,19 +1823,19 @@
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1849,13 +1849,13 @@
         <v>32</v>
       </c>
       <c r="E23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1869,13 +1869,13 @@
         <v>31</v>
       </c>
       <c r="E24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1883,19 +1883,19 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1903,19 +1903,19 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1926,16 +1926,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F27" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G27" t="s">
         <v>103</v>
-      </c>
-      <c r="G27" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1949,13 +1949,13 @@
         <v>33</v>
       </c>
       <c r="E28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F28" t="s">
         <v>51</v>
       </c>
       <c r="G28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1969,13 +1969,13 @@
         <v>34</v>
       </c>
       <c r="E29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F29" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G29" t="s">
         <v>105</v>
-      </c>
-      <c r="G29" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1989,10 +1989,10 @@
         <v>36</v>
       </c>
       <c r="F30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2028,7 +2028,7 @@
         <v>39</v>
       </c>
       <c r="F33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2042,7 +2042,7 @@
         <v>40</v>
       </c>
       <c r="F34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2050,16 +2050,16 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C35" t="s">
         <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2067,13 +2067,13 @@
         <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D36" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2081,13 +2081,13 @@
         <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C37" t="s">
         <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F37" s="4"/>
     </row>
@@ -2096,13 +2096,13 @@
         <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C38" t="s">
         <v>19</v>
       </c>
       <c r="D38" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2110,7 +2110,7 @@
         <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C39" t="s">
         <v>20</v>
@@ -2124,7 +2124,7 @@
         <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C40" t="s">
         <v>21</v>
@@ -2138,7 +2138,7 @@
         <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C41" t="s">
         <v>22</v>
@@ -2152,7 +2152,7 @@
         <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C42" t="s">
         <v>23</v>
@@ -2166,7 +2166,7 @@
         <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C43" t="s">
         <v>24</v>
@@ -2180,7 +2180,7 @@
         <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C44" t="s">
         <v>25</v>
@@ -2194,7 +2194,7 @@
         <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C45" t="s">
         <v>26</v>
@@ -2208,7 +2208,7 @@
         <v>38</v>
       </c>
       <c r="B46" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C46" t="s">
         <v>27</v>
@@ -2222,10 +2222,10 @@
         <v>39</v>
       </c>
       <c r="C47" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D47" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2236,7 +2236,7 @@
         <v>28</v>
       </c>
       <c r="D48" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -15,6 +15,7 @@
     <sheet name="meta_data_names" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -483,9 +484,6 @@
     <t>Integer: switch to estimate or fix numbers-at-age: 0 = estimate dynamics, 1 = use input numbers-at-age in NbyageFixed, 2 = multiply input numbers-at-age (NbyageFixed) by a single scaling coefficient, 3 = multiply input numbers-at-age (NbyageFixed) by age specific scaling coefficient.</t>
   </si>
   <si>
-    <t>Integer: switch for which bioenergetics equation to use for each species for ft to scale max consumtion: 1 = Exponential (Stewart et al 1983), 2 = Temperature-dependendence for warm-water species (Kitchell et al 1977; sensu Holsman et al 2015), 3 = temperature dependence for cool and cold-water species (Thornton and Lessem 1979)</t>
-  </si>
-  <si>
     <t>Integer: which environmental index in env_data to use to drive bioenergetics</t>
   </si>
   <si>
@@ -502,6 +500,9 @@
   </si>
   <si>
     <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity,  descending logistic , or non-parametric (Selectivity = 5). 0 = no, 1 = penalized deviates given sel_sd_prior, 2 = random effect, 3 = time blocks with no penality, 4 = random walk following Dorn, 5 = random walk on ascending portion of double logistic only. If selectivity is set to type = 2 (non-parametric) this value will be the 1st penalty on selectivity.</t>
+  </si>
+  <si>
+    <t>Integer: switch for which bioenergetics equation to use for each species for ft to scale max consumtion: 1 = Exponential (Stewart et al 1983), 2 = Temperature-dependendence for warm-water species (Kitchell et al 1977; sensu Holsman et al 2015), 3 = temperature dependence for cool and cold-water species (Thornton and Lessem 1979); 4 = 1 for direct input of consumption in Pyrs  where consumption at age = Wt * Pyrs (CA set to 1, fday set to 1, CB set to 0)</t>
   </si>
 </sst>
 </file>
@@ -1493,7 +1494,7 @@
         <v>49</v>
       </c>
       <c r="G7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1516,7 +1517,7 @@
         <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1539,7 +1540,7 @@
         <v>67</v>
       </c>
       <c r="G9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2056,7 +2057,7 @@
         <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="F35" t="s">
         <v>75</v>
@@ -2073,7 +2074,7 @@
         <v>113</v>
       </c>
       <c r="D36" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2087,7 +2088,7 @@
         <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F37" s="4"/>
     </row>
@@ -2102,7 +2103,7 @@
         <v>19</v>
       </c>
       <c r="D38" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -15,12 +15,11 @@
     <sheet name="meta_data_names" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="157">
   <si>
     <t>nspp</t>
   </si>
@@ -67,9 +66,6 @@
     <t>M1_base</t>
   </si>
   <si>
-    <t>Mn_LatAge</t>
-  </si>
-  <si>
     <t>aLW</t>
   </si>
   <si>
@@ -139,9 +135,6 @@
     <t>Residual natural mortality for each species</t>
   </si>
   <si>
-    <t>Mean length-at-age for each species. Used when estimating time-invariant length-based gamma suitability (suitMode = 1) or time invariant length-based lognormal suitability (suitMode = 4)</t>
-  </si>
-  <si>
     <t>Parameters for weight-at-length power function for each species. . Used when estimating time-variant length-based gamma suitability (suitMode = 2) or time-variant length-based lognormal suitability (suitMode = 5)</t>
   </si>
   <si>
@@ -154,13 +147,7 @@
     <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
   </si>
   <si>
-    <t>UobsAge</t>
-  </si>
-  <si>
     <t>UobsWtAge</t>
-  </si>
-  <si>
-    <t>Stomach proportion by numbers for each predator, prey, predator age, prey age combination. Can also be year specific by including the column, "Year"</t>
   </si>
   <si>
     <t>Stomach proportion by weight for each predator, prey, predator age, prey age combination. Can also be year specific by including the column, "Year"</t>
@@ -1326,7 +1313,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
@@ -1338,25 +1325,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1364,22 +1351,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1387,22 +1374,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3" t="s">
         <v>84</v>
-      </c>
-      <c r="F3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1410,22 +1397,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1433,22 +1420,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1456,22 +1443,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1479,22 +1466,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" t="s">
         <v>133</v>
       </c>
-      <c r="C7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" t="s">
-        <v>137</v>
-      </c>
       <c r="E7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1502,22 +1489,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1525,22 +1512,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1548,22 +1535,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1571,22 +1558,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1594,22 +1581,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F12" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1617,22 +1604,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F13" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G13" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1640,22 +1627,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D14" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E14" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G14" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1663,22 +1650,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F15" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" t="s">
         <v>52</v>
-      </c>
-      <c r="G15" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1686,22 +1673,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C16" t="s">
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E16" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G16" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1709,22 +1696,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C17" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D17" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E17" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F17" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G17" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1732,22 +1719,22 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C18" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E18" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G18" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1755,22 +1742,22 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C19" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D19" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E19" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1778,22 +1765,22 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E20" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F20" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G20" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1801,22 +1788,22 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E21" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F21" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G21" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1824,19 +1811,19 @@
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F22" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G22" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1847,16 +1834,16 @@
         <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E23" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G23" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1867,16 +1854,16 @@
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E24" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1884,19 +1871,19 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E25" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G25" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1904,19 +1891,19 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D26" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E26" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G26" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1927,16 +1914,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E27" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G27" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1947,16 +1934,16 @@
         <v>10</v>
       </c>
       <c r="D28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E28" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F28" t="s">
+        <v>47</v>
+      </c>
+      <c r="G28" t="s">
         <v>51</v>
-      </c>
-      <c r="G28" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1967,16 +1954,16 @@
         <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E29" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G29" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1987,13 +1974,13 @@
         <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F30" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2004,7 +1991,7 @@
         <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2015,7 +2002,7 @@
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2026,24 +2013,27 @@
         <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F33" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26</v>
       </c>
+      <c r="B34" t="s">
+        <v>130</v>
+      </c>
       <c r="C34" t="s">
         <v>16</v>
       </c>
       <c r="D34" t="s">
-        <v>40</v>
+        <v>156</v>
       </c>
       <c r="F34" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2051,16 +2041,16 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C35" t="s">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F35" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2068,13 +2058,13 @@
         <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C36" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="D36" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2082,13 +2072,13 @@
         <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C37" t="s">
         <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F37" s="4"/>
     </row>
@@ -2097,13 +2087,13 @@
         <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C38" t="s">
         <v>19</v>
       </c>
       <c r="D38" t="s">
-        <v>156</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2111,13 +2101,13 @@
         <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C39" t="s">
         <v>20</v>
       </c>
       <c r="D39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2125,13 +2115,13 @@
         <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C40" t="s">
         <v>21</v>
       </c>
       <c r="D40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2139,13 +2129,13 @@
         <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C41" t="s">
         <v>22</v>
       </c>
       <c r="D41" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2153,13 +2143,13 @@
         <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C42" t="s">
         <v>23</v>
       </c>
       <c r="D42" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2167,13 +2157,13 @@
         <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C43" t="s">
         <v>24</v>
       </c>
       <c r="D43" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2181,13 +2171,13 @@
         <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C44" t="s">
         <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2195,27 +2185,24 @@
         <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C45" t="s">
         <v>26</v>
       </c>
       <c r="D45" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>38</v>
       </c>
-      <c r="B46" t="s">
-        <v>134</v>
-      </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="D46" t="s">
-        <v>43</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2223,10 +2210,10 @@
         <v>39</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="D47" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2234,32 +2221,10 @@
         <v>40</v>
       </c>
       <c r="C48" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D48" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>41</v>
-      </c>
-      <c r="C49" t="s">
-        <v>44</v>
-      </c>
-      <c r="D49" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>42</v>
-      </c>
-      <c r="C50" t="s">
-        <v>45</v>
-      </c>
-      <c r="D50" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="155">
   <si>
     <t>nspp</t>
   </si>
@@ -390,9 +390,6 @@
     <t>Age transition matrix (e.g. growth trajectory) used to convert age to length for length comp data. Can have multiple matrices for a species specified by Age_transition_index.</t>
   </si>
   <si>
-    <t>est_M1</t>
-  </si>
-  <si>
     <t>est_sex_ratio</t>
   </si>
   <si>
@@ -463,9 +460,6 @@
   </si>
   <si>
     <t>Numeric: initial value or fixed value for sd of normal likelihood for sex ration. Not yet able to estimate.</t>
-  </si>
-  <si>
-    <t>Integer: switch to estimate residual (multi-species mode) or total natural mortality (single-species mode). 0 = use fixed natural mortality from M1_base, 1 = estimate sex- and age-invariant M1, 2 = sex-specific (two-sex model), age-invariant M1, 3 =   estimate sex- and age-specific M1.</t>
   </si>
   <si>
     <t>Integer: switch to estimate or fix numbers-at-age: 0 = estimate dynamics, 1 = use input numbers-at-age in NbyageFixed, 2 = multiply input numbers-at-age (NbyageFixed) by a single scaling coefficient, 3 = multiply input numbers-at-age (NbyageFixed) by age specific scaling coefficient.</t>
@@ -1313,7 +1307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
@@ -1351,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
         <v>80</v>
@@ -1374,13 +1368,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E3" t="s">
         <v>80</v>
@@ -1397,13 +1391,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
         <v>80</v>
@@ -1420,13 +1414,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C5" t="s">
         <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E5" t="s">
         <v>80</v>
@@ -1443,13 +1437,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
         <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s">
         <v>80</v>
@@ -1466,13 +1460,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C7" t="s">
         <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E7" t="s">
         <v>80</v>
@@ -1481,7 +1475,7 @@
         <v>45</v>
       </c>
       <c r="G7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1489,13 +1483,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" t="s">
         <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E8" t="s">
         <v>80</v>
@@ -1504,7 +1498,7 @@
         <v>46</v>
       </c>
       <c r="G8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1512,13 +1506,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E9" t="s">
         <v>80</v>
@@ -1527,7 +1521,7 @@
         <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1535,13 +1529,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C10" t="s">
         <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E10" t="s">
         <v>80</v>
@@ -1558,13 +1552,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E11" t="s">
         <v>80</v>
@@ -1581,13 +1575,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E12" t="s">
         <v>80</v>
@@ -1604,13 +1598,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C13" t="s">
         <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E13" t="s">
         <v>80</v>
@@ -1627,13 +1621,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" t="s">
         <v>119</v>
       </c>
       <c r="D14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E14" t="s">
         <v>80</v>
@@ -1650,13 +1644,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C15" t="s">
         <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E15" t="s">
         <v>80</v>
@@ -1673,13 +1667,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C16" t="s">
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E16" t="s">
         <v>80</v>
@@ -1696,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E17" t="s">
         <v>80</v>
@@ -1719,13 +1713,13 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" t="s">
         <v>127</v>
-      </c>
-      <c r="D18" t="s">
-        <v>128</v>
       </c>
       <c r="E18" t="s">
         <v>80</v>
@@ -1742,13 +1736,13 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E19" t="s">
         <v>80</v>
@@ -1765,13 +1759,13 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E20" t="s">
         <v>80</v>
@@ -1787,14 +1781,11 @@
       <c r="A21">
         <v>13</v>
       </c>
-      <c r="B21" t="s">
-        <v>129</v>
-      </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="D21" t="s">
-        <v>148</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
         <v>80</v>
@@ -1811,10 +1802,10 @@
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="E22" t="s">
         <v>80</v>
@@ -1831,10 +1822,10 @@
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E23" t="s">
         <v>80</v>
@@ -1851,10 +1842,10 @@
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="E24" t="s">
         <v>80</v>
@@ -1871,10 +1862,10 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E25" t="s">
         <v>80</v>
@@ -1891,10 +1882,10 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E26" t="s">
         <v>80</v>
@@ -1911,10 +1902,10 @@
         <v>19</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="E27" t="s">
         <v>80</v>
@@ -1931,10 +1922,10 @@
         <v>20</v>
       </c>
       <c r="C28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E28" t="s">
         <v>80</v>
@@ -1951,10 +1942,10 @@
         <v>21</v>
       </c>
       <c r="C29" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E29" t="s">
         <v>80</v>
@@ -1971,10 +1962,10 @@
         <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F30" t="s">
         <v>79</v>
@@ -1988,10 +1979,10 @@
         <v>23</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1999,21 +1990,24 @@
         <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>25</v>
       </c>
+      <c r="B33" t="s">
+        <v>129</v>
+      </c>
       <c r="C33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D33" t="s">
-        <v>38</v>
+        <v>154</v>
       </c>
       <c r="F33" t="s">
         <v>55</v>
@@ -2024,13 +2018,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="F34" t="s">
         <v>62</v>
@@ -2041,13 +2035,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F35" t="s">
         <v>71</v>
@@ -2058,13 +2052,13 @@
         <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2072,13 +2066,13 @@
         <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D37" t="s">
-        <v>152</v>
+        <v>39</v>
       </c>
       <c r="F37" s="4"/>
     </row>
@@ -2087,13 +2081,13 @@
         <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2101,13 +2095,13 @@
         <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2115,10 +2109,10 @@
         <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D40" t="s">
         <v>41</v>
@@ -2129,10 +2123,10 @@
         <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C41" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D41" t="s">
         <v>41</v>
@@ -2143,10 +2137,10 @@
         <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D42" t="s">
         <v>41</v>
@@ -2157,10 +2151,10 @@
         <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C43" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D43" t="s">
         <v>41</v>
@@ -2171,10 +2165,10 @@
         <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C44" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D44" t="s">
         <v>41</v>
@@ -2184,14 +2178,11 @@
       <c r="A45">
         <v>37</v>
       </c>
-      <c r="B45" t="s">
-        <v>130</v>
-      </c>
       <c r="C45" t="s">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="D45" t="s">
-        <v>41</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2199,10 +2190,10 @@
         <v>38</v>
       </c>
       <c r="C46" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2210,20 +2201,9 @@
         <v>39</v>
       </c>
       <c r="C47" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D47" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>40</v>
-      </c>
-      <c r="C48" t="s">
-        <v>42</v>
-      </c>
-      <c r="D48" t="s">
         <v>43</v>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -342,9 +342,6 @@
     <t>Variance of q prior: dnorm (log_q, log_q_prior, q_sd_prior)</t>
   </si>
   <si>
-    <t>Wether a time-varying q should be estimated. 0 = no, 1 = penalized deviate, 2 = random effect, 3 = time blocks with no penalty; 4 = random walk from mean following Dorn 2018 (dnorm(q_y - q_y-1, 0, sigma). If Estimate_q = 5, this determines the environmental index to be used in the equation log(q_y) = q_mu + beta * index_y</t>
-  </si>
-  <si>
     <t>Estimate catchability? (0 = fixed at prior; - 1 = Estimate single parameter; - 2 = Estimate single parameter with prior; - 3 = Estimate analytical q  from Ludwig and Walters 1994;  - 4 = Estimate power equation; - 5 - Linear equation log(q_y) = q_mu + beta * index_y)</t>
   </si>
   <si>
@@ -480,10 +477,13 @@
     <t>Number of ages to estimate non-parametric selectivity for Selectivity = 2 &amp; 5. Not used otherwise</t>
   </si>
   <si>
-    <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity,  descending logistic , or non-parametric (Selectivity = 5). 0 = no, 1 = penalized deviates given sel_sd_prior, 2 = random effect, 3 = time blocks with no penality, 4 = random walk following Dorn, 5 = random walk on ascending portion of double logistic only. If selectivity is set to type = 2 (non-parametric) this value will be the 1st penalty on selectivity.</t>
-  </si>
-  <si>
     <t>Integer: switch for which bioenergetics equation to use for each species for ft to scale max consumtion: 1 = Exponential (Stewart et al 1983), 2 = Temperature-dependendence for warm-water species (Kitchell et al 1977; sensu Holsman et al 2015), 3 = temperature dependence for cool and cold-water species (Thornton and Lessem 1979); 4 = 1 for direct input of consumption in Pyrs  where consumption at age = Wt * Pyrs (CA set to 1, fday set to 1, CB set to 0)</t>
+  </si>
+  <si>
+    <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity,  descending logistic , or non-parametric (Selectivity = 5). 0 = no, 1 = penalized deviates given sel_sd_prior, 3 = time blocks with no penality, 4 = random walk following Dorn, 5 = random walk on ascending portion of double logistic only. If selectivity is set to type = 2 (non-parametric) this value will be the 1st penalty on selectivity. "random_sel" treats random deviates and random walk parameters as random effects.</t>
+  </si>
+  <si>
+    <t>Wether a time-varying q should be estimated. 0 = no, 1 = penalized deviate, 3 = time blocks with no penalty; 4 = random walk from mean following Dorn 2018 (dnorm(q_y - q_y-1, 0, sigma). If Estimate_q = 5, this determines the environmental index to be used in the equation log(q_y) = q_mu + beta * index_y. If "random_q" is selected in fit_mod, penalized deviates (1) and random walk parameters (4) will be treated as random effects.</t>
   </si>
 </sst>
 </file>
@@ -1325,7 +1325,7 @@
         <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>29</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" t="s">
         <v>80</v>
@@ -1368,13 +1368,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E3" t="s">
         <v>80</v>
@@ -1391,13 +1391,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s">
         <v>80</v>
@@ -1414,13 +1414,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5" t="s">
         <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
         <v>80</v>
@@ -1437,13 +1437,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C6" t="s">
         <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E6" t="s">
         <v>80</v>
@@ -1452,7 +1452,7 @@
         <v>68</v>
       </c>
       <c r="G6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1460,13 +1460,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C7" t="s">
         <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E7" t="s">
         <v>80</v>
@@ -1475,7 +1475,7 @@
         <v>45</v>
       </c>
       <c r="G7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1483,13 +1483,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C8" t="s">
         <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
         <v>80</v>
@@ -1498,7 +1498,7 @@
         <v>46</v>
       </c>
       <c r="G8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1506,13 +1506,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E9" t="s">
         <v>80</v>
@@ -1529,13 +1529,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
         <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E10" t="s">
         <v>80</v>
@@ -1552,13 +1552,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E11" t="s">
         <v>80</v>
@@ -1575,13 +1575,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E12" t="s">
         <v>80</v>
@@ -1598,13 +1598,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C13" t="s">
         <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E13" t="s">
         <v>80</v>
@@ -1621,13 +1621,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E14" t="s">
         <v>80</v>
@@ -1644,13 +1644,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C15" t="s">
         <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E15" t="s">
         <v>80</v>
@@ -1667,22 +1667,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C16" t="s">
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E16" t="s">
         <v>80</v>
       </c>
       <c r="F16" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" t="s">
         <v>120</v>
-      </c>
-      <c r="G16" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E17" t="s">
         <v>80</v>
@@ -1713,13 +1713,13 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C18" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" t="s">
         <v>126</v>
-      </c>
-      <c r="D18" t="s">
-        <v>127</v>
       </c>
       <c r="E18" t="s">
         <v>80</v>
@@ -1728,7 +1728,7 @@
         <v>49</v>
       </c>
       <c r="G18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1736,13 +1736,13 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E19" t="s">
         <v>80</v>
@@ -1759,13 +1759,13 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E20" t="s">
         <v>80</v>
@@ -1794,7 +1794,7 @@
         <v>65</v>
       </c>
       <c r="G21" t="s">
-        <v>107</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1842,10 +1842,10 @@
         <v>16</v>
       </c>
       <c r="C24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" t="s">
         <v>114</v>
-      </c>
-      <c r="D24" t="s">
-        <v>115</v>
       </c>
       <c r="E24" t="s">
         <v>80</v>
@@ -1862,10 +1862,10 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" t="s">
         <v>112</v>
-      </c>
-      <c r="D25" t="s">
-        <v>113</v>
       </c>
       <c r="E25" t="s">
         <v>80</v>
@@ -1885,7 +1885,7 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E26" t="s">
         <v>80</v>
@@ -2001,13 +2001,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C33" t="s">
         <v>16</v>
       </c>
       <c r="D33" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F33" t="s">
         <v>55</v>
@@ -2018,13 +2018,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F34" t="s">
         <v>62</v>
@@ -2035,13 +2035,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C35" t="s">
         <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F35" t="s">
         <v>71</v>
@@ -2052,13 +2052,13 @@
         <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C36" t="s">
         <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2066,7 +2066,7 @@
         <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C37" t="s">
         <v>19</v>
@@ -2081,7 +2081,7 @@
         <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C38" t="s">
         <v>20</v>
@@ -2095,7 +2095,7 @@
         <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C39" t="s">
         <v>21</v>
@@ -2109,7 +2109,7 @@
         <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C40" t="s">
         <v>22</v>
@@ -2123,7 +2123,7 @@
         <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C41" t="s">
         <v>23</v>
@@ -2137,7 +2137,7 @@
         <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C42" t="s">
         <v>24</v>
@@ -2151,7 +2151,7 @@
         <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C43" t="s">
         <v>25</v>
@@ -2165,7 +2165,7 @@
         <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C44" t="s">
         <v>26</v>
@@ -2179,10 +2179,10 @@
         <v>37</v>
       </c>
       <c r="C45" t="s">
+        <v>109</v>
+      </c>
+      <c r="D45" t="s">
         <v>110</v>
-      </c>
-      <c r="D45" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2193,7 +2193,7 @@
         <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11013"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grant Adams\Documents\GitHub\Rceattle\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grantadams/Documents/GitHub/Rceattle/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BA65B8-EA28-7146-8B5C-B1CE252624DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="465" windowWidth="25605" windowHeight="12345"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="31540" windowHeight="18100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data_names" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="153">
   <si>
     <t>nspp</t>
   </si>
@@ -291,18 +292,6 @@
     <t>Age at which selectivity is non-zero</t>
   </si>
   <si>
-    <t>Acuumulation_age_lower</t>
-  </si>
-  <si>
-    <t>Ages below this will be grouped to this age for composition data. For example, if set to 2, comp data for age 2 will include 1 and 2 year olds.</t>
-  </si>
-  <si>
-    <t>Acuumulation_age_upper</t>
-  </si>
-  <si>
-    <t>Ages above this will be grouped to this age for composition data. For example, if set to 9 for a species with 10 ages, comp data for age 9 will include 9 and 10 year olds.</t>
-  </si>
-  <si>
     <t>Survey_sd_prior</t>
   </si>
   <si>
@@ -484,12 +473,18 @@
   </si>
   <si>
     <t>Wether a time-varying q should be estimated. 0 = no, 1 = penalized deviate, 3 = time blocks with no penalty; 4 = random walk from mean following Dorn 2018 (dnorm(q_y - q_y-1, 0, sigma). If Estimate_q = 5, this determines the environmental index to be used in the equation log(q_y) = q_mu + beta * index_y. If "random_q" is selected in fit_mod, penalized deviates (1) and random walk parameters (4) will be treated as random effects.</t>
+  </si>
+  <si>
+    <t>Comp_loglike</t>
+  </si>
+  <si>
+    <t>Composition data distribution (0 = multinomial; 1 = dirichlet-multinomial)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -974,16 +969,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1306,18 +1298,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G47"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="119.42578125" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="119.5" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -1325,7 +1317,7 @@
         <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>29</v>
@@ -1340,18 +1332,18 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E2" t="s">
         <v>80</v>
@@ -1363,18 +1355,18 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E3" t="s">
         <v>80</v>
@@ -1386,18 +1378,18 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
         <v>80</v>
@@ -1409,18 +1401,18 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
         <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
         <v>80</v>
@@ -1432,18 +1424,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C6" t="s">
         <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
         <v>80</v>
@@ -1452,21 +1444,21 @@
         <v>68</v>
       </c>
       <c r="G6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C7" t="s">
         <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E7" t="s">
         <v>80</v>
@@ -1475,21 +1467,21 @@
         <v>45</v>
       </c>
       <c r="G7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C8" t="s">
         <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E8" t="s">
         <v>80</v>
@@ -1498,21 +1490,21 @@
         <v>46</v>
       </c>
       <c r="G8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E9" t="s">
         <v>80</v>
@@ -1521,21 +1513,21 @@
         <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C10" t="s">
         <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E10" t="s">
         <v>80</v>
@@ -1547,18 +1539,18 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E11" t="s">
         <v>80</v>
@@ -1570,214 +1562,214 @@
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E12" t="s">
         <v>80</v>
       </c>
       <c r="F12" t="s">
-        <v>90</v>
+        <v>151</v>
       </c>
       <c r="G12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C13" t="s">
         <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E13" t="s">
         <v>80</v>
       </c>
-      <c r="F13" t="s">
-        <v>92</v>
+      <c r="F13" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="G13" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E14" t="s">
         <v>80</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>56</v>
+      <c r="F14" t="s">
+        <v>48</v>
       </c>
       <c r="G14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C15" t="s">
         <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E15" t="s">
         <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>115</v>
       </c>
       <c r="G15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C16" t="s">
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E16" t="s">
         <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="G16" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D17" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E17" t="s">
         <v>80</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E18" t="s">
         <v>80</v>
       </c>
-      <c r="F18" t="s">
-        <v>49</v>
+      <c r="F18" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="G18" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E19" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>104</v>
+      <c r="F19" t="s">
+        <v>66</v>
       </c>
       <c r="G19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E20" t="s">
         <v>80</v>
       </c>
       <c r="F20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G20" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>13</v>
       </c>
@@ -1785,19 +1777,19 @@
         <v>80</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E21" t="s">
         <v>80</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="G21" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>14</v>
       </c>
@@ -1810,14 +1802,14 @@
       <c r="E22" t="s">
         <v>80</v>
       </c>
-      <c r="F22" t="s">
-        <v>105</v>
+      <c r="F22" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="G22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>15</v>
       </c>
@@ -1830,54 +1822,54 @@
       <c r="E23" t="s">
         <v>80</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>95</v>
+      <c r="F23" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="G23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s">
         <v>80</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G24" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E25" t="s">
         <v>80</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>96</v>
+      <c r="F25" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="G25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>18</v>
       </c>
@@ -1885,19 +1877,19 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E26" t="s">
         <v>80</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G26" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>19</v>
       </c>
@@ -1910,14 +1902,14 @@
       <c r="E27" t="s">
         <v>80</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>98</v>
+      <c r="F27" t="s">
+        <v>47</v>
       </c>
       <c r="G27" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>20</v>
       </c>
@@ -1930,14 +1922,14 @@
       <c r="E28" t="s">
         <v>80</v>
       </c>
-      <c r="F28" t="s">
-        <v>47</v>
+      <c r="F28" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="G28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>21</v>
       </c>
@@ -1950,14 +1942,8 @@
       <c r="E29" t="s">
         <v>80</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G29" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>22</v>
       </c>
@@ -1971,10 +1957,10 @@
         <v>79</v>
       </c>
       <c r="G30" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>23</v>
       </c>
@@ -1985,7 +1971,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>24</v>
       </c>
@@ -1996,77 +1982,77 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C33" t="s">
         <v>16</v>
       </c>
       <c r="D33" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F33" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D34" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F34" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C35" t="s">
         <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F35" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C36" t="s">
         <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C37" t="s">
         <v>19</v>
@@ -2074,14 +2060,14 @@
       <c r="D37" t="s">
         <v>39</v>
       </c>
-      <c r="F37" s="4"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C38" t="s">
         <v>20</v>
@@ -2090,12 +2076,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C39" t="s">
         <v>21</v>
@@ -2104,12 +2090,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C40" t="s">
         <v>22</v>
@@ -2118,12 +2104,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C41" t="s">
         <v>23</v>
@@ -2132,12 +2118,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C42" t="s">
         <v>24</v>
@@ -2146,12 +2132,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C43" t="s">
         <v>25</v>
@@ -2160,12 +2146,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C44" t="s">
         <v>26</v>
@@ -2174,18 +2160,18 @@
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>37</v>
       </c>
       <c r="C45" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D45" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>38</v>
       </c>
@@ -2193,10 +2179,10 @@
         <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>39</v>
       </c>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grantadams/Documents/GitHub/Rceattle/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BA65B8-EA28-7146-8B5C-B1CE252624DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96251511-3738-954F-96A4-1F55F65F221A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="31540" windowHeight="18100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35760" yWindow="2340" windowWidth="31540" windowHeight="18100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data_names" sheetId="1" r:id="rId1"/>
@@ -43,12 +43,6 @@
     <t>other_food</t>
   </si>
   <si>
-    <t>srv_biom</t>
-  </si>
-  <si>
-    <t>fsh_biom</t>
-  </si>
-  <si>
     <t>age_trans_matrix</t>
   </si>
   <si>
@@ -196,15 +190,9 @@
     <t>Is the observation in weight (kg) set as 1, if the observation is in numbers caught, set as 2</t>
   </si>
   <si>
-    <t>Estimate survey variance (0 = use CV from srv_biom, 1 = yes, 2 = analytically estimate following (Ludwig and Walters 1994)</t>
-  </si>
-  <si>
     <t>Starting value to be used if Estimate_sigma_index = 1</t>
   </si>
   <si>
-    <t>Estimate fishery variance (0 = use CV from srv_biom, 1 = yes, 2 = analytically estimate following (Ludwig and Walters 1994)</t>
-  </si>
-  <si>
     <t>Starting value to be used if Estimate_sigma_catch = 1</t>
   </si>
   <si>
@@ -479,6 +467,18 @@
   </si>
   <si>
     <t>Composition data distribution (0 = multinomial; 1 = dirichlet-multinomial)</t>
+  </si>
+  <si>
+    <t>index_data</t>
+  </si>
+  <si>
+    <t>Estimate survey variance (0 = use CV from index_data, 1 = yes, 2 = analytically estimate following (Ludwig and Walters 1994)</t>
+  </si>
+  <si>
+    <t>Estimate fishery variance (0 = use CV from index_data, 1 = yes, 2 = analytically estimate following (Ludwig and Walters 1994)</t>
+  </si>
+  <si>
+    <t>catch_data</t>
   </si>
 </sst>
 </file>
@@ -1311,25 +1311,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -1337,22 +1337,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -1360,22 +1360,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" t="s">
         <v>80</v>
-      </c>
-      <c r="F3" t="s">
-        <v>82</v>
-      </c>
-      <c r="G3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -1383,22 +1383,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -1406,22 +1406,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -1429,22 +1429,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -1452,22 +1452,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" t="s">
         <v>123</v>
       </c>
-      <c r="C7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" t="s">
-        <v>127</v>
-      </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -1475,22 +1475,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -1498,22 +1498,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -1521,22 +1521,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -1544,22 +1544,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G11" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -1567,22 +1567,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F12" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G12" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -1590,22 +1590,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -1613,22 +1613,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C14" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -1636,22 +1636,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G15" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -1659,22 +1659,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C16" t="s">
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E16" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G16" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -1682,22 +1682,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E17" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G17" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -1705,22 +1705,22 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D18" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -1728,22 +1728,22 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F19" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G19" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -1751,22 +1751,22 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E20" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G20" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -1774,19 +1774,19 @@
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F21" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G21" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -1794,19 +1794,19 @@
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G22" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -1814,19 +1814,19 @@
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>152</v>
       </c>
       <c r="D23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E23" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -1834,19 +1834,19 @@
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E24" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s">
-        <v>60</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -1854,19 +1854,19 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E25" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G25" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -1874,19 +1874,19 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E26" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G26" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -1894,19 +1894,19 @@
         <v>19</v>
       </c>
       <c r="C27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E27" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -1914,19 +1914,19 @@
         <v>20</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E28" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G28" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
@@ -1934,13 +1934,13 @@
         <v>21</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D29" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E29" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -1948,16 +1948,16 @@
         <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F30" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -1965,10 +1965,10 @@
         <v>23</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
@@ -1976,10 +1976,10 @@
         <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -1987,16 +1987,16 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C33" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F33" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -2004,16 +2004,16 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D34" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F34" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -2021,16 +2021,16 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C35" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F35" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
@@ -2038,13 +2038,13 @@
         <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
@@ -2052,13 +2052,13 @@
         <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C37" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F37" s="2"/>
     </row>
@@ -2067,13 +2067,13 @@
         <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C38" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
@@ -2081,13 +2081,13 @@
         <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C39" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -2095,13 +2095,13 @@
         <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C40" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D40" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
@@ -2109,13 +2109,13 @@
         <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C41" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D41" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -2123,13 +2123,13 @@
         <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C42" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D42" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -2137,13 +2137,13 @@
         <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C43" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D43" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
@@ -2151,13 +2151,13 @@
         <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C44" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D44" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
@@ -2165,10 +2165,10 @@
         <v>37</v>
       </c>
       <c r="C45" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D45" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
@@ -2176,10 +2176,10 @@
         <v>38</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
@@ -2187,10 +2187,10 @@
         <v>39</v>
       </c>
       <c r="C47" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D47" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grantadams/Documents/GitHub/Rceattle/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96251511-3738-954F-96A4-1F55F65F221A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4630FE8B-3C65-534F-A794-743F0BED64D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35760" yWindow="2340" windowWidth="31540" windowHeight="18100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data_names" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="155">
   <si>
     <t>nspp</t>
   </si>
@@ -479,6 +479,12 @@
   </si>
   <si>
     <t>catch_data</t>
+  </si>
+  <si>
+    <t>Age_max_selected</t>
+  </si>
+  <si>
+    <t>Age at which selectivity = 1. If NA, it will not normalize selectivity. If &lt; 0, will normalize selectivity by the max.</t>
   </si>
 </sst>
 </file>
@@ -1579,10 +1585,10 @@
         <v>76</v>
       </c>
       <c r="F12" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="G12" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -1601,11 +1607,11 @@
       <c r="E13" t="s">
         <v>76</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>54</v>
+      <c r="F13" t="s">
+        <v>147</v>
       </c>
       <c r="G13" t="s">
-        <v>55</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -1624,11 +1630,11 @@
       <c r="E14" t="s">
         <v>76</v>
       </c>
-      <c r="F14" t="s">
-        <v>46</v>
+      <c r="F14" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="G14" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -1648,10 +1654,10 @@
         <v>76</v>
       </c>
       <c r="F15" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="G15" t="s">
-        <v>112</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -1671,10 +1677,10 @@
         <v>76</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="G16" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -1694,10 +1700,10 @@
         <v>76</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -1716,11 +1722,11 @@
       <c r="E18" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>96</v>
+      <c r="F18" t="s">
+        <v>47</v>
       </c>
       <c r="G18" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -1739,11 +1745,11 @@
       <c r="E19" t="s">
         <v>76</v>
       </c>
-      <c r="F19" t="s">
-        <v>62</v>
+      <c r="F19" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="G19" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -1763,10 +1769,10 @@
         <v>76</v>
       </c>
       <c r="F20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G20" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -1783,10 +1789,10 @@
         <v>76</v>
       </c>
       <c r="F21" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="G21" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -1802,11 +1808,11 @@
       <c r="E22" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>87</v>
+      <c r="F22" t="s">
+        <v>97</v>
       </c>
       <c r="G22" t="s">
-        <v>150</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -1823,10 +1829,10 @@
         <v>76</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G23" t="s">
-        <v>56</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -1843,10 +1849,10 @@
         <v>76</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G24" t="s">
-        <v>151</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -1863,10 +1869,10 @@
         <v>76</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -1883,10 +1889,10 @@
         <v>76</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G26" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -1902,11 +1908,11 @@
       <c r="E27" t="s">
         <v>76</v>
       </c>
-      <c r="F27" t="s">
-        <v>45</v>
+      <c r="F27" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="G27" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -1922,11 +1928,11 @@
       <c r="E28" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>92</v>
+      <c r="F28" t="s">
+        <v>45</v>
       </c>
       <c r="G28" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
@@ -1942,6 +1948,12 @@
       <c r="E29" t="s">
         <v>76</v>
       </c>
+      <c r="F29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G29" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30">
@@ -1953,11 +1965,8 @@
       <c r="D30" t="s">
         <v>34</v>
       </c>
-      <c r="F30" t="s">
-        <v>75</v>
-      </c>
-      <c r="G30" t="s">
-        <v>94</v>
+      <c r="E30" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -1969,6 +1978,12 @@
       </c>
       <c r="D31" t="s">
         <v>35</v>
+      </c>
+      <c r="F31" t="s">
+        <v>75</v>
+      </c>
+      <c r="G31" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grantadams/Documents/GitHub/Rceattle/inst/extdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grant.adams\GitHub\Rceattle\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4630FE8B-3C65-534F-A794-743F0BED64D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0872DD-B699-47F9-A158-D628F2BC7191}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="765" windowWidth="34560" windowHeight="21585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data_names" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="147">
   <si>
     <t>nspp</t>
   </si>
@@ -142,9 +142,6 @@
     <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
   </si>
   <si>
-    <t>UobsWtAge</t>
-  </si>
-  <si>
     <t>Stomach proportion by weight for each predator, prey, predator age, prey age combination. Can also be year specific by including the column, "Year"</t>
   </si>
   <si>
@@ -235,9 +232,6 @@
     <t>spawn_month</t>
   </si>
   <si>
-    <t>R_sexr</t>
-  </si>
-  <si>
     <t>minage</t>
   </si>
   <si>
@@ -364,21 +358,9 @@
     <t>Age transition matrix (e.g. growth trajectory) used to convert age to length for length comp data. Can have multiple matrices for a species specified by Age_transition_index.</t>
   </si>
   <si>
-    <t>est_sex_ratio</t>
-  </si>
-  <si>
-    <t>sex_ratio_sigma</t>
-  </si>
-  <si>
     <t>estDynamics</t>
   </si>
   <si>
-    <t>proj_F</t>
-  </si>
-  <si>
-    <t>Unused</t>
-  </si>
-  <si>
     <t>Control</t>
   </si>
   <si>
@@ -394,9 +376,6 @@
     <t>Numeric: spawning month of the population to adjust the numbers at spawning</t>
   </si>
   <si>
-    <t>Numeric: percent of recruitment that is female (ignored if nsex = 1)</t>
-  </si>
-  <si>
     <t>Integer: end year of the hindcast</t>
   </si>
   <si>
@@ -430,12 +409,6 @@
     <t>Numeric: other food in the ecosystem for each species (kg)</t>
   </si>
   <si>
-    <t>Integer: is sex ration F/(M+F) to be included in the likelihood (assumed normal); 0 = no, 1 = use annual average across ages (uses 2nd age in propF data), 2 = age, and year specific (TBD)</t>
-  </si>
-  <si>
-    <t>Numeric: initial value or fixed value for sd of normal likelihood for sex ration. Not yet able to estimate.</t>
-  </si>
-  <si>
     <t>Integer: switch to estimate or fix numbers-at-age: 0 = estimate dynamics, 1 = use input numbers-at-age in NbyageFixed, 2 = multiply input numbers-at-age (NbyageFixed) by a single scaling coefficient, 3 = multiply input numbers-at-age (NbyageFixed) by age specific scaling coefficient.</t>
   </si>
   <si>
@@ -485,6 +458,9 @@
   </si>
   <si>
     <t>Age at which selectivity = 1. If NA, it will not normalize selectivity. If &lt; 0, will normalize selectivity by the max.</t>
+  </si>
+  <si>
+    <t>stom_prop_data</t>
   </si>
 </sst>
 </file>
@@ -1305,17 +1281,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G43"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="119.5" customWidth="1"/>
-    <col min="5" max="5" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="119.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
@@ -1323,7 +1299,7 @@
         <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>27</v>
@@ -1332,880 +1308,824 @@
         <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" t="s">
         <v>77</v>
       </c>
-      <c r="G2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" t="s">
         <v>76</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>78</v>
       </c>
-      <c r="G3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" t="s">
         <v>70</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" t="s">
         <v>123</v>
       </c>
-      <c r="E7" t="s">
-        <v>76</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="E10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" t="s">
+        <v>144</v>
+      </c>
+      <c r="G12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" t="s">
+        <v>138</v>
+      </c>
+      <c r="G13" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" t="s">
+        <v>127</v>
+      </c>
+      <c r="E14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" t="s">
+        <v>128</v>
+      </c>
+      <c r="E15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" t="s">
+        <v>129</v>
+      </c>
+      <c r="E16" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" t="s">
+        <v>109</v>
+      </c>
+      <c r="G16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>143</v>
+      </c>
+      <c r="D19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" t="s">
+        <v>74</v>
+      </c>
+      <c r="F21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>18</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" t="s">
+        <v>111</v>
+      </c>
+      <c r="E22" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>20</v>
+      </c>
+      <c r="C24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>21</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" t="s">
+        <v>74</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G25" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" t="s">
-        <v>124</v>
-      </c>
-      <c r="E8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" t="s">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>23</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" t="s">
         <v>44</v>
       </c>
-      <c r="G8" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E9" t="s">
-        <v>76</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>119</v>
-      </c>
-      <c r="C10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" t="s">
-        <v>129</v>
-      </c>
-      <c r="E10" t="s">
-        <v>76</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="G28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" t="s">
+        <v>135</v>
+      </c>
+      <c r="E29" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G29" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" t="s">
         <v>130</v>
       </c>
-      <c r="E11" t="s">
-        <v>76</v>
-      </c>
-      <c r="F11" t="s">
-        <v>84</v>
-      </c>
-      <c r="G11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>119</v>
-      </c>
-      <c r="C12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="E30" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>27</v>
+      </c>
+      <c r="B31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" t="s">
         <v>131</v>
       </c>
-      <c r="E12" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" t="s">
-        <v>153</v>
-      </c>
-      <c r="G12" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>119</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="F31" t="s">
         <v>73</v>
       </c>
-      <c r="D13" t="s">
+      <c r="G31" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" t="s">
         <v>132</v>
       </c>
-      <c r="E13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F13" t="s">
-        <v>147</v>
-      </c>
-      <c r="G13" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" t="s">
-        <v>133</v>
-      </c>
-      <c r="E14" t="s">
-        <v>76</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" t="s">
-        <v>134</v>
-      </c>
-      <c r="E15" t="s">
-        <v>76</v>
-      </c>
-      <c r="F15" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>119</v>
-      </c>
-      <c r="C16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" t="s">
-        <v>135</v>
-      </c>
-      <c r="E16" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" t="s">
-        <v>111</v>
-      </c>
-      <c r="G16" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" t="s">
-        <v>116</v>
-      </c>
-      <c r="D17" t="s">
-        <v>138</v>
-      </c>
-      <c r="E17" t="s">
-        <v>76</v>
-      </c>
-      <c r="F17" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17" t="s">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
+        <v>114</v>
+      </c>
+      <c r="C34" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" t="s">
+        <v>38</v>
+      </c>
+      <c r="F34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>31</v>
+      </c>
+      <c r="B35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" t="s">
+        <v>39</v>
+      </c>
+      <c r="F35" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>10</v>
-      </c>
-      <c r="B18" t="s">
-        <v>119</v>
-      </c>
-      <c r="C18" t="s">
-        <v>117</v>
-      </c>
-      <c r="D18" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" t="s">
-        <v>76</v>
-      </c>
-      <c r="F18" t="s">
-        <v>47</v>
-      </c>
-      <c r="G18" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>11</v>
-      </c>
-      <c r="B19" t="s">
-        <v>119</v>
-      </c>
-      <c r="C19" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>32</v>
+      </c>
+      <c r="B36" t="s">
         <v>114</v>
       </c>
-      <c r="D19" t="s">
-        <v>136</v>
-      </c>
-      <c r="E19" t="s">
-        <v>76</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G19" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>12</v>
-      </c>
-      <c r="B20" t="s">
-        <v>119</v>
-      </c>
-      <c r="C20" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" t="s">
-        <v>137</v>
-      </c>
-      <c r="E20" t="s">
-        <v>76</v>
-      </c>
-      <c r="F20" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>13</v>
-      </c>
-      <c r="C21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" t="s">
-        <v>95</v>
-      </c>
-      <c r="E21" t="s">
-        <v>76</v>
-      </c>
-      <c r="F21" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>14</v>
-      </c>
-      <c r="C22" t="s">
-        <v>149</v>
-      </c>
-      <c r="D22" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" t="s">
-        <v>76</v>
-      </c>
-      <c r="F22" t="s">
-        <v>97</v>
-      </c>
-      <c r="G22" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>15</v>
-      </c>
-      <c r="C23" t="s">
-        <v>152</v>
-      </c>
-      <c r="D23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G23" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>16</v>
-      </c>
-      <c r="C24" t="s">
-        <v>105</v>
-      </c>
-      <c r="D24" t="s">
-        <v>106</v>
-      </c>
-      <c r="E24" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>17</v>
-      </c>
-      <c r="C25" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" t="s">
-        <v>104</v>
-      </c>
-      <c r="E25" t="s">
-        <v>76</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G25" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>18</v>
-      </c>
-      <c r="C26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" t="s">
-        <v>113</v>
-      </c>
-      <c r="E26" t="s">
-        <v>76</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>19</v>
-      </c>
-      <c r="C27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27" t="s">
-        <v>76</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G27" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28">
+      <c r="C36" t="s">
         <v>20</v>
       </c>
-      <c r="C28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" t="s">
-        <v>76</v>
-      </c>
-      <c r="F28" t="s">
-        <v>45</v>
-      </c>
-      <c r="G28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29">
+      <c r="D36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>33</v>
+      </c>
+      <c r="B37" t="s">
+        <v>114</v>
+      </c>
+      <c r="C37" t="s">
         <v>21</v>
       </c>
-      <c r="C29" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" t="s">
-        <v>33</v>
-      </c>
-      <c r="E29" t="s">
-        <v>76</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G29" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30">
+      <c r="D37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>34</v>
+      </c>
+      <c r="B38" t="s">
+        <v>114</v>
+      </c>
+      <c r="C38" t="s">
         <v>22</v>
       </c>
-      <c r="C30" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" t="s">
-        <v>34</v>
-      </c>
-      <c r="E30" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31">
+      <c r="D38" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>35</v>
+      </c>
+      <c r="B39" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" t="s">
         <v>23</v>
-      </c>
-      <c r="C31" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" t="s">
-        <v>35</v>
-      </c>
-      <c r="F31" t="s">
-        <v>75</v>
-      </c>
-      <c r="G31" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>24</v>
-      </c>
-      <c r="C32" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>25</v>
-      </c>
-      <c r="B33" t="s">
-        <v>120</v>
-      </c>
-      <c r="C33" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33" t="s">
-        <v>144</v>
-      </c>
-      <c r="F33" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>26</v>
-      </c>
-      <c r="B34" t="s">
-        <v>120</v>
-      </c>
-      <c r="C34" t="s">
-        <v>100</v>
-      </c>
-      <c r="D34" t="s">
-        <v>139</v>
-      </c>
-      <c r="F34" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>27</v>
-      </c>
-      <c r="B35" t="s">
-        <v>120</v>
-      </c>
-      <c r="C35" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" t="s">
-        <v>140</v>
-      </c>
-      <c r="F35" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>28</v>
-      </c>
-      <c r="B36" t="s">
-        <v>120</v>
-      </c>
-      <c r="C36" t="s">
-        <v>16</v>
-      </c>
-      <c r="D36" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>29</v>
-      </c>
-      <c r="B37" t="s">
-        <v>120</v>
-      </c>
-      <c r="C37" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" t="s">
-        <v>37</v>
-      </c>
-      <c r="F37" s="2"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>30</v>
-      </c>
-      <c r="B38" t="s">
-        <v>120</v>
-      </c>
-      <c r="C38" t="s">
-        <v>18</v>
-      </c>
-      <c r="D38" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>31</v>
-      </c>
-      <c r="B39" t="s">
-        <v>120</v>
-      </c>
-      <c r="C39" t="s">
-        <v>19</v>
       </c>
       <c r="D39" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C40" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D40" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>33</v>
-      </c>
-      <c r="B41" t="s">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="C41" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="D41" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>38</v>
+      </c>
+      <c r="C42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43">
         <v>39</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>34</v>
-      </c>
-      <c r="B42" t="s">
-        <v>120</v>
-      </c>
-      <c r="C42" t="s">
-        <v>22</v>
-      </c>
-      <c r="D42" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>35</v>
-      </c>
-      <c r="B43" t="s">
-        <v>120</v>
-      </c>
       <c r="C43" t="s">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="D43" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>36</v>
-      </c>
-      <c r="B44" t="s">
-        <v>120</v>
-      </c>
-      <c r="C44" t="s">
-        <v>24</v>
-      </c>
-      <c r="D44" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>37</v>
-      </c>
-      <c r="C45" t="s">
-        <v>101</v>
-      </c>
-      <c r="D45" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>38</v>
-      </c>
-      <c r="C46" t="s">
-        <v>25</v>
-      </c>
-      <c r="D46" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <v>39</v>
-      </c>
-      <c r="C47" t="s">
         <v>40</v>
-      </c>
-      <c r="D47" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grant.adams\GitHub\Rceattle\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grantadams/Documents/GitHub/Rceattle/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0872DD-B699-47F9-A158-D628F2BC7191}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4630FE8B-3C65-534F-A794-743F0BED64D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="765" windowWidth="34560" windowHeight="21585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data_names" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="155">
   <si>
     <t>nspp</t>
   </si>
@@ -142,6 +142,9 @@
     <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
   </si>
   <si>
+    <t>UobsWtAge</t>
+  </si>
+  <si>
     <t>Stomach proportion by weight for each predator, prey, predator age, prey age combination. Can also be year specific by including the column, "Year"</t>
   </si>
   <si>
@@ -232,6 +235,9 @@
     <t>spawn_month</t>
   </si>
   <si>
+    <t>R_sexr</t>
+  </si>
+  <si>
     <t>minage</t>
   </si>
   <si>
@@ -358,9 +364,21 @@
     <t>Age transition matrix (e.g. growth trajectory) used to convert age to length for length comp data. Can have multiple matrices for a species specified by Age_transition_index.</t>
   </si>
   <si>
+    <t>est_sex_ratio</t>
+  </si>
+  <si>
+    <t>sex_ratio_sigma</t>
+  </si>
+  <si>
     <t>estDynamics</t>
   </si>
   <si>
+    <t>proj_F</t>
+  </si>
+  <si>
+    <t>Unused</t>
+  </si>
+  <si>
     <t>Control</t>
   </si>
   <si>
@@ -376,6 +394,9 @@
     <t>Numeric: spawning month of the population to adjust the numbers at spawning</t>
   </si>
   <si>
+    <t>Numeric: percent of recruitment that is female (ignored if nsex = 1)</t>
+  </si>
+  <si>
     <t>Integer: end year of the hindcast</t>
   </si>
   <si>
@@ -409,6 +430,12 @@
     <t>Numeric: other food in the ecosystem for each species (kg)</t>
   </si>
   <si>
+    <t>Integer: is sex ration F/(M+F) to be included in the likelihood (assumed normal); 0 = no, 1 = use annual average across ages (uses 2nd age in propF data), 2 = age, and year specific (TBD)</t>
+  </si>
+  <si>
+    <t>Numeric: initial value or fixed value for sd of normal likelihood for sex ration. Not yet able to estimate.</t>
+  </si>
+  <si>
     <t>Integer: switch to estimate or fix numbers-at-age: 0 = estimate dynamics, 1 = use input numbers-at-age in NbyageFixed, 2 = multiply input numbers-at-age (NbyageFixed) by a single scaling coefficient, 3 = multiply input numbers-at-age (NbyageFixed) by age specific scaling coefficient.</t>
   </si>
   <si>
@@ -458,9 +485,6 @@
   </si>
   <si>
     <t>Age at which selectivity = 1. If NA, it will not normalize selectivity. If &lt; 0, will normalize selectivity by the max.</t>
-  </si>
-  <si>
-    <t>stom_prop_data</t>
   </si>
 </sst>
 </file>
@@ -1281,17 +1305,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G43"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G47"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="119.42578125" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="119.5" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
@@ -1299,7 +1323,7 @@
         <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>27</v>
@@ -1308,824 +1332,880 @@
         <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" t="s">
+        <v>153</v>
+      </c>
+      <c r="G12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" t="s">
+        <v>147</v>
+      </c>
+      <c r="G13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" t="s">
+        <v>133</v>
+      </c>
+      <c r="E14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" t="s">
+        <v>135</v>
+      </c>
+      <c r="E16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>10</v>
+      </c>
+      <c r="B18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" t="s">
+        <v>136</v>
+      </c>
+      <c r="E19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" t="s">
+        <v>137</v>
+      </c>
+      <c r="E20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>149</v>
+      </c>
+      <c r="D22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>15</v>
+      </c>
+      <c r="C23" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G25" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>18</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" t="s">
         <v>113</v>
       </c>
-      <c r="C7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="E26" t="s">
+        <v>76</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G26" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>19</v>
+      </c>
+      <c r="C27" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" t="s">
-        <v>121</v>
-      </c>
-      <c r="E8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="D27" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>20</v>
+      </c>
+      <c r="C28" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" t="s">
-        <v>122</v>
-      </c>
-      <c r="E9" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="D28" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F28" t="s">
+        <v>45</v>
+      </c>
+      <c r="G28" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>21</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G29" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>22</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>23</v>
+      </c>
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" t="s">
+        <v>35</v>
+      </c>
+      <c r="F31" t="s">
+        <v>75</v>
+      </c>
+      <c r="G31" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>24</v>
+      </c>
+      <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>120</v>
+      </c>
+      <c r="C33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" t="s">
+        <v>144</v>
+      </c>
+      <c r="F33" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>26</v>
+      </c>
+      <c r="B34" t="s">
+        <v>120</v>
+      </c>
+      <c r="C34" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" t="s">
+        <v>139</v>
+      </c>
+      <c r="F34" t="s">
         <v>58</v>
       </c>
-      <c r="G9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>113</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" t="s">
-        <v>74</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>113</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" t="s">
-        <v>124</v>
-      </c>
-      <c r="E11" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11" t="s">
-        <v>82</v>
-      </c>
-      <c r="G11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" t="s">
-        <v>125</v>
-      </c>
-      <c r="E12" t="s">
-        <v>74</v>
-      </c>
-      <c r="F12" t="s">
-        <v>144</v>
-      </c>
-      <c r="G12" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C13" t="s">
-        <v>108</v>
-      </c>
-      <c r="D13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F13" t="s">
-        <v>138</v>
-      </c>
-      <c r="G13" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>113</v>
-      </c>
-      <c r="C14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15">
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>27</v>
+      </c>
+      <c r="B35" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" t="s">
         <v>15</v>
       </c>
-      <c r="B15" t="s">
-        <v>113</v>
-      </c>
-      <c r="C15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" t="s">
-        <v>128</v>
-      </c>
-      <c r="E15" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="D35" t="s">
+        <v>140</v>
+      </c>
+      <c r="F35" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>28</v>
+      </c>
+      <c r="B36" t="s">
+        <v>120</v>
+      </c>
+      <c r="C36" t="s">
         <v>16</v>
       </c>
-      <c r="B16" t="s">
-        <v>113</v>
-      </c>
-      <c r="C16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" t="s">
-        <v>129</v>
-      </c>
-      <c r="E16" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" t="s">
-        <v>109</v>
-      </c>
-      <c r="G16" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>13</v>
-      </c>
-      <c r="C17" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" t="s">
-        <v>64</v>
-      </c>
-      <c r="G17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>14</v>
-      </c>
-      <c r="C18" t="s">
-        <v>140</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="D36" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37">
         <v>29</v>
       </c>
-      <c r="E18" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G18" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>15</v>
-      </c>
-      <c r="C19" t="s">
-        <v>143</v>
-      </c>
-      <c r="D19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" t="s">
-        <v>74</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>16</v>
-      </c>
-      <c r="C20" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" t="s">
-        <v>74</v>
-      </c>
-      <c r="F20" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="B37" t="s">
+        <v>120</v>
+      </c>
+      <c r="C37" t="s">
         <v>17</v>
       </c>
-      <c r="C21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D21" t="s">
-        <v>102</v>
-      </c>
-      <c r="E21" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="D37" t="s">
+        <v>37</v>
+      </c>
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>30</v>
+      </c>
+      <c r="B38" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" t="s">
         <v>18</v>
       </c>
-      <c r="C22" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" t="s">
-        <v>111</v>
-      </c>
-      <c r="E22" t="s">
-        <v>74</v>
-      </c>
-      <c r="F22" t="s">
-        <v>95</v>
-      </c>
-      <c r="G22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="D38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>31</v>
+      </c>
+      <c r="B39" t="s">
+        <v>120</v>
+      </c>
+      <c r="C39" t="s">
         <v>19</v>
-      </c>
-      <c r="C23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G23" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>20</v>
-      </c>
-      <c r="C24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" t="s">
-        <v>74</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G24" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>21</v>
-      </c>
-      <c r="C25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" t="s">
-        <v>33</v>
-      </c>
-      <c r="E25" t="s">
-        <v>74</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G25" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>22</v>
-      </c>
-      <c r="C26" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" t="s">
-        <v>34</v>
-      </c>
-      <c r="E26" t="s">
-        <v>74</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G26" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>23</v>
-      </c>
-      <c r="C27" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G27" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>24</v>
-      </c>
-      <c r="C28" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" t="s">
-        <v>74</v>
-      </c>
-      <c r="F28" t="s">
-        <v>44</v>
-      </c>
-      <c r="G28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>25</v>
-      </c>
-      <c r="B29" t="s">
-        <v>114</v>
-      </c>
-      <c r="C29" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" t="s">
-        <v>135</v>
-      </c>
-      <c r="E29" t="s">
-        <v>74</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G29" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>26</v>
-      </c>
-      <c r="B30" t="s">
-        <v>114</v>
-      </c>
-      <c r="C30" t="s">
-        <v>98</v>
-      </c>
-      <c r="D30" t="s">
-        <v>130</v>
-      </c>
-      <c r="E30" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>27</v>
-      </c>
-      <c r="B31" t="s">
-        <v>114</v>
-      </c>
-      <c r="C31" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F31" t="s">
-        <v>73</v>
-      </c>
-      <c r="G31" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>28</v>
-      </c>
-      <c r="B32" t="s">
-        <v>114</v>
-      </c>
-      <c r="C32" t="s">
-        <v>16</v>
-      </c>
-      <c r="D32" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>29</v>
-      </c>
-      <c r="B33" t="s">
-        <v>114</v>
-      </c>
-      <c r="C33" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33" t="s">
-        <v>37</v>
-      </c>
-      <c r="F33" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>30</v>
-      </c>
-      <c r="B34" t="s">
-        <v>114</v>
-      </c>
-      <c r="C34" t="s">
-        <v>18</v>
-      </c>
-      <c r="D34" t="s">
-        <v>38</v>
-      </c>
-      <c r="F34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>31</v>
-      </c>
-      <c r="B35" t="s">
-        <v>114</v>
-      </c>
-      <c r="C35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" t="s">
-        <v>39</v>
-      </c>
-      <c r="F35" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>32</v>
-      </c>
-      <c r="B36" t="s">
-        <v>114</v>
-      </c>
-      <c r="C36" t="s">
-        <v>20</v>
-      </c>
-      <c r="D36" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>33</v>
-      </c>
-      <c r="B37" t="s">
-        <v>114</v>
-      </c>
-      <c r="C37" t="s">
-        <v>21</v>
-      </c>
-      <c r="D37" t="s">
-        <v>39</v>
-      </c>
-      <c r="F37" s="2"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>34</v>
-      </c>
-      <c r="B38" t="s">
-        <v>114</v>
-      </c>
-      <c r="C38" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>35</v>
-      </c>
-      <c r="B39" t="s">
-        <v>114</v>
-      </c>
-      <c r="C39" t="s">
-        <v>23</v>
       </c>
       <c r="D39" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C40" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D40" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41">
+        <v>33</v>
+      </c>
+      <c r="B41" t="s">
+        <v>120</v>
+      </c>
+      <c r="C41" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>34</v>
+      </c>
+      <c r="B42" t="s">
+        <v>120</v>
+      </c>
+      <c r="C42" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>35</v>
+      </c>
+      <c r="B43" t="s">
+        <v>120</v>
+      </c>
+      <c r="C43" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>36</v>
+      </c>
+      <c r="B44" t="s">
+        <v>120</v>
+      </c>
+      <c r="C44" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45">
         <v>37</v>
       </c>
-      <c r="C41" t="s">
-        <v>99</v>
-      </c>
-      <c r="D41" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42">
+      <c r="C45" t="s">
+        <v>101</v>
+      </c>
+      <c r="D45" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46">
         <v>38</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C46" t="s">
         <v>25</v>
       </c>
-      <c r="D42" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43">
+      <c r="D46" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47">
         <v>39</v>
       </c>
-      <c r="C43" t="s">
-        <v>146</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="C47" t="s">
         <v>40</v>
+      </c>
+      <c r="D47" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grant.adams\GitHub\Rceattle\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0872DD-B699-47F9-A158-D628F2BC7191}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF88D93E-E48A-4C47-950E-A281CB2CA96D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="765" windowWidth="34560" windowHeight="21585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="141">
   <si>
     <t>nspp</t>
   </si>
@@ -49,21 +49,9 @@
     <t>age_error</t>
   </si>
   <si>
-    <t>wt</t>
-  </si>
-  <si>
-    <t>pmature</t>
-  </si>
-  <si>
-    <t>propF</t>
-  </si>
-  <si>
     <t>M1_base</t>
   </si>
   <si>
-    <t>aLW</t>
-  </si>
-  <si>
     <t>Ceq</t>
   </si>
   <si>
@@ -97,30 +85,15 @@
     <t>CK4</t>
   </si>
   <si>
-    <t>Pyrs</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
     <t>Total catch in weight (kg) or numbers data</t>
   </si>
   <si>
-    <t>Survey index in weight (kg) or numbers data</t>
-  </si>
-  <si>
     <t>Aging error matrices. Can have only one per species.</t>
   </si>
   <si>
-    <t>Weight-at-age (wt) to use for calculation of derived quantities (SSB, Consumption/Ration, Suitability, Total Catch, Survey Biomass, etc). Can have multiple weight-at-age data-sets for each species, but must be full for all years of the hindcast.</t>
-  </si>
-  <si>
-    <t>Sheet location</t>
-  </si>
-  <si>
     <t>Maturity-at-age for each species</t>
   </si>
   <si>
@@ -130,9 +103,6 @@
     <t>Residual natural mortality for each species</t>
   </si>
   <si>
-    <t>Parameters for weight-at-length power function for each species. . Used when estimating time-variant length-based gamma suitability (suitMode = 2) or time-variant length-based lognormal suitability (suitMode = 5)</t>
-  </si>
-  <si>
     <t>Intercept of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
   </si>
   <si>
@@ -154,9 +124,6 @@
     <t>Nselages</t>
   </si>
   <si>
-    <t>Catch_units</t>
-  </si>
-  <si>
     <t>Weight_index</t>
   </si>
   <si>
@@ -166,33 +133,15 @@
     <t>Species number</t>
   </si>
   <si>
-    <t>Units used for survey: 1 = kg; 2 = numbers</t>
-  </si>
-  <si>
-    <t>Weight-at-age (wt) index to use for calculation of derived quantities</t>
-  </si>
-  <si>
     <t>Starting value or fixed value for catchability</t>
   </si>
   <si>
-    <t>Column names</t>
-  </si>
-  <si>
     <t>NOTE: Most objects are ordered by species code if not specified</t>
   </si>
   <si>
     <t>weight1_Numbers2</t>
   </si>
   <si>
-    <t>Is the observation in weight (kg) set as 1, if the observation is in numbers caught, set as 2</t>
-  </si>
-  <si>
-    <t>Starting value to be used if Estimate_sigma_index = 1</t>
-  </si>
-  <si>
-    <t>Starting value to be used if Estimate_sigma_catch = 1</t>
-  </si>
-  <si>
     <t>NOTE: Lengths are index 1 through nlenths</t>
   </si>
   <si>
@@ -208,9 +157,6 @@
     <t>Q_sd_prior</t>
   </si>
   <si>
-    <t>The sd to use for the random walk of time varying q if set to 1</t>
-  </si>
-  <si>
     <t>Selectivity_index</t>
   </si>
   <si>
@@ -256,30 +202,15 @@
     <t>Name of survey or fishery</t>
   </si>
   <si>
-    <t>Index of survey/fishery ACROSS species</t>
-  </si>
-  <si>
     <t>Fleet_type</t>
   </si>
   <si>
-    <t>0 = Do not estimate; 1 = Fishery; 2 = Survey</t>
-  </si>
-  <si>
-    <t>The sd to use for the random walk of time varying selectivity if set to 1. If selectivity is set to type = 2 (non-parametric) this value will be the 2nd penalty on selectivity.</t>
-  </si>
-  <si>
     <t>Age_first_selected</t>
   </si>
   <si>
     <t>Age at which selectivity is non-zero</t>
   </si>
   <si>
-    <t>Survey_sd_prior</t>
-  </si>
-  <si>
-    <t>Estimate_survey_sd</t>
-  </si>
-  <si>
     <t>Estimate_catch_sd</t>
   </si>
   <si>
@@ -289,18 +220,12 @@
     <t>Comp_weights</t>
   </si>
   <si>
-    <t>Composition weights to be used for multinomial likelihood. These are multiplied. After running model, these will update to McAllister &amp; Ianelli 1997 weights using the harmonic mean.</t>
-  </si>
-  <si>
     <t>proj_F_prop</t>
   </si>
   <si>
     <t>The proportion of future fishing mortality assigned to this fleet</t>
   </si>
   <si>
-    <t>sex codes: 0=combined; 1=use female only; 2=use male only; 3 = joint female and male</t>
-  </si>
-  <si>
     <t>Survey and fishery data specifications</t>
   </si>
   <si>
@@ -310,21 +235,12 @@
     <t>Time_varying_q_sd_prior</t>
   </si>
   <si>
-    <t>Variance of q prior: dnorm (log_q, log_q_prior, q_sd_prior)</t>
-  </si>
-  <si>
-    <t>Estimate catchability? (0 = fixed at prior; - 1 = Estimate single parameter; - 2 = Estimate single parameter with prior; - 3 = Estimate analytical q  from Ludwig and Walters 1994;  - 4 = Estimate power equation; - 5 - Linear equation log(q_y) = q_mu + beta * index_y)</t>
-  </si>
-  <si>
     <t>Cindex</t>
   </si>
   <si>
     <t>env_data</t>
   </si>
   <si>
-    <t>Environmental indices such as bottom temperature data to incorporate into ration equation specificed by Ceq and Cindex. Also used to drive catchability if Estimate_q = 5. Will use the mean for missing years. Temperature should be in celcius.</t>
-  </si>
-  <si>
     <t>emp_sel</t>
   </si>
   <si>
@@ -337,12 +253,6 @@
     <t>Survey/fishery age or length composition data. Note if sex is 3, put female composition data then male composition data (similar to SS).</t>
   </si>
   <si>
-    <t>Object name</t>
-  </si>
-  <si>
-    <t>index to use if selectivities of different surveys are to be the same</t>
-  </si>
-  <si>
     <t>Annual relative foraging rate by age. Multiplied by pvalue and fday to scale maximum consumption to the number of days in a year that foraging occurs.</t>
   </si>
   <si>
@@ -352,12 +262,6 @@
     <t>Age_transition_index</t>
   </si>
   <si>
-    <t>Age transition matrix (e.g. growth trajectory) index to use for derived quantities to convert age to length</t>
-  </si>
-  <si>
-    <t>Age transition matrix (e.g. growth trajectory) used to convert age to length for length comp data. Can have multiple matrices for a species specified by Age_transition_index.</t>
-  </si>
-  <si>
     <t>estDynamics</t>
   </si>
   <si>
@@ -385,33 +289,15 @@
     <t>Integer: number of species included in CEATTLE</t>
   </si>
   <si>
-    <t>Integer: number of ages of each species included in the hindcast</t>
-  </si>
-  <si>
     <t>Numeric: minimum age for each population (i.e.does recruitment correspond to age 0, 1, 2?)</t>
   </si>
   <si>
-    <t>Integer: number of lengths of each species included in the hindcast</t>
-  </si>
-  <si>
-    <t>Integer: weight-at-age (wt) index to use for calculation of each species population derived quantities (SSB, Consumption/Ration, Suitability, etc)</t>
-  </si>
-  <si>
-    <t>Integer: weight-at-age (wt) index to use for calculation of each species spawning biomass</t>
-  </si>
-  <si>
-    <t>Integer: age transition matrix (e.g. growth trajectory) index to use for derived quantities of the population to convert age to length (also used in length-based predation estimation)</t>
-  </si>
-  <si>
     <t>Numeric: fixed or initial value of standard deviation for recruitment deviates</t>
   </si>
   <si>
     <t>Numeric: other food in the ecosystem for each species (kg)</t>
   </si>
   <si>
-    <t>Integer: switch to estimate or fix numbers-at-age: 0 = estimate dynamics, 1 = use input numbers-at-age in NbyageFixed, 2 = multiply input numbers-at-age (NbyageFixed) by a single scaling coefficient, 3 = multiply input numbers-at-age (NbyageFixed) by age specific scaling coefficient.</t>
-  </si>
-  <si>
     <t>Integer: which environmental index in env_data to use to drive bioenergetics</t>
   </si>
   <si>
@@ -421,46 +307,191 @@
     <t>Numeric: number of foraging days per year for each species</t>
   </si>
   <si>
-    <t>Selectivity to use for the species: 0 = empirical selectivity provided in srv_emp_sel; 1 = logistic selectivity; 2 = non-parametric selecitivty sensu Ianelli et al 2018; 3 = double logistic; 4 = descending logistic; 5 = non-parametric selectivity sensu Taylor et al 2014 (Hake)</t>
-  </si>
-  <si>
     <t>Number of ages to estimate non-parametric selectivity for Selectivity = 2 &amp; 5. Not used otherwise</t>
   </si>
   <si>
-    <t>Integer: switch for which bioenergetics equation to use for each species for ft to scale max consumtion: 1 = Exponential (Stewart et al 1983), 2 = Temperature-dependendence for warm-water species (Kitchell et al 1977; sensu Holsman et al 2015), 3 = temperature dependence for cool and cold-water species (Thornton and Lessem 1979); 4 = 1 for direct input of consumption in Pyrs  where consumption at age = Wt * Pyrs (CA set to 1, fday set to 1, CB set to 0)</t>
-  </si>
-  <si>
-    <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity,  descending logistic , or non-parametric (Selectivity = 5). 0 = no, 1 = penalized deviates given sel_sd_prior, 3 = time blocks with no penality, 4 = random walk following Dorn, 5 = random walk on ascending portion of double logistic only. If selectivity is set to type = 2 (non-parametric) this value will be the 1st penalty on selectivity. "random_sel" treats random deviates and random walk parameters as random effects.</t>
-  </si>
-  <si>
-    <t>Wether a time-varying q should be estimated. 0 = no, 1 = penalized deviate, 3 = time blocks with no penalty; 4 = random walk from mean following Dorn 2018 (dnorm(q_y - q_y-1, 0, sigma). If Estimate_q = 5, this determines the environmental index to be used in the equation log(q_y) = q_mu + beta * index_y. If "random_q" is selected in fit_mod, penalized deviates (1) and random walk parameters (4) will be treated as random effects.</t>
-  </si>
-  <si>
     <t>Comp_loglike</t>
   </si>
   <si>
-    <t>Composition data distribution (0 = multinomial; 1 = dirichlet-multinomial)</t>
-  </si>
-  <si>
     <t>index_data</t>
   </si>
   <si>
-    <t>Estimate survey variance (0 = use CV from index_data, 1 = yes, 2 = analytically estimate following (Ludwig and Walters 1994)</t>
-  </si>
-  <si>
-    <t>Estimate fishery variance (0 = use CV from index_data, 1 = yes, 2 = analytically estimate following (Ludwig and Walters 1994)</t>
-  </si>
-  <si>
     <t>catch_data</t>
   </si>
   <si>
     <t>Age_max_selected</t>
   </si>
   <si>
-    <t>Age at which selectivity = 1. If NA, it will not normalize selectivity. If &lt; 0, will normalize selectivity by the max.</t>
-  </si>
-  <si>
-    <t>stom_prop_data</t>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>maturity</t>
+  </si>
+  <si>
+    <t>sex_ratio</t>
+  </si>
+  <si>
+    <t>diet_data</t>
+  </si>
+  <si>
+    <t>ration_data</t>
+  </si>
+  <si>
+    <t>Integer: number of ages of each species</t>
+  </si>
+  <si>
+    <t>Integer: number of lengths of each species</t>
+  </si>
+  <si>
+    <t>Integer: weight index for calculating  biomass, consumption/ration, and suitability for each species</t>
+  </si>
+  <si>
+    <t>Integer: weight index for calculating  spawning biomass for each species</t>
+  </si>
+  <si>
+    <t>Integer: age transition matrix (e.g. growth trajectory) index to use deriving length-based predation</t>
+  </si>
+  <si>
+    <t>Index of survey/fishery (does not restart for each species)</t>
+  </si>
+  <si>
+    <t>Index to match selectivities (otherwise, same as fleet_code)</t>
+  </si>
+  <si>
+    <t>Integer: switch to estimate or fix numbers-at-age: 
+0 = estimate dynamics
+1 = use input numbers-at-age in NbyageFixed, 
+2 = multiply input numbers-at-age (NbyageFixed) by a single scaling coefficient
+3 = multiply input numbers-at-age (NbyageFixed) by age specific scaling coefficient.</t>
+  </si>
+  <si>
+    <t>0 = Do not estimate (fixes all parameters for this fleet to initial values)
+1 = Fishery
+2 = Survey</t>
+  </si>
+  <si>
+    <t>0 = empirical selectivity provided in srv_emp_sel
+1 = logistic selectivity
+2 = non-parametric selecitivty sensu Ianelli et al 2018
+3 = double logistic
+4 = descending logistic
+5 = non-parametric selectivity sensu Taylor et al 2014 (Hake)</t>
+  </si>
+  <si>
+    <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity,  descending logistic , or non-parametric (Selectivity = 5). 
+0 = no
+1 = penalized deviates given sel_sd_prior (or random effects if "random_sel" is selected in "fit_mod"), 
+3 = time blocks with no penality 
+4 = random walk following Dorn
+5 = random walk on ascending portion of double logistic only. 
+If selectivity is set to type = 2 (non-parametric) this value will be the 1st penalty on selectivity.</t>
+  </si>
+  <si>
+    <t>The sd to use for the random walk of time varying selectivity if set to 1. 
+If selectivity is set to type = 2 (non-parametric) this value will be the 2nd penalty on selectivity.</t>
+  </si>
+  <si>
+    <t>Age at which selectivity = 1. 
+If NA, it will not normalize selectivity. 
+If &lt; 0, will normalize selectivity by the max.</t>
+  </si>
+  <si>
+    <t>Composition data distribution:
+-1 = AFSC multinomial
+0 = full multinomial
+1 = dirichlet-multinomial</t>
+  </si>
+  <si>
+    <t>1 = catch/index is weight (kg) the observation 
+2 = catch/index is in numbers</t>
+  </si>
+  <si>
+    <t>Weight index to use for calculation of derived quantities</t>
+  </si>
+  <si>
+    <t>Age transition matrix (e.g. growth trajectory) index to used convert age to length</t>
+  </si>
+  <si>
+    <t>0 = fixed at "Q_sd_prior" 
+1 = Estimate as free parameter; 
+2 = Estimate as free parameter with normal prior of N(Q_prior, Q_sd_prior)
+3 = Estimate analytically following Ludwig and Walters 1994
+4 = Estimate power equation (NOT YET IMPLEMENTED)
+5 = Linear equation log(q_y) = q_mu + beta * index_y)
+6 = AR1 random deviates fit to environmental index (sensu Rogers et al 2024; 10.1093/icesjms/fsae005)</t>
+  </si>
+  <si>
+    <t>Standard deviation for q prior</t>
+  </si>
+  <si>
+    <t>0 = no
+1 = penalized deviate or random effect 
+3 = time blocks with no penalty
+4 = random walk from mean following Dorn 2018 (dnorm(q_y - q_y-1, 0, sigma)
+If "Estimate_q" = 5, this determines the environmental index to be used in the equation log(q_y) = q_mu + beta * index_y
+If "random_q" is selected in fit_mod, penalized deviates (1) and random walk parameters (4) will be treated as random effects</t>
+  </si>
+  <si>
+    <t>starting or fixed sd to use for the random walk of time varying q if set to 1</t>
+  </si>
+  <si>
+    <t>Estimate_index_sd</t>
+  </si>
+  <si>
+    <t>Index_sd_prior</t>
+  </si>
+  <si>
+    <t>Starting value to be used if "Estimate_index_sd" = 1</t>
+  </si>
+  <si>
+    <t>0 = use input "Log_sd" from catch_data
+1 = estimate as free parameter
+2 = estimate analytically following Ludwig and Walters (1994)</t>
+  </si>
+  <si>
+    <t>0 = use input "Log_sd" from index_data
+1 = estimate as free parameter
+2 = estimate analytically following Ludwig and Walters (1994)</t>
+  </si>
+  <si>
+    <t>Starting value to be used if Estimate_catch_sd = 1</t>
+  </si>
+  <si>
+    <t>Composition weights for composition likelihood. 
+After running model, these will update to McAllister &amp; Ianelli 1997 weights using the harmonic mean.</t>
+  </si>
+  <si>
+    <t>Survey index or fishery indices in weight (kg) or numbers</t>
+  </si>
+  <si>
+    <t>Age transition matrix (e.g. growth trajectory) used to convert age to length for length comp data. 
+Can have multiple matrices for a species specified by Age_transition_index.</t>
+  </si>
+  <si>
+    <t>Time-invariant or -varying empirical weight-at-age for calculation of derived quantities (SSB, Consumption/Ration, Suitability, Total Catch, Survey Biomass, etc). 
+Can have multiple weight-at-age data-sets for each species.</t>
+  </si>
+  <si>
+    <t>Integer: switch for which bioenergetics equation to use for each species for ft to scale max consumtion: 
+1 = Exponential (Stewart et al 1983)
+2 = Temperature-dependendence for warm-water species (Kitchell et al 1977; sensu Holsman et al 2015)
+3 = temperature dependence for cool and cold-water species (Thornton and Lessem 1979)
+4 = for direct input of consumption in Pyrs  where consumption at age = Wt * Pyrs (CA set to 1, fday set to 1, CB set to 0)</t>
+  </si>
+  <si>
+    <t>Environmental indices such as bottom temperature data to incorporate into ration equation specificed by Ceq and Cindex. Also used to drive catchability if Estimate_q = 5 or 6. Will use the mean for missing years. Temperature should be in celcius.</t>
+  </si>
+  <si>
+    <t>0 = combined
+1 = use female only 
+2 = use male only
+3 = joint female and male</t>
+  </si>
+  <si>
+    <t>Column/row name</t>
+  </si>
+  <si>
+    <t>Sheet name</t>
   </si>
 </sst>
 </file>
@@ -951,7 +982,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -959,6 +990,24 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1281,854 +1330,771 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="119.42578125" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="119.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>95</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C40" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C46" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C47" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="56" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A56" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C57" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G2" t="s">
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C66" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C67" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C68" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C69" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" t="s">
-        <v>121</v>
-      </c>
-      <c r="E8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" t="s">
-        <v>122</v>
-      </c>
-      <c r="E9" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>113</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" t="s">
-        <v>74</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>113</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" t="s">
-        <v>124</v>
-      </c>
-      <c r="E11" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11" t="s">
-        <v>82</v>
-      </c>
-      <c r="G11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" t="s">
-        <v>125</v>
-      </c>
-      <c r="E12" t="s">
-        <v>74</v>
-      </c>
-      <c r="F12" t="s">
-        <v>144</v>
-      </c>
-      <c r="G12" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C13" t="s">
-        <v>108</v>
-      </c>
-      <c r="D13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F13" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C70" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A73" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B73" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="G13" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>113</v>
-      </c>
-      <c r="C14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>113</v>
-      </c>
-      <c r="C15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" t="s">
-        <v>128</v>
-      </c>
-      <c r="E15" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>113</v>
-      </c>
-      <c r="C16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" t="s">
-        <v>129</v>
-      </c>
-      <c r="E16" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" t="s">
-        <v>109</v>
-      </c>
-      <c r="G16" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>13</v>
-      </c>
-      <c r="C17" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" t="s">
-        <v>64</v>
-      </c>
-      <c r="G17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>14</v>
-      </c>
-      <c r="C18" t="s">
-        <v>140</v>
-      </c>
-      <c r="D18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G18" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>15</v>
-      </c>
-      <c r="C19" t="s">
-        <v>143</v>
-      </c>
-      <c r="D19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" t="s">
-        <v>74</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>16</v>
-      </c>
-      <c r="C20" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" t="s">
-        <v>74</v>
-      </c>
-      <c r="F20" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>17</v>
-      </c>
-      <c r="C21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D21" t="s">
-        <v>102</v>
-      </c>
-      <c r="E21" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>18</v>
-      </c>
-      <c r="C22" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" t="s">
-        <v>111</v>
-      </c>
-      <c r="E22" t="s">
-        <v>74</v>
-      </c>
-      <c r="F22" t="s">
-        <v>95</v>
-      </c>
-      <c r="G22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>19</v>
-      </c>
-      <c r="C23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G23" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>20</v>
-      </c>
-      <c r="C24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" t="s">
-        <v>74</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G24" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>21</v>
-      </c>
-      <c r="C25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" t="s">
-        <v>33</v>
-      </c>
-      <c r="E25" t="s">
-        <v>74</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G25" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>22</v>
-      </c>
-      <c r="C26" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" t="s">
-        <v>34</v>
-      </c>
-      <c r="E26" t="s">
-        <v>74</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G26" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>23</v>
-      </c>
-      <c r="C27" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G27" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>24</v>
-      </c>
-      <c r="C28" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" t="s">
-        <v>74</v>
-      </c>
-      <c r="F28" t="s">
-        <v>44</v>
-      </c>
-      <c r="G28" t="s">
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="6" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>25</v>
-      </c>
-      <c r="B29" t="s">
-        <v>114</v>
-      </c>
-      <c r="C29" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" t="s">
-        <v>135</v>
-      </c>
-      <c r="E29" t="s">
-        <v>74</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G29" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>26</v>
-      </c>
-      <c r="B30" t="s">
-        <v>114</v>
-      </c>
-      <c r="C30" t="s">
-        <v>98</v>
-      </c>
-      <c r="D30" t="s">
-        <v>130</v>
-      </c>
-      <c r="E30" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>27</v>
-      </c>
-      <c r="B31" t="s">
-        <v>114</v>
-      </c>
-      <c r="C31" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F31" t="s">
-        <v>73</v>
-      </c>
-      <c r="G31" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>28</v>
-      </c>
-      <c r="B32" t="s">
-        <v>114</v>
-      </c>
-      <c r="C32" t="s">
-        <v>16</v>
-      </c>
-      <c r="D32" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>29</v>
-      </c>
-      <c r="B33" t="s">
-        <v>114</v>
-      </c>
-      <c r="C33" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33" t="s">
-        <v>37</v>
-      </c>
-      <c r="F33" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>30</v>
-      </c>
-      <c r="B34" t="s">
-        <v>114</v>
-      </c>
-      <c r="C34" t="s">
-        <v>18</v>
-      </c>
-      <c r="D34" t="s">
-        <v>38</v>
-      </c>
-      <c r="F34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>31</v>
-      </c>
-      <c r="B35" t="s">
-        <v>114</v>
-      </c>
-      <c r="C35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" t="s">
-        <v>39</v>
-      </c>
-      <c r="F35" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>32</v>
-      </c>
-      <c r="B36" t="s">
-        <v>114</v>
-      </c>
-      <c r="C36" t="s">
-        <v>20</v>
-      </c>
-      <c r="D36" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>33</v>
-      </c>
-      <c r="B37" t="s">
-        <v>114</v>
-      </c>
-      <c r="C37" t="s">
-        <v>21</v>
-      </c>
-      <c r="D37" t="s">
-        <v>39</v>
-      </c>
-      <c r="F37" s="2"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>34</v>
-      </c>
-      <c r="B38" t="s">
-        <v>114</v>
-      </c>
-      <c r="C38" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>35</v>
-      </c>
-      <c r="B39" t="s">
-        <v>114</v>
-      </c>
-      <c r="C39" t="s">
-        <v>23</v>
-      </c>
-      <c r="D39" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>36</v>
-      </c>
-      <c r="B40" t="s">
-        <v>114</v>
-      </c>
-      <c r="C40" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>37</v>
-      </c>
-      <c r="C41" t="s">
-        <v>99</v>
-      </c>
-      <c r="D41" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>38</v>
-      </c>
-      <c r="C42" t="s">
-        <v>25</v>
-      </c>
-      <c r="D42" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>39</v>
-      </c>
-      <c r="C43" t="s">
-        <v>146</v>
-      </c>
-      <c r="D43" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grant.adams\GitHub\Rceattle\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF88D93E-E48A-4C47-950E-A281CB2CA96D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BD06EC-C598-4F3D-9E6F-C40129725B64}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="765" windowWidth="34560" windowHeight="21585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="143">
   <si>
     <t>nspp</t>
   </si>
@@ -492,6 +492,12 @@
   </si>
   <si>
     <t>Sheet name</t>
+  </si>
+  <si>
+    <t>Age_max_selected_upper</t>
+  </si>
+  <si>
+    <t>Upper age for selectivity normalization (default = NA). If NA, does not use the age range, If not NA, uses mean selectivity between `Age_max_selected` and `Age_max_selected_upper`</t>
   </si>
 </sst>
 </file>
@@ -1330,7 +1336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="6" bestFit="1" customWidth="1"/>
@@ -1655,39 +1661,40 @@
       <c r="C28" s="4" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>56</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C30" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" s="7" t="s">
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C31" s="4" t="s">
         <v>119</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1695,10 +1702,10 @@
         <v>56</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1706,234 +1713,234 @@
         <v>56</v>
       </c>
       <c r="B33" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C34" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="6" t="s">
+    <row r="35" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C35" s="4" t="s">
         <v>122</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C35" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C37" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" s="6" t="s">
+    <row r="38" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C38" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E37" s="2"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="6" t="s">
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C39" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B39" s="8" t="s">
+    <row r="40" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C40" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B40" s="8" t="s">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B41" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C41" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B41" s="8" t="s">
+    <row r="42" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C42" s="4" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B42" s="8" t="s">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C43" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B43" s="8" t="s">
+    <row r="44" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B44" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C44" s="4" t="s">
         <v>132</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C44" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>97</v>
+        <v>56</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="C45" t="s">
-        <v>133</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C46" t="s">
-        <v>22</v>
+        <v>133</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C47" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C49" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
+    <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C50" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C51" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
+    <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C52" s="4" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C52" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C54" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C55" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>82</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C57" t="s">
-        <v>92</v>
+        <v>10</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1941,10 +1948,10 @@
         <v>82</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="C58" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1952,10 +1959,10 @@
         <v>82</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1963,10 +1970,10 @@
         <v>82</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C60" t="s">
-        <v>27</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1974,10 +1981,10 @@
         <v>82</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1985,10 +1992,10 @@
         <v>82</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C62" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1996,7 +2003,7 @@
         <v>82</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C63" t="s">
         <v>29</v>
@@ -2007,7 +2014,7 @@
         <v>82</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C64" t="s">
         <v>29</v>
@@ -2018,7 +2025,7 @@
         <v>82</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C65" t="s">
         <v>29</v>
@@ -2029,7 +2036,7 @@
         <v>82</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C66" t="s">
         <v>29</v>
@@ -2040,7 +2047,7 @@
         <v>82</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C67" t="s">
         <v>29</v>
@@ -2048,48 +2055,59 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>72</v>
+        <v>82</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="C68" t="s">
-        <v>137</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="C69" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C70" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C71" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A73" s="6" t="s">
+    <row r="74" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A74" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B74" s="9" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="6" t="s">
         <v>48</v>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grant.adams\GitHub\Rceattle\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BD06EC-C598-4F3D-9E6F-C40129725B64}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8189E839-E1F0-4A38-84B5-E0BF69DEF48F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="765" windowWidth="34560" windowHeight="21585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="145">
   <si>
     <t>nspp</t>
   </si>
@@ -110,9 +110,6 @@
   </si>
   <si>
     <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
-  </si>
-  <si>
-    <t>Stomach proportion by weight for each predator, prey, predator age, prey age combination. Can also be year specific by including the column, "Year"</t>
   </si>
   <si>
     <t>Species</t>
@@ -461,9 +458,6 @@
 After running model, these will update to McAllister &amp; Ianelli 1997 weights using the harmonic mean.</t>
   </si>
   <si>
-    <t>Survey index or fishery indices in weight (kg) or numbers</t>
-  </si>
-  <si>
     <t>Age transition matrix (e.g. growth trajectory) used to convert age to length for length comp data. 
 Can have multiple matrices for a species specified by Age_transition_index.</t>
   </si>
@@ -498,6 +492,24 @@
   </si>
   <si>
     <t>Upper age for selectivity normalization (default = NA). If NA, does not use the age range, If not NA, uses mean selectivity between `Age_max_selected` and `Age_max_selected_upper`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Survey index or fishery indices in weight (kg) or numbers. </t>
+  </si>
+  <si>
+    <t>NOTE: For catch, index, and comp data, if "Year" is negative, it will predict for that year, but not include the data in the likelihood.</t>
+  </si>
+  <si>
+    <t>NOTE: For emp_sel, weight, and ration_data, if "Year" == 0, those data will be used for all years</t>
+  </si>
+  <si>
+    <t>Stomach proportion by weight for each predator, prey, predator age, prey age combination. Multiple diet-data formats can be included:
+1) If Pred_age &gt;= 0 and Prey_age &gt;= 0, data is assumed to be  diet proportion of prey-at-age/sex in predator-at-age/sex. 
+2) If Pred_age &gt;= 0 and Prey_age &lt; 0, data is assumed to be mean diet proportion of prey-spp in predator-at-age/sex (sum across prey ages and sexes)
+3) If Pred_age &lt; 0 and Prey_age &lt; 0, data is assumed to be  mean diet proportion of prey-spp in predator-spp (sum across prey ages/sexes and take mean across predator ages/sexes)
+4) If Pred_age &lt; -500 and Prey_age &lt; 0, data is assumed to be weighted mean diet proportion of prey-spp in predator-spp (sum across prey ages/sexes and take weighted mean across predator ages/sexes). Weights are estimated predators-at-age.
+If "Year = 0", the the diet will be assumed to be the average between "suit_styr" and "suit_endyr". 
+Only diet-data type 1 can be used for MSVPA based suitability</t>
   </si>
 </sst>
 </file>
@@ -1336,7 +1348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="6" bestFit="1" customWidth="1"/>
@@ -1348,10 +1360,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>21</v>
@@ -1362,507 +1374,507 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>57</v>
-      </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" t="s">
         <v>61</v>
-      </c>
-      <c r="C27" t="s">
-        <v>62</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" t="s">
         <v>46</v>
-      </c>
-      <c r="C34" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C39" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B41" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C41" t="s">
         <v>127</v>
-      </c>
-      <c r="C41" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C43" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B45" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" t="s">
         <v>66</v>
-      </c>
-      <c r="C45" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C46" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C47" t="s">
         <v>22</v>
@@ -1870,18 +1882,18 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C48" t="s">
         <v>75</v>
-      </c>
-      <c r="C48" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" t="s">
         <v>73</v>
-      </c>
-      <c r="C49" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -1889,7 +1901,7 @@
         <v>7</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1902,15 +1914,15 @@
     </row>
     <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C53" t="s">
         <v>24</v>
@@ -1918,7 +1930,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C54" t="s">
         <v>25</v>
@@ -1934,51 +1946,51 @@
     </row>
     <row r="57" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C58" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C59" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>13</v>
@@ -1989,7 +2001,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>14</v>
@@ -2000,7 +2012,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>15</v>
@@ -2011,7 +2023,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>16</v>
@@ -2022,7 +2034,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>17</v>
@@ -2033,7 +2045,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>18</v>
@@ -2044,7 +2056,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>19</v>
@@ -2055,7 +2067,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>20</v>
@@ -2066,49 +2078,59 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C69" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C70" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="210" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C71" t="s">
-        <v>30</v>
+        <v>102</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="6" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grant.adams\GitHub\Rceattle\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grantadams/Documents/GitHub/Rceattle/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8189E839-E1F0-4A38-84B5-E0BF69DEF48F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6940EDAC-9B17-BB4F-88DF-FDDECB12F63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="765" windowWidth="34560" windowHeight="21585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data_names" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="151">
   <si>
     <t>nspp</t>
   </si>
@@ -118,9 +118,6 @@
     <t>Selectivity</t>
   </si>
   <si>
-    <t>Nselages</t>
-  </si>
-  <si>
     <t>Weight_index</t>
   </si>
   <si>
@@ -205,9 +202,6 @@
     <t>Age_first_selected</t>
   </si>
   <si>
-    <t>Age at which selectivity is non-zero</t>
-  </si>
-  <si>
     <t>Estimate_catch_sd</t>
   </si>
   <si>
@@ -304,9 +298,6 @@
     <t>Numeric: number of foraging days per year for each species</t>
   </si>
   <si>
-    <t>Number of ages to estimate non-parametric selectivity for Selectivity = 2 &amp; 5. Not used otherwise</t>
-  </si>
-  <si>
     <t>Comp_loglike</t>
   </si>
   <si>
@@ -316,9 +307,6 @@
     <t>catch_data</t>
   </si>
   <si>
-    <t>Age_max_selected</t>
-  </si>
-  <si>
     <t>weight</t>
   </si>
   <si>
@@ -350,9 +338,6 @@
   </si>
   <si>
     <t>Index of survey/fishery (does not restart for each species)</t>
-  </si>
-  <si>
-    <t>Index to match selectivities (otherwise, same as fleet_code)</t>
   </si>
   <si>
     <t>Integer: switch to estimate or fix numbers-at-age: 
@@ -388,11 +373,6 @@
 If selectivity is set to type = 2 (non-parametric) this value will be the 2nd penalty on selectivity.</t>
   </si>
   <si>
-    <t>Age at which selectivity = 1. 
-If NA, it will not normalize selectivity. 
-If &lt; 0, will normalize selectivity by the max.</t>
-  </si>
-  <si>
     <t>Composition data distribution:
 -1 = AFSC multinomial
 0 = full multinomial
@@ -466,13 +446,6 @@
 Can have multiple weight-at-age data-sets for each species.</t>
   </si>
   <si>
-    <t>Integer: switch for which bioenergetics equation to use for each species for ft to scale max consumtion: 
-1 = Exponential (Stewart et al 1983)
-2 = Temperature-dependendence for warm-water species (Kitchell et al 1977; sensu Holsman et al 2015)
-3 = temperature dependence for cool and cold-water species (Thornton and Lessem 1979)
-4 = for direct input of consumption in Pyrs  where consumption at age = Wt * Pyrs (CA set to 1, fday set to 1, CB set to 0)</t>
-  </si>
-  <si>
     <t>Environmental indices such as bottom temperature data to incorporate into ration equation specificed by Ceq and Cindex. Also used to drive catchability if Estimate_q = 5 or 6. Will use the mean for missing years. Temperature should be in celcius.</t>
   </si>
   <si>
@@ -486,12 +459,6 @@
   </si>
   <si>
     <t>Sheet name</t>
-  </si>
-  <si>
-    <t>Age_max_selected_upper</t>
-  </si>
-  <si>
-    <t>Upper age for selectivity normalization (default = NA). If NA, does not use the age range, If not NA, uses mean selectivity between `Age_max_selected` and `Age_max_selected_upper`</t>
   </si>
   <si>
     <t xml:space="preserve">Survey index or fishery indices in weight (kg) or numbers. </t>
@@ -510,6 +477,57 @@
 4) If Pred_age &lt; -500 and Prey_age &lt; 0, data is assumed to be weighted mean diet proportion of prey-spp in predator-spp (sum across prey ages/sexes and take weighted mean across predator ages/sexes). Weights are estimated predators-at-age.
 If "Year = 0", the the diet will be assumed to be the average between "suit_styr" and "suit_endyr". 
 Only diet-data type 1 can be used for MSVPA based suitability</t>
+  </si>
+  <si>
+    <t>alpha_wt_len</t>
+  </si>
+  <si>
+    <t>beta_wt_len</t>
+  </si>
+  <si>
+    <t>Alpha parameter from Weight = alpha * Length ^ beta</t>
+  </si>
+  <si>
+    <t>Beta parameter from Weight = alpha * Length ^ beta</t>
+  </si>
+  <si>
+    <t>Index to mirror selectivities (otherwise, same as fleet_code)</t>
+  </si>
+  <si>
+    <t>N_sel_bins</t>
+  </si>
+  <si>
+    <t>Number of age or length bins to estimate non-parametric selectivity for Selectivity = 2 &amp; 5. Not used otherwise</t>
+  </si>
+  <si>
+    <t>Sel_norm_bin1</t>
+  </si>
+  <si>
+    <t>Sel_norm_bin2</t>
+  </si>
+  <si>
+    <t>Upper age/length bin for selectivity normalization (default = NA). If NA, does not use the age range, If not NA, uses mean selectivity between `Age_max_selected` and `Age_max_selected_upper`</t>
+  </si>
+  <si>
+    <t>Age/length bin at which selectivity = 1. 
+If NA, it will not normalize selectivity. 
+If &lt; 0, will normalize selectivity by the max.</t>
+  </si>
+  <si>
+    <t>Age at which selectivity becomes non-zero</t>
+  </si>
+  <si>
+    <t>Integer: switch for which bioenergetics equation to use for each species for ft to scale max consumtion: 
+1 = Exponential (Stewart et al 1983)
+2 = Temperature-dependendence for warm-water species (Kitchell et al 1977; sensu Holsman et al 2015)
+3 = temperature dependence for cool and cold-water species (Thornton and Lessem 1979)
+4 = for direct input of consumption in Pyrs  where consumption at age = Numbers * Pyrs (CA set to 1, fday set to 1, CB set to 0)</t>
+  </si>
+  <si>
+    <t>caal_data</t>
+  </si>
+  <si>
+    <t>Survey/fishery CAAL data. Note if sex is 3, put female CAAL data then male CAAL data (similar to SS).</t>
   </si>
 </sst>
 </file>
@@ -1348,22 +1366,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F80"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F83"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="119.42578125" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.83203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="119.5" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>21</v>
@@ -1372,765 +1390,795 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="6" t="s">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C12" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="80" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="96" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C26" t="s">
+        <v>142</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" ht="112" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" t="s">
+        <v>147</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="112" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="96" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C41" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A42" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C43" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C45" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A46" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C51" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="A53" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+      <c r="A55" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C56" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C57" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+      <c r="A60" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C61" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" s="6" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" t="s">
-        <v>109</v>
-      </c>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" t="s">
-        <v>94</v>
-      </c>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="1:5" ht="120" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" t="s">
-        <v>61</v>
-      </c>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C34" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C36" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E38" s="2"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C39" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="C41" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C43" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C45" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C46" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C47" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C48" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C49" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C53" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C54" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C55" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C58" t="s">
+      <c r="B63" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C59" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C60" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B61" s="6" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C64" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B62" s="6" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B65" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C65" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B63" s="6" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B66" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="C63" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C65" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>18</v>
       </c>
       <c r="C66" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C67" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C68" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
-        <v>71</v>
+        <v>79</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="C69" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C70" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C72" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C73" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="192" x14ac:dyDescent="0.2">
+      <c r="A74" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C74" s="4" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C70" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="210" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A74" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="64" x14ac:dyDescent="0.2">
       <c r="A77" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" s="6" t="s">
-        <v>143</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A81" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A82" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A83" s="6" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grantadams/Documents/GitHub/Rceattle/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6940EDAC-9B17-BB4F-88DF-FDDECB12F63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD74161-B810-414B-A58B-4F9D3E63D020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="155">
   <si>
     <t>nspp</t>
   </si>
@@ -197,9 +197,6 @@
   </si>
   <si>
     <t>Fleet_type</t>
-  </si>
-  <si>
-    <t>Age_first_selected</t>
   </si>
   <si>
     <t>Estimate_catch_sd</t>
@@ -350,27 +347,6 @@
     <t>0 = Do not estimate (fixes all parameters for this fleet to initial values)
 1 = Fishery
 2 = Survey</t>
-  </si>
-  <si>
-    <t>0 = empirical selectivity provided in srv_emp_sel
-1 = logistic selectivity
-2 = non-parametric selecitivty sensu Ianelli et al 2018
-3 = double logistic
-4 = descending logistic
-5 = non-parametric selectivity sensu Taylor et al 2014 (Hake)</t>
-  </si>
-  <si>
-    <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity,  descending logistic , or non-parametric (Selectivity = 5). 
-0 = no
-1 = penalized deviates given sel_sd_prior (or random effects if "random_sel" is selected in "fit_mod"), 
-3 = time blocks with no penality 
-4 = random walk following Dorn
-5 = random walk on ascending portion of double logistic only. 
-If selectivity is set to type = 2 (non-parametric) this value will be the 1st penalty on selectivity.</t>
-  </si>
-  <si>
-    <t>The sd to use for the random walk of time varying selectivity if set to 1. 
-If selectivity is set to type = 2 (non-parametric) this value will be the 2nd penalty on selectivity.</t>
   </si>
   <si>
     <t>Composition data distribution:
@@ -514,9 +490,6 @@
 If &lt; 0, will normalize selectivity by the max.</t>
   </si>
   <si>
-    <t>Age at which selectivity becomes non-zero</t>
-  </si>
-  <si>
     <t>Integer: switch for which bioenergetics equation to use for each species for ft to scale max consumtion: 
 1 = Exponential (Stewart et al 1983)
 2 = Temperature-dependendence for warm-water species (Kitchell et al 1977; sensu Holsman et al 2015)
@@ -528,6 +501,48 @@
   </si>
   <si>
     <t>Survey/fishery CAAL data. Note if sex is 3, put female CAAL data then male CAAL data (similar to SS).</t>
+  </si>
+  <si>
+    <t>Bin_first_selected</t>
+  </si>
+  <si>
+    <t>Age/length bin at which selectivity becomes non-zero</t>
+  </si>
+  <si>
+    <t>0 = empirical selectivity provided in srv_emp_sel
+1 = Age-based logistic selectivity
+2 = Age-based non-parametric selecitivty sensu Ianelli et al 2018
+3 = Age-based double logistic
+4 = Age-based descending logistic
+5 = Age-based non-parametric selectivity sensu Taylor et al 2014 (Hake)
+6 = Length-based logistic selectivity
+7 = Length-based non-parametric selecitivty sensu Ianelli et al 2018
+8 = Length-based double logistic
+9 = Length-based descending logistic
+10 = Length-based non-parametric selectivity sensu Taylor et al 2014 (Hake)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity,  descending logistic , or non-parametric (Selectivity = 5). 
+0 = no
+1 = penalized deviates given sel_sd_prior (or random effects if "random_sel" is selected in "fit_mod"), 
+3 = time blocks with no penality 
+4 = random walk following Dorn
+5 = random walk on ascending portion of double logistic only. </t>
+  </si>
+  <si>
+    <t>Sel_curve_pen1</t>
+  </si>
+  <si>
+    <t>Sel_curve_pen2</t>
+  </si>
+  <si>
+    <t>The sd to use for the random walk of time varying selectivity if set to 1, 4, or 5.</t>
+  </si>
+  <si>
+    <t>If selectivity is set to type = 2 or 7 (non-parametric) this value will be the 1st penalty on selectivity.</t>
+  </si>
+  <si>
+    <t>If selectivity is set to type = 2 or 7 (non-parametric) this value will be the 2nd penalty on selectivity.</t>
   </si>
 </sst>
 </file>
@@ -1366,7 +1381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.6640625" style="6" bestFit="1" customWidth="1"/>
@@ -1378,10 +1393,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>21</v>
@@ -1392,190 +1407,190 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="80" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C17" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C18" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -1584,7 +1599,7 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -1606,7 +1621,7 @@
         <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E21" s="2"/>
     </row>
@@ -1618,7 +1633,7 @@
         <v>58</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -1640,10 +1655,10 @@
         <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="96" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="176" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>54</v>
       </c>
@@ -1651,7 +1666,7 @@
         <v>31</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="E25" s="2"/>
     </row>
@@ -1660,81 +1675,82 @@
         <v>54</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C26" t="s">
+        <v>138</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" t="s">
+        <v>153</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C28" t="s">
+        <v>154</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" ht="96" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C31" t="s">
+        <v>147</v>
+      </c>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="1:5" ht="112" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" t="s">
-        <v>147</v>
-      </c>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A31" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="E32" s="2"/>
     </row>
@@ -1742,33 +1758,34 @@
       <c r="A33" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" t="s">
-        <v>114</v>
+      <c r="C35" s="4" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -1776,88 +1793,88 @@
         <v>54</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="112" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>115</v>
+        <v>75</v>
+      </c>
+      <c r="C37" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>66</v>
+      <c r="B38" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="C38" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="112" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C39" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="96" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E40" s="2"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="C41" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="96" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>119</v>
+      <c r="B42" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>123</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="E42" s="2"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="8" t="s">
-        <v>120</v>
+      <c r="B43" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="C43" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="48" x14ac:dyDescent="0.2">
@@ -1865,10 +1882,10 @@
         <v>54</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -1876,21 +1893,21 @@
         <v>54</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="C45" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -1898,194 +1915,194 @@
         <v>54</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C47" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C48" t="s">
-        <v>132</v>
+        <v>54</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
-        <v>94</v>
+        <v>54</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="C49" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C50" t="s">
-        <v>73</v>
+        <v>128</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
-        <v>149</v>
+        <v>93</v>
       </c>
       <c r="C51" t="s">
-        <v>150</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C52" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>126</v>
+        <v>144</v>
+      </c>
+      <c r="C53" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="C54" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C57" t="s">
-        <v>25</v>
+        <v>94</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C58" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C59" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C60" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="80" x14ac:dyDescent="0.2">
-      <c r="A60" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B60" s="6" t="s">
+    <row r="62" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+      <c r="A62" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B62" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C60" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A61" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C62" t="s">
-        <v>90</v>
+      <c r="C62" s="4" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C67" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C68" t="s">
         <v>29</v>
@@ -2093,10 +2110,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C69" t="s">
         <v>29</v>
@@ -2104,10 +2121,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C70" t="s">
         <v>29</v>
@@ -2115,10 +2132,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C71" t="s">
         <v>29</v>
@@ -2126,59 +2143,81 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
-        <v>69</v>
+        <v>78</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="C72" t="s">
-        <v>128</v>
+        <v>29</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" s="6" t="s">
-        <v>99</v>
+        <v>78</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="C73" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="192" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C74" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C74" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" ht="64" x14ac:dyDescent="0.2">
-      <c r="A77" s="6" t="s">
+      <c r="C75" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="192" x14ac:dyDescent="0.2">
+      <c r="A76" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A79" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B77" s="9" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A79" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A80" s="6" t="s">
-        <v>38</v>
+      <c r="B79" s="9" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81" s="6" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82" s="6" t="s">
-        <v>133</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A83" s="6" t="s">
-        <v>134</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A84" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A85" s="6" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grantadams/Documents/GitHub/Rceattle/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD74161-B810-414B-A58B-4F9D3E63D020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0A6E23-7146-7249-BECD-2D0D2B1F9B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="159">
   <si>
     <t>nspp</t>
   </si>
@@ -121,9 +121,6 @@
     <t>Weight_index</t>
   </si>
   <si>
-    <t>Estimate_q</t>
-  </si>
-  <si>
     <t>Species number</t>
   </si>
   <si>
@@ -140,9 +137,6 @@
   </si>
   <si>
     <t>Time_varying_sel</t>
-  </si>
-  <si>
-    <t>Sel_sd_prior</t>
   </si>
   <si>
     <t>Time_varying_q</t>
@@ -536,13 +530,33 @@
     <t>Sel_curve_pen2</t>
   </si>
   <si>
-    <t>The sd to use for the random walk of time varying selectivity if set to 1, 4, or 5.</t>
-  </si>
-  <si>
     <t>If selectivity is set to type = 2 or 7 (non-parametric) this value will be the 1st penalty on selectivity.</t>
   </si>
   <si>
     <t>If selectivity is set to type = 2 or 7 (non-parametric) this value will be the 2nd penalty on selectivity.</t>
+  </si>
+  <si>
+    <t>The fixed or initial sd to use for time varying selectivity if set to 1, 4, or 5.</t>
+  </si>
+  <si>
+    <t>Time_varying_sel_sd_prior</t>
+  </si>
+  <si>
+    <t>Catchability</t>
+  </si>
+  <si>
+    <t>CAAL_loglike</t>
+  </si>
+  <si>
+    <t>CAAL_weights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Composition weights for CAAL  likelihood. </t>
+  </si>
+  <si>
+    <t>Composition data distribution:
+0 = full multinomial
+1 = dirichlet-multinomial</t>
   </si>
 </sst>
 </file>
@@ -1381,7 +1395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.6640625" style="6" bestFit="1" customWidth="1"/>
@@ -1393,10 +1407,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>21</v>
@@ -1407,323 +1421,323 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
         <v>77</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="80" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C17" t="s">
         <v>132</v>
-      </c>
-      <c r="C17" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" t="s">
         <v>133</v>
-      </c>
-      <c r="C18" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
         <v>55</v>
-      </c>
-      <c r="C20" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>56</v>
-      </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="176" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C26" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" t="s">
         <v>150</v>
-      </c>
-      <c r="C27" t="s">
-        <v>153</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" t="s">
         <v>151</v>
-      </c>
-      <c r="C28" t="s">
-        <v>154</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:5" ht="96" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>40</v>
+        <v>153</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>152</v>
@@ -1732,247 +1746,255 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C31" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="64" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E34" s="2"/>
+        <v>105</v>
+      </c>
     </row>
     <row r="35" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>37</v>
+        <v>52</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B36" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C36" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="112" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>111</v>
+      <c r="C39" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>65</v>
+        <v>52</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>42</v>
       </c>
       <c r="C41" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="96" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="112" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E42" s="2"/>
+        <v>109</v>
+      </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>66</v>
+        <v>52</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="C43" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="96" x14ac:dyDescent="0.2">
+      <c r="A45" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="8" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A44" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B44" s="8" t="s">
+      <c r="C48" t="s">
         <v>115</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B45" s="8" t="s">
+    </row>
+    <row r="49" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+      <c r="A49" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="C45" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A46" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C47" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A48" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C49" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
-        <v>92</v>
+        <v>52</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>58</v>
       </c>
       <c r="C50" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
-        <v>93</v>
+        <v>52</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="C51" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C52" t="s">
-        <v>72</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="C53" t="s">
-        <v>145</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -1983,148 +2005,142 @@
         <v>70</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>122</v>
+        <v>142</v>
+      </c>
+      <c r="C55" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="C56" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C59" t="s">
-        <v>25</v>
+        <v>92</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C60" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C61" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C62" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="80" x14ac:dyDescent="0.2">
-      <c r="A62" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B62" s="6" t="s">
+    <row r="64" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+      <c r="A64" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C62" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C63" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C64" t="s">
-        <v>89</v>
+      <c r="C64" s="4" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="C65" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C66" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C67" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C69" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C70" t="s">
         <v>29</v>
@@ -2132,10 +2148,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C71" t="s">
         <v>29</v>
@@ -2143,10 +2159,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C72" t="s">
         <v>29</v>
@@ -2154,10 +2170,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C73" t="s">
         <v>29</v>
@@ -2165,59 +2181,81 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" s="6" t="s">
-        <v>68</v>
+        <v>76</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="C74" t="s">
-        <v>124</v>
+        <v>29</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
-        <v>98</v>
+        <v>76</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="C75" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" ht="192" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="64" x14ac:dyDescent="0.2">
-      <c r="A79" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B79" s="9" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+      <c r="C76" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C77" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="192" x14ac:dyDescent="0.2">
+      <c r="A78" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="64" x14ac:dyDescent="0.2">
       <c r="A81" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A82" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" s="6" t="s">
-        <v>130</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" s="6" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grant.adams\GitHub\Rceattle\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grantadams/Documents/GitHub/Rceattle/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8189E839-E1F0-4A38-84B5-E0BF69DEF48F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0A6E23-7146-7249-BECD-2D0D2B1F9B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="765" windowWidth="34560" windowHeight="21585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data_names" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="159">
   <si>
     <t>nspp</t>
   </si>
@@ -118,15 +118,9 @@
     <t>Selectivity</t>
   </si>
   <si>
-    <t>Nselages</t>
-  </si>
-  <si>
     <t>Weight_index</t>
   </si>
   <si>
-    <t>Estimate_q</t>
-  </si>
-  <si>
     <t>Species number</t>
   </si>
   <si>
@@ -145,9 +139,6 @@
     <t>Time_varying_sel</t>
   </si>
   <si>
-    <t>Sel_sd_prior</t>
-  </si>
-  <si>
     <t>Time_varying_q</t>
   </si>
   <si>
@@ -202,12 +193,6 @@
     <t>Fleet_type</t>
   </si>
   <si>
-    <t>Age_first_selected</t>
-  </si>
-  <si>
-    <t>Age at which selectivity is non-zero</t>
-  </si>
-  <si>
     <t>Estimate_catch_sd</t>
   </si>
   <si>
@@ -304,9 +289,6 @@
     <t>Numeric: number of foraging days per year for each species</t>
   </si>
   <si>
-    <t>Number of ages to estimate non-parametric selectivity for Selectivity = 2 &amp; 5. Not used otherwise</t>
-  </si>
-  <si>
     <t>Comp_loglike</t>
   </si>
   <si>
@@ -316,9 +298,6 @@
     <t>catch_data</t>
   </si>
   <si>
-    <t>Age_max_selected</t>
-  </si>
-  <si>
     <t>weight</t>
   </si>
   <si>
@@ -350,9 +329,6 @@
   </si>
   <si>
     <t>Index of survey/fishery (does not restart for each species)</t>
-  </si>
-  <si>
-    <t>Index to match selectivities (otherwise, same as fleet_code)</t>
   </si>
   <si>
     <t>Integer: switch to estimate or fix numbers-at-age: 
@@ -365,32 +341,6 @@
     <t>0 = Do not estimate (fixes all parameters for this fleet to initial values)
 1 = Fishery
 2 = Survey</t>
-  </si>
-  <si>
-    <t>0 = empirical selectivity provided in srv_emp_sel
-1 = logistic selectivity
-2 = non-parametric selecitivty sensu Ianelli et al 2018
-3 = double logistic
-4 = descending logistic
-5 = non-parametric selectivity sensu Taylor et al 2014 (Hake)</t>
-  </si>
-  <si>
-    <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity,  descending logistic , or non-parametric (Selectivity = 5). 
-0 = no
-1 = penalized deviates given sel_sd_prior (or random effects if "random_sel" is selected in "fit_mod"), 
-3 = time blocks with no penality 
-4 = random walk following Dorn
-5 = random walk on ascending portion of double logistic only. 
-If selectivity is set to type = 2 (non-parametric) this value will be the 1st penalty on selectivity.</t>
-  </si>
-  <si>
-    <t>The sd to use for the random walk of time varying selectivity if set to 1. 
-If selectivity is set to type = 2 (non-parametric) this value will be the 2nd penalty on selectivity.</t>
-  </si>
-  <si>
-    <t>Age at which selectivity = 1. 
-If NA, it will not normalize selectivity. 
-If &lt; 0, will normalize selectivity by the max.</t>
   </si>
   <si>
     <t>Composition data distribution:
@@ -466,13 +416,6 @@
 Can have multiple weight-at-age data-sets for each species.</t>
   </si>
   <si>
-    <t>Integer: switch for which bioenergetics equation to use for each species for ft to scale max consumtion: 
-1 = Exponential (Stewart et al 1983)
-2 = Temperature-dependendence for warm-water species (Kitchell et al 1977; sensu Holsman et al 2015)
-3 = temperature dependence for cool and cold-water species (Thornton and Lessem 1979)
-4 = for direct input of consumption in Pyrs  where consumption at age = Wt * Pyrs (CA set to 1, fday set to 1, CB set to 0)</t>
-  </si>
-  <si>
     <t>Environmental indices such as bottom temperature data to incorporate into ration equation specificed by Ceq and Cindex. Also used to drive catchability if Estimate_q = 5 or 6. Will use the mean for missing years. Temperature should be in celcius.</t>
   </si>
   <si>
@@ -486,12 +429,6 @@
   </si>
   <si>
     <t>Sheet name</t>
-  </si>
-  <si>
-    <t>Age_max_selected_upper</t>
-  </si>
-  <si>
-    <t>Upper age for selectivity normalization (default = NA). If NA, does not use the age range, If not NA, uses mean selectivity between `Age_max_selected` and `Age_max_selected_upper`</t>
   </si>
   <si>
     <t xml:space="preserve">Survey index or fishery indices in weight (kg) or numbers. </t>
@@ -510,6 +447,116 @@
 4) If Pred_age &lt; -500 and Prey_age &lt; 0, data is assumed to be weighted mean diet proportion of prey-spp in predator-spp (sum across prey ages/sexes and take weighted mean across predator ages/sexes). Weights are estimated predators-at-age.
 If "Year = 0", the the diet will be assumed to be the average between "suit_styr" and "suit_endyr". 
 Only diet-data type 1 can be used for MSVPA based suitability</t>
+  </si>
+  <si>
+    <t>alpha_wt_len</t>
+  </si>
+  <si>
+    <t>beta_wt_len</t>
+  </si>
+  <si>
+    <t>Alpha parameter from Weight = alpha * Length ^ beta</t>
+  </si>
+  <si>
+    <t>Beta parameter from Weight = alpha * Length ^ beta</t>
+  </si>
+  <si>
+    <t>Index to mirror selectivities (otherwise, same as fleet_code)</t>
+  </si>
+  <si>
+    <t>N_sel_bins</t>
+  </si>
+  <si>
+    <t>Number of age or length bins to estimate non-parametric selectivity for Selectivity = 2 &amp; 5. Not used otherwise</t>
+  </si>
+  <si>
+    <t>Sel_norm_bin1</t>
+  </si>
+  <si>
+    <t>Sel_norm_bin2</t>
+  </si>
+  <si>
+    <t>Upper age/length bin for selectivity normalization (default = NA). If NA, does not use the age range, If not NA, uses mean selectivity between `Age_max_selected` and `Age_max_selected_upper`</t>
+  </si>
+  <si>
+    <t>Age/length bin at which selectivity = 1. 
+If NA, it will not normalize selectivity. 
+If &lt; 0, will normalize selectivity by the max.</t>
+  </si>
+  <si>
+    <t>Integer: switch for which bioenergetics equation to use for each species for ft to scale max consumtion: 
+1 = Exponential (Stewart et al 1983)
+2 = Temperature-dependendence for warm-water species (Kitchell et al 1977; sensu Holsman et al 2015)
+3 = temperature dependence for cool and cold-water species (Thornton and Lessem 1979)
+4 = for direct input of consumption in Pyrs  where consumption at age = Numbers * Pyrs (CA set to 1, fday set to 1, CB set to 0)</t>
+  </si>
+  <si>
+    <t>caal_data</t>
+  </si>
+  <si>
+    <t>Survey/fishery CAAL data. Note if sex is 3, put female CAAL data then male CAAL data (similar to SS).</t>
+  </si>
+  <si>
+    <t>Bin_first_selected</t>
+  </si>
+  <si>
+    <t>Age/length bin at which selectivity becomes non-zero</t>
+  </si>
+  <si>
+    <t>0 = empirical selectivity provided in srv_emp_sel
+1 = Age-based logistic selectivity
+2 = Age-based non-parametric selecitivty sensu Ianelli et al 2018
+3 = Age-based double logistic
+4 = Age-based descending logistic
+5 = Age-based non-parametric selectivity sensu Taylor et al 2014 (Hake)
+6 = Length-based logistic selectivity
+7 = Length-based non-parametric selecitivty sensu Ianelli et al 2018
+8 = Length-based double logistic
+9 = Length-based descending logistic
+10 = Length-based non-parametric selectivity sensu Taylor et al 2014 (Hake)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity,  descending logistic , or non-parametric (Selectivity = 5). 
+0 = no
+1 = penalized deviates given sel_sd_prior (or random effects if "random_sel" is selected in "fit_mod"), 
+3 = time blocks with no penality 
+4 = random walk following Dorn
+5 = random walk on ascending portion of double logistic only. </t>
+  </si>
+  <si>
+    <t>Sel_curve_pen1</t>
+  </si>
+  <si>
+    <t>Sel_curve_pen2</t>
+  </si>
+  <si>
+    <t>If selectivity is set to type = 2 or 7 (non-parametric) this value will be the 1st penalty on selectivity.</t>
+  </si>
+  <si>
+    <t>If selectivity is set to type = 2 or 7 (non-parametric) this value will be the 2nd penalty on selectivity.</t>
+  </si>
+  <si>
+    <t>The fixed or initial sd to use for time varying selectivity if set to 1, 4, or 5.</t>
+  </si>
+  <si>
+    <t>Time_varying_sel_sd_prior</t>
+  </si>
+  <si>
+    <t>Catchability</t>
+  </si>
+  <si>
+    <t>CAAL_loglike</t>
+  </si>
+  <si>
+    <t>CAAL_weights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Composition weights for CAAL  likelihood. </t>
+  </si>
+  <si>
+    <t>Composition data distribution:
+0 = full multinomial
+1 = dirichlet-multinomial</t>
   </si>
 </sst>
 </file>
@@ -1348,22 +1395,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F80"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F87"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="119.42578125" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.83203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="119.5" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>21</v>
@@ -1372,765 +1419,843 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="80" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C17" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="6" t="s">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="C22" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="176" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C26" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" t="s">
+        <v>150</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" t="s">
+        <v>151</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" ht="96" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" t="s">
+        <v>145</v>
+      </c>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="112" x14ac:dyDescent="0.2">
+      <c r="A42" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" t="s">
-        <v>94</v>
-      </c>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="1:5" ht="120" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" t="s">
-        <v>61</v>
-      </c>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C34" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C36" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E38" s="2"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C39" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="C41" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>63</v>
       </c>
       <c r="C43" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B44" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="96" x14ac:dyDescent="0.2">
+      <c r="A45" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B45" s="8" t="s">
+      <c r="C46" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C48" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+      <c r="A49" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C52" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C53" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C54" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C55" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C56" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="A57" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+      <c r="A59" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C60" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C61" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+      <c r="A64" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B65" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C65" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C69" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C72" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" s="6" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
+      <c r="C76" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C46" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C47" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C48" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C49" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C53" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C54" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C55" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C58" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C59" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C60" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C62" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C63" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C65" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C66" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C67" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C68" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
+      <c r="C77" t="s">
         <v>71</v>
       </c>
-      <c r="C69" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C70" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="210" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A74" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="6" t="s">
+    </row>
+    <row r="78" spans="1:3" ht="192" x14ac:dyDescent="0.2">
+      <c r="A78" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="64" x14ac:dyDescent="0.2">
+      <c r="A81" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="6" t="s">
-        <v>143</v>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" s="6" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grantadams/Documents/GitHub/Rceattle/inst/extdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grant.adams\GitHub\Rceattle ecosystem\Rceattle\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0A6E23-7146-7249-BECD-2D0D2B1F9B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C59BD4-347B-4D38-A803-5ADBAC992B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data_names" sheetId="1" r:id="rId1"/>
@@ -86,9 +86,6 @@
   </si>
   <si>
     <t>Description</t>
-  </si>
-  <si>
-    <t>Total catch in weight (kg) or numbers data</t>
   </si>
   <si>
     <t>Aging error matrices. Can have only one per species.</t>
@@ -557,6 +554,9 @@
     <t>Composition data distribution:
 0 = full multinomial
 1 = dirichlet-multinomial</t>
+  </si>
+  <si>
+    <t>Total catch in weight (mt) or numbers data</t>
   </si>
 </sst>
 </file>
@@ -1396,21 +1396,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F87"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.83203125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="119.5" customWidth="1"/>
-    <col min="4" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="119.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>21</v>
@@ -1419,843 +1419,843 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" s="6" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B12" s="6" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>50</v>
-      </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="80" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
-        <v>75</v>
-      </c>
       <c r="B17" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C18" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" t="s">
+        <v>135</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" t="s">
+        <v>149</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C28" t="s">
+        <v>150</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C31" t="s">
+        <v>144</v>
+      </c>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="8" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" t="s">
-        <v>102</v>
-      </c>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="6" t="s">
+      <c r="C43" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C48" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A49" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="176" x14ac:dyDescent="0.2">
-      <c r="A25" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C26" t="s">
-        <v>136</v>
-      </c>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C27" t="s">
-        <v>150</v>
-      </c>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C28" t="s">
-        <v>151</v>
-      </c>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:5" ht="96" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C31" t="s">
-        <v>145</v>
-      </c>
-      <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="E32" s="2"/>
-    </row>
-    <row r="33" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A33" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B34" s="6" t="s">
+      <c r="C49" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A35" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E35" s="2"/>
-    </row>
-    <row r="36" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C36" s="4" t="s">
+      <c r="C52" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C53" t="s">
         <v>158</v>
       </c>
-      <c r="E36" s="2"/>
-    </row>
-    <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="E37" s="2"/>
-    </row>
-    <row r="38" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C40" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="112" x14ac:dyDescent="0.2">
-      <c r="A42" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C43" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C44" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="96" x14ac:dyDescent="0.2">
-      <c r="A45" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E45" s="2"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C46" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A47" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="C48" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="48" x14ac:dyDescent="0.2">
-      <c r="A49" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C50" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C51" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A52" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C52" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A53" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C53" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54" t="s">
         <v>69</v>
       </c>
-      <c r="C54" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C55" t="s">
         <v>142</v>
       </c>
-      <c r="C55" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" t="s">
         <v>67</v>
       </c>
-      <c r="C56" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C58" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A59" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C60" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="48" x14ac:dyDescent="0.2">
-      <c r="A59" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60" s="6" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C61" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A61" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C61" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C65" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C66" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C67" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C69" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C70" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C71" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C72" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C73" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C74" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C75" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C76" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C77" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A78" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A81" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B81" s="9" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A77" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C77" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" ht="192" x14ac:dyDescent="0.2">
-      <c r="A78" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" ht="64" x14ac:dyDescent="0.2">
-      <c r="A81" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B81" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="6" t="s">
         <v>127</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A87" s="6" t="s">
-        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grant.adams\GitHub\Rceattle ecosystem\Rceattle\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grantadams/Documents/GitHub/Rceattle ecosystem/Rceattle/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C59BD4-347B-4D38-A803-5ADBAC992B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A530785-78A1-D346-AE9B-C58520816F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data_names" sheetId="1" r:id="rId1"/>
@@ -354,15 +354,6 @@
   </si>
   <si>
     <t>Age transition matrix (e.g. growth trajectory) index to used convert age to length</t>
-  </si>
-  <si>
-    <t>0 = fixed at "Q_sd_prior" 
-1 = Estimate as free parameter; 
-2 = Estimate as free parameter with normal prior of N(Q_prior, Q_sd_prior)
-3 = Estimate analytically following Ludwig and Walters 1994
-4 = Estimate power equation (NOT YET IMPLEMENTED)
-5 = Linear equation log(q_y) = q_mu + beta * index_y)
-6 = AR1 random deviates fit to environmental index (sensu Rogers et al 2024; 10.1093/icesjms/fsae005)</t>
   </si>
   <si>
     <t>Standard deviation for q prior</t>
@@ -557,6 +548,15 @@
   </si>
   <si>
     <t>Total catch in weight (mt) or numbers data</t>
+  </si>
+  <si>
+    <t>0 = fixed at "Q_sd_prior" 
+1 = Estimate as free parameter; 
+2 = Estimate as free parameter with normal prior of N(Q_prior, Q_sd_prior)
+3 = Estimate analytically following Ludwig and Walters 1994
+4 = Estimate power equation (NOT YET IMPLEMENTED)
+5 = Linear equation log(q_y) = q_mu + beta * index_y). Indices are comma seperated and specified by Time_varying_q
+6 = AR1 random deviates fit to environmental index (sensu Rogers et al 2024; 10.1093/icesjms/fsae005). Index is specified by Time_varying_q</t>
   </si>
 </sst>
 </file>
@@ -1396,21 +1396,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F87"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="119.42578125" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.83203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="119.5" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>21</v>
@@ -1419,7 +1419,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>74</v>
       </c>
@@ -1430,7 +1430,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>74</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>74</v>
       </c>
@@ -1452,7 +1452,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>74</v>
       </c>
@@ -1463,7 +1463,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>74</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>74</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>74</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>74</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>74</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>74</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>74</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
         <v>74</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
         <v>74</v>
       </c>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
         <v>74</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="80" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
         <v>74</v>
       </c>
@@ -1585,29 +1585,29 @@
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>74</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
         <v>74</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C18" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>51</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
         <v>51</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
         <v>51</v>
       </c>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>51</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>51</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>51</v>
       </c>
@@ -1669,10 +1669,10 @@
         <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="176" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>51</v>
       </c>
@@ -1680,47 +1680,47 @@
         <v>30</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>51</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C26" t="s">
         <v>134</v>
       </c>
-      <c r="C26" t="s">
-        <v>135</v>
-      </c>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>51</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C27" t="s">
+        <v>148</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>149</v>
       </c>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C28" t="s">
-        <v>150</v>
-      </c>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="96" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>51</v>
       </c>
@@ -1728,58 +1728,58 @@
         <v>37</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>51</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>51</v>
       </c>
       <c r="B31" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C31" t="s">
         <v>143</v>
       </c>
-      <c r="C31" t="s">
-        <v>144</v>
-      </c>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>51</v>
       </c>
       <c r="B32" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E32" s="2"/>
-    </row>
-    <row r="33" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="6" t="s">
+      <c r="C33" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:5" ht="64" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
         <v>51</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
         <v>51</v>
       </c>
@@ -1798,35 +1798,35 @@
         <v>58</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
         <v>51</v>
       </c>
       <c r="B36" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="E36" s="2"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B37" s="8" t="s">
+      <c r="C37" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>156</v>
-      </c>
       <c r="E37" s="2"/>
     </row>
-    <row r="38" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
         <v>51</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
         <v>51</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
         <v>51</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
         <v>51</v>
       </c>
@@ -1870,18 +1870,18 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" ht="112" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
         <v>51</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>51</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>51</v>
       </c>
@@ -1900,10 +1900,10 @@
         <v>39</v>
       </c>
       <c r="C44" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="96" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>51</v>
       </c>
@@ -1911,11 +1911,11 @@
         <v>38</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E45" s="2"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>51</v>
       </c>
@@ -1923,32 +1923,32 @@
         <v>63</v>
       </c>
       <c r="C46" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="8" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B47" s="8" t="s">
+      <c r="C47" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B48" s="8" t="s">
+      <c r="C48" t="s">
         <v>113</v>
       </c>
-      <c r="C48" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>51</v>
       </c>
@@ -1956,10 +1956,10 @@
         <v>56</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
         <v>51</v>
       </c>
@@ -1967,10 +1967,10 @@
         <v>57</v>
       </c>
       <c r="C50" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
         <v>51</v>
       </c>
@@ -1981,23 +1981,23 @@
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
         <v>89</v>
       </c>
       <c r="C52" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
         <v>90</v>
       </c>
       <c r="C53" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
         <v>68</v>
       </c>
@@ -2005,15 +2005,15 @@
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C55" t="s">
         <v>141</v>
       </c>
-      <c r="C55" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
         <v>66</v>
       </c>
@@ -2021,15 +2021,15 @@
         <v>67</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
         <v>8</v>
       </c>
@@ -2037,15 +2037,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
         <v>91</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
         <v>92</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
         <v>93</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
         <v>9</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="80" x14ac:dyDescent="0.2">
       <c r="A64" s="6" t="s">
         <v>75</v>
       </c>
@@ -2077,10 +2077,10 @@
         <v>10</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
         <v>75</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
         <v>75</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
         <v>75</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
         <v>75</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
         <v>75</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
         <v>75</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
         <v>75</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
         <v>75</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" s="6" t="s">
         <v>75</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" s="6" t="s">
         <v>75</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
         <v>75</v>
       </c>
@@ -2201,15 +2201,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
         <v>65</v>
       </c>
       <c r="C76" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" s="6" t="s">
         <v>95</v>
       </c>
@@ -2217,45 +2217,45 @@
         <v>70</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" ht="192" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="s">
         <v>94</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="64" x14ac:dyDescent="0.2">
       <c r="A81" s="6" t="s">
         <v>50</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" s="6" t="s">
         <v>126</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="6" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:C98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -798,12 +798,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>N_sel_bins</t>
+          <t>Selectivity_dimension</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Number of age or length bins to estimate non-parametric selectivity for Selectivity = 2 &amp; 5. Not used otherwise</t>
+          <t>"Age" or "Length".</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sel_curve_pen1</t>
+          <t>N_sel_bins</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>If selectivity is set to type = 2 or 7 (non-parametric) this value will be the 1st penalty on selectivity.</t>
+          <t>Number of age or length bins to estimate non-parametric selectivity for Selectivity = 2 &amp; 5. Not used otherwise</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sel_curve_pen2</t>
+          <t>Sel_curve_pen1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>If selectivity is set to type = 2 or 7 (non-parametric) this value will be the 2nd penalty on selectivity.</t>
+          <t>If selectivity is set to type = 2 or 7 (non-parametric) this value will be the 1st penalty on selectivity.</t>
         </is>
       </c>
     </row>
@@ -849,10 +849,44 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>Sel_curve_pen2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>If selectivity is set to type = 2 or 7 (non-parametric) this value will be the 2nd penalty on selectivity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sel_curve_pen3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Deviation-magnitude penalty weight (Sel_curve_pen3) for non-parametric / LogisticPM selectivity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>Time_varying_sel</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity,  descending logistic , or non-parametric (Selectivity = 5). _x000D_
 0 = no_x000D_
@@ -863,40 +897,6 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Time_varying_sel_sd</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>The fixed or initial sd to use for time varying selectivity if set to 1, 4, or 5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Bin_first_selected</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Age/length bin at which selectivity becomes non-zero</t>
-        </is>
-      </c>
-    </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -905,10 +905,214 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>Time_varying_sel_sd</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>The fixed or initial sd to use for time varying selectivity if set to 1, 4, or 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sel_start_year</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>First year the fleet's time-varying selectivity deviations are estimated and penalized (NA -&gt; earliest year of data across fleets sharing the Selectivity_index, bounded below by styr).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bin_first_selected</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Age/length bin at which selectivity becomes non-zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sel_shape_sd</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Shape/smoothness selectivity penalty expressed as a standard deviation (an intuitive alternative to Sel_curve_pen1); weight = 1/(2*sd^2). NonParametric (2/9) and LogisticPM (11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sel_curvature_sd</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2nd-difference curvature selectivity penalty expressed as a standard deviation (Sel_curve_pen2); NonParametric-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sel_devmag_sd</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Deviation-magnitude selectivity penalty expressed as a standard deviation (Sel_curve_pen3). NonParametric (2/9) and LogisticPM (11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sel_shape_dir</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Direction of the (directional-mode) NonParametric shape penalty when Sel_shape_sd is used: "Decreasing" (default) or "Increasing".</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sel_pen_first_bin</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>First bin (age or length) for the non-parametric shape penalty (NA -&gt; Bin_first_selected).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sel_pen_last_bin</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Last (left) bin of the shape-penalty pairs (NA -&gt; nbins-2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sel_shape_mode</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Shape-penalty mode: "Directional" (default) or "Smooth" (two-sided d^2, RTMB).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sel_avgsel_pen</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Weight on the AMAK avgsel base-level penalty (type 9); 0 = off (default), 10 matches AMAK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sel_cap_bin</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>NonParametricRPM bin cap (NA -&gt; no cap).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>Sel_norm_bin1</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Age/length bin at which selectivity = 1. _x000D_
 If NA, it will not normalize selectivity. _x000D_
@@ -916,35 +1120,35 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>Sel_norm_bin2</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Upper age/length bin for selectivity normalization (default = NA). If NA, does not use the age range, If not NA, uses mean selectivity between `Age_max_selected` and `Age_max_selected_upper`</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>Comp_loglike</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Composition data distribution:_x000D_
 -1 = AFSC multinomial_x000D_
@@ -953,36 +1157,36 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>Comp_weights</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Composition weights for composition likelihood. _x000D_
 After running model, these will update to McAllister &amp; Ianelli 1997 weights using the harmonic mean.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>CAAL_loglike</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Composition data distribution:_x000D_
 0 = full multinomial_x000D_
@@ -990,104 +1194,104 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>CAAL_weights</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Composition weights for CAAL  likelihood.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>weight1_Numbers2</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>1 = catch/index is weight (kg) the observation _x000D_
 2 = catch/index is in numbers</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>Weight_index</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Weight index to use for calculation of derived quantities</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>Age_transition_index</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Age transition matrix (e.g. growth trajectory) index to used convert age to length</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>Q_index</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>index to use if catchability coefficients are to be set the same</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>Catchability</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>0 = fixed at "Q_sd_prior" _x000D_
 1 = Estimate as free parameter; _x000D_
@@ -1099,52 +1303,52 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>Q_init</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Starting value or fixed value for catchability</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>Q_sd_prior</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Standard deviation for q prior</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>Time_varying_q</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>0 = no_x000D_
 1 = penalized deviate or random effect _x000D_
@@ -1155,35 +1359,35 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>Time_varying_q_sd</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>starting or fixed sd to use for the random walk of time varying q if set to 1</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>Estimate_index_sd</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>0 = use input "Log_sd" from index_data_x000D_
 1 = estimate as free parameter_x000D_
@@ -1191,35 +1395,35 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>Index_sd</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Starting value to be used if "Estimate_index_sd" = 1</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>Estimate_catch_sd</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>0 = use input "Log_sd" from catch_data_x000D_
 1 = estimate as free parameter_x000D_
@@ -1227,186 +1431,220 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>Catch_sd</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Starting value to be used if Estimate_catch_sd = 1</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Index_loglike</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Survey/index biomass observation likelihood family. 0 or "Lognormal" (default) = independent lognormal; "MVN"/"MVNORM" use a multivariate normal with a user-supplied covariance in index_cov.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Observation month for the fleet (0 = not specified).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
         <is>
           <t>proj_F_prop</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>The proportion of future fishing mortality assigned to this fleet</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>index_data</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Survey index or fishery indices in weight (kg) or numbers.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>catch_data</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Total catch in weight (mt) or numbers data</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>comp_data</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Survey/fishery age or length composition data. Note if sex is 3, put female composition data then male composition data (similar to SS).</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>caal_data</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Survey/fishery CAAL data. Note if sex is 3, put female CAAL data then male CAAL data (similar to SS).</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>emp_sel</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Empirical/fixed selectivity for surveys and fisheries (leave empty if not used)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>age_trans_matrix</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Age transition matrix (e.g. growth trajectory) used to convert age to length for length comp data. _x000D_
 Can have multiple matrices for a species specified by Age_transition_index.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>age_error</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Aging error matrices. Can have only one per species.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Time-invariant or -varying empirical weight-at-age for calculation of derived quantities (SSB, Consumption/Ration, Suitability, Total Catch, Survey Biomass, etc). _x000D_
 Can have multiple weight-at-age data-sets for each species.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>maturity</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Maturity-at-age for each species</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>sex_ratio</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Percent female at age for each species</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>M1_base</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Residual natural mortality for each species</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>Ceq</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Integer: switch for which bioenergetics equation to use for each species for ft to scale max consumtion: _x000D_
 1 = Exponential (Stewart et al 1983)_x000D_
@@ -1416,224 +1654,258 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>Cindex</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Integer: which environmental index in env_data to use to drive bioenergetics</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Pvalue</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Numeric: this scales the maximum consumption used for ration for each species; Pvalue is in Cmax*fT*Pvalue*Pyrs</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>fday</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Numeric: number of foraging days per year for each species</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Intercept of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>CB</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Slope of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>Qc</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>Tco</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Tcm</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>Tcl</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>CK1</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>CK4</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Diet_loglike</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Diet composition likelihood distribution per predator species (0 = multinomial).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Diet_comp_weights</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Diet composition weight (multinomial multiplier) per predator species.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>env_data</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Environmental indices such as bottom temperature data to incorporate into ration equation specificed by Ceq and Cindex. Also used to drive catchability if Estimate_q = 5 or 6. Will use the mean for missing years. Temperature should be in celcius.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>ration_data</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Annual relative foraging rate by age. Multiplied by pvalue and fday to scale maximum consumption to the number of days in a year that foraging occurs.</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>diet_data</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Stomach proportion by weight for each predator, prey, predator age, prey age combination. Multiple diet-data formats can be included:_x000D_
 _x000D_
@@ -1648,36 +1920,36 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>NOTE: Most objects are ordered by species code if not specified</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>NOTE: Lengths are index 1 through nlenths</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>NOTE: Columns for ages are index by 1 trhough nages, but are place holders.</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>NOTE: For catch, index, and comp data, if "Year" is negative, it will predict for that year, but not include the data in the likelihood.</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>NOTE: For emp_sel, weight, and ration_data, if "Year" == 0, those data will be used for all years</t>
         </is>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Q_index</t>
+          <t>Catchability_index</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Q_init</t>
+          <t>Catchability_init</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Q_sd_prior</t>
+          <t>Catchability_prior_sd</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Comp_loglike</t>
+          <t>Comp_distribution</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CAAL_loglike</t>
+          <t>CAAL_distribution</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Index_loglike</t>
+          <t>Index_distribution</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sel_norm_bin1</t>
+          <t>Sel_norm_bin</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sel_norm_bin2</t>
+          <t>Sel_norm_bin_upper</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Upper age/length bin for selectivity normalization (default = NA). If NA, does not use the age range, If not NA, uses mean selectivity between `Age_max_selected` and `Age_max_selected_upper`</t>
+          <t>Upper age/length bin for selectivity normalization (default = NA). If NA, does not use the age range, If not NA, uses mean selectivity between `Sel_norm_bin` and `Sel_norm_bin_upper`</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>weight1_Numbers2</t>
+          <t>Observation_units</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>proj_F_prop</t>
+          <t>Proj_F_proportion</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sigma_rec_prior</t>
+          <t>sigma_rec</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Diet_loglike</t>
+          <t>Diet_distribution</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1293,13 +1293,15 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0 = fixed at "Q_sd_prior" _x000D_
-1 = Estimate as free parameter; _x000D_
-2 = Estimate as free parameter with normal prior of N(Q_prior, Q_sd_prior)_x000D_
-3 = Estimate analytically following Ludwig and Walters 1994_x000D_
-4 = Estimate power equation (NOT YET IMPLEMENTED)_x000D_
-5 = Linear equation log(q_y) = q_mu + beta * index_y). Indices are comma seperated and specified by Time_varying_q_x000D_
-6 = AR1 random deviates fit to environmental index (sensu Rogers et al 2024; 10.1093/icesjms/fsae005). Index is specified by Time_varying_q</t>
+          <t>Catchability form. Accepts integer codes or readable strings:_x000D_
+0 or "Fixed" = fixed at Catchability_init_x000D_
+1 or "Estimated" = estimate as a free parameter_x000D_
+2 or "Estimated-with-prior" = estimate with a normal prior N(Catchability_init, Catchability_prior_sd)_x000D_
+3 or "Analytical" = geometric-mean analytical q following Ludwig and Walters 1994_x000D_
+4 or "PowerEquation" = power equation (NOT YET IMPLEMENTED)_x000D_
+5 or "Environmental" = linear equation log(q_y) = q_mu + beta * index_y; the environmental index is specified by Time_varying_q_x000D_
+6 or "AR1" = AR1 random deviates fit to an environmental index (sensu Rogers et al 2024; 10.1093/icesjms/fsae005), index specified by Time_varying_q_x000D_
+7 or "AnalyticalArith" = arithmetic-mean analytical q (AMAK/ebswp form, pair with the MVN survey likelihood)</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1356,7 @@
 1 = penalized deviate or random effect _x000D_
 3 = time blocks with no penalty_x000D_
 4 = random walk from mean following Dorn 2018 (dnorm(q_y - q_y-1, 0, sigma)_x000D_
-If "Estimate_q" = 5, this determines the environmental index to be used in the equation log(q_y) = q_mu + beta * index_y_x000D_
+If Catchability = 5, this determines the environmental index to be used in the equation log(q_y) = q_mu + beta * index_y_x000D_
 If "random_q" is selected in fit_mod, penalized deviates (1) and random walk parameters (4) will be treated as random effects</t>
         </is>
       </c>
@@ -1883,7 +1885,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Environmental indices such as bottom temperature data to incorporate into ration equation specificed by Ceq and Cindex. Also used to drive catchability if Estimate_q = 5 or 6. Will use the mean for missing years. Temperature should be in celcius.</t>
+          <t>Environmental indices such as bottom temperature data to incorporate into ration equation specificed by Ceq and Cindex. Also used to drive catchability if Catchability = 5 or 6. Will use the mean for missing years. Temperature should be in celcius.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C98"/>
+  <dimension ref="A1:C100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1219,50 +1219,50 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>Comp_accum_young</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Age/length composition young-tail accumulation bin (AFSC ac_yng): a 1-based ordinal on the fleet's composition dimension; bins below it are folded into it before the likelihood. NA or 1 = no young accumulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Comp_accum_old</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Age/length composition old-tail accumulation bin (AFSC ac_old): a 1-based ordinal on the fleet's composition dimension; bins above it are folded into it before the likelihood. NA, 0, or a value &gt;= the number of bins = no old accumulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>Observation_units</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>1 = catch/index is weight (kg) the observation _x000D_
 2 = catch/index is in numbers</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Weight_index</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Weight index to use for calculation of derived quantities</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Age_transition_index</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Age transition matrix (e.g. growth trajectory) index to used convert age to length</t>
-        </is>
-      </c>
-    </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Catchability_index</t>
+          <t>Weight_index</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>index to use if catchability coefficients are to be set the same</t>
+          <t>Weight index to use for calculation of derived quantities</t>
         </is>
       </c>
     </row>
@@ -1288,10 +1288,44 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>Age_transition_index</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Age transition matrix (e.g. growth trajectory) index to used convert age to length</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Catchability_index</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>index to use if catchability coefficients are to be set the same</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>Catchability</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Catchability form. Accepts integer codes or readable strings:_x000D_
 0 or "Fixed" = fixed at Catchability_init_x000D_
@@ -1305,40 +1339,6 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Catchability_init</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Starting value or fixed value for catchability</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Catchability_prior_sd</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Standard deviation for q prior</t>
-        </is>
-      </c>
-    </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
@@ -1347,10 +1347,44 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>Catchability_init</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Starting value or fixed value for catchability</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Catchability_prior_sd</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Standard deviation for q prior</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>Time_varying_q</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>0 = no_x000D_
 1 = penalized deviate or random effect _x000D_
@@ -1361,35 +1395,35 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>Time_varying_q_sd</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>starting or fixed sd to use for the random walk of time varying q if set to 1</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>Estimate_index_sd</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>0 = use input "Log_sd" from index_data_x000D_
 1 = estimate as free parameter_x000D_
@@ -1397,35 +1431,35 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>Index_sd</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Starting value to be used if "Estimate_index_sd" = 1</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
         <is>
           <t>Estimate_catch_sd</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>0 = use input "Log_sd" from catch_data_x000D_
 1 = estimate as free parameter_x000D_
@@ -1433,40 +1467,6 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Catch_sd</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Starting value to be used if Estimate_catch_sd = 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Index_distribution</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Survey/index biomass observation likelihood family. 0 or "Lognormal" (default) = independent lognormal; "MVN"/"MVNORM" use a multivariate normal with a user-supplied covariance in index_cov.</t>
-        </is>
-      </c>
-    </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Catch_sd</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Observation month for the fleet (0 = not specified).</t>
+          <t>Starting value to be used if Estimate_catch_sd = 1</t>
         </is>
       </c>
     </row>
@@ -1492,161 +1492,195 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Proj_F_proportion</t>
+          <t>Index_distribution</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>The proportion of future fishing mortality assigned to this fleet</t>
+          <t>Survey/index biomass observation likelihood family. 0 or "Lognormal" (default) = independent lognormal; "MVN"/"MVNORM" use a multivariate normal with a user-supplied covariance in index_cov.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>index_data</t>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Month</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Survey index or fishery indices in weight (kg) or numbers.</t>
+          <t>Observation month for the fleet (0 = not specified).</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>catch_data</t>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Proj_F_proportion</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Total catch in weight (mt) or numbers data</t>
+          <t>The proportion of future fishing mortality assigned to this fleet</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comp_data</t>
+          <t>index_data</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Survey/fishery age or length composition data. Note if sex is 3, put female composition data then male composition data (similar to SS).</t>
+          <t>Survey index or fishery indices in weight (kg) or numbers.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>caal_data</t>
+          <t>catch_data</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Survey/fishery CAAL data. Note if sex is 3, put female CAAL data then male CAAL data (similar to SS).</t>
+          <t>Total catch in weight (mt) or numbers data</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>emp_sel</t>
+          <t>comp_data</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Empirical/fixed selectivity for surveys and fisheries (leave empty if not used)</t>
+          <t>Survey/fishery age or length composition data. Note if sex is 3, put female composition data then male composition data (similar to SS).</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>caal_data</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Survey/fishery CAAL data. Note if sex is 3, put female CAAL data then male CAAL data (similar to SS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>emp_sel</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Empirical/fixed selectivity for surveys and fisheries (leave empty if not used)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>age_trans_matrix</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Age transition matrix (e.g. growth trajectory) used to convert age to length for length comp data. _x000D_
 Can have multiple matrices for a species specified by Age_transition_index.</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>age_error</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Aging error matrices. Can have only one per species.</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Time-invariant or -varying empirical weight-at-age for calculation of derived quantities (SSB, Consumption/Ration, Suitability, Total Catch, Survey Biomass, etc). _x000D_
 Can have multiple weight-at-age data-sets for each species.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>maturity</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Maturity-at-age for each species</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>sex_ratio</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Percent female at age for each species</t>
-        </is>
-      </c>
-    </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>M1_base</t>
+          <t>maturity</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Residual natural mortality for each species</t>
+          <t>Maturity-at-age for each species</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>sex_ratio</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Percent female at age for each species</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>M1_base</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Residual natural mortality for each species</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Ceq</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Integer: switch for which bioenergetics equation to use for each species for ft to scale max consumtion: _x000D_
 1 = Exponential (Stewart et al 1983)_x000D_
@@ -1656,40 +1690,6 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>bioenergetics_control</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Cindex</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Integer: which environmental index in env_data to use to drive bioenergetics</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>bioenergetics_control</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Pvalue</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Numeric: this scales the maximum consumption used for ration for each species; Pvalue is in Cmax*fT*Pvalue*Pyrs</t>
-        </is>
-      </c>
-    </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>fday</t>
+          <t>Cindex</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Numeric: number of foraging days per year for each species</t>
+          <t>Integer: which environmental index in env_data to use to drive bioenergetics</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>Pvalue</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Intercept of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
+          <t>Numeric: this scales the maximum consumption used for ration for each species; Pvalue is in Cmax*fT*Pvalue*Pyrs</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>fday</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Slope of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
+          <t>Numeric: number of foraging days per year for each species</t>
         </is>
       </c>
     </row>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Qc</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
+          <t>Intercept of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tco</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
+          <t>Slope of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tcm</t>
+          <t>Qc</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tcl</t>
+          <t>Tco</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CK1</t>
+          <t>Tcm</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CK4</t>
+          <t>Tcl</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Diet_distribution</t>
+          <t>CK1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Diet composition likelihood distribution per predator species (0 = multinomial).</t>
+          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
         </is>
       </c>
     </row>
@@ -1868,46 +1868,80 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Diet_comp_weights</t>
+          <t>CK4</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Diet composition weight (multinomial multiplier) per predator species.</t>
+          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>env_data</t>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Diet_distribution</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Environmental indices such as bottom temperature data to incorporate into ration equation specificed by Ceq and Cindex. Also used to drive catchability if Catchability = 5 or 6. Will use the mean for missing years. Temperature should be in celcius.</t>
+          <t>Diet composition likelihood distribution per predator species (0 = multinomial).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ration_data</t>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Diet_comp_weights</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Annual relative foraging rate by age. Multiplied by pvalue and fday to scale maximum consumption to the number of days in a year that foraging occurs.</t>
+          <t>Diet composition weight (multinomial multiplier) per predator species.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>env_data</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Environmental indices such as bottom temperature data to incorporate into ration equation specificed by Ceq and Cindex. Also used to drive catchability if Catchability = 5 or 6. Will use the mean for missing years. Temperature should be in celcius.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ration_data</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Annual relative foraging rate by age. Multiplied by pvalue and fday to scale maximum consumption to the number of days in a year that foraging occurs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>diet_data</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Stomach proportion by weight for each predator, prey, predator age, prey age combination. Multiple diet-data formats can be included:_x000D_
 _x000D_
@@ -1922,36 +1956,36 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>NOTE: Most objects are ordered by species code if not specified</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>NOTE: Lengths are index 1 through nlenths</t>
-        </is>
-      </c>
-    </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>NOTE: Columns for ages are index by 1 trhough nages, but are place holders.</t>
+          <t>NOTE: Most objects are ordered by species code if not specified</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>NOTE: For catch, index, and comp data, if "Year" is negative, it will predict for that year, but not include the data in the likelihood.</t>
+          <t>NOTE: Lengths are index 1 through nlenths</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
+        <is>
+          <t>NOTE: Columns for ages are index by 1 trhough nages, but are place holders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>NOTE: For catch, index, and comp data, if "Year" is negative, it will predict for that year, but not include the data in the likelihood.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>NOTE: For emp_sel, weight, and ration_data, if "Year" == 0, those data will be used for all years</t>
         </is>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Numeric: minimum age for each population (i.e.does recruitment correspond to age 0, 1, 2?)</t>
+          <t>Numeric: minimum age for each population (i.e. does recruitment correspond to age 0, 1, 2?)</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Integer: weight index for calculating  biomass, consumption/ration, and suitability for each species</t>
+          <t>Integer: weight index for calculating biomass, consumption/ration, and suitability for each species</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Integer: weight index for calculating  spawning biomass for each species</t>
+          <t>Integer: weight index for calculating female spawning-stock biomass (SSB) for each species</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,18 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0 = empirical selectivity provided in srv_emp_sel_x000D_
-1 = Age-based logistic selectivity_x000D_
-2 = Age-based non-parametric selecitivty sensu Ianelli et al 2018_x000D_
-3 = Age-based double logistic_x000D_
-4 = Age-based descending logistic_x000D_
-5 = Age-based non-parametric selectivity sensu Taylor et al 2014 (Hake)_x000D_
-6 = Length-based logistic selectivity_x000D_
-7 = Length-based non-parametric selecitivty sensu Ianelli et al 2018_x000D_
-8 = Length-based double logistic_x000D_
-9 = Length-based descending logistic_x000D_
-10 = Length-based non-parametric selectivity sensu Taylor et al 2014 (Hake)</t>
+          <t>0 = fixed (empirical selectivity from srv_emp_sel)_x000D_
+1 = logistic_x000D_
+2 = non-parametric (Ianelli et al. 2018)_x000D_
+3 = double logistic_x000D_
+4 = descending logistic_x000D_
+5 = non-parametric (Taylor et al. 2014, 'Hake')_x000D_
+6 = 2D AR1 (age x year)_x000D_
+7 = 3D AR1 (Cheng et al. 2024)_x000D_
+8 = double normal_x000D_
+9 = non-parametric random walk (AMAK 'pm')_x000D_
+11 = logistic with a free age-1 selectivity (AMAK 'pm')_x000D_
+Whether a form is age- or length-based is set by Selectivity_dimension, not by the code.</t>
         </is>
       </c>
     </row>
@@ -820,7 +821,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Number of age or length bins to estimate non-parametric selectivity for Selectivity = 2 &amp; 5. Not used otherwise</t>
+          <t>Number of age or length bins to estimate for non-parametric and AR1 selectivity (Selectivity = 2, 5, 6, 7, or 9).</t>
         </is>
       </c>
     </row>
@@ -837,7 +838,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>If selectivity is set to type = 2 or 7 (non-parametric) this value will be the 1st penalty on selectivity.</t>
+          <t>Shape/smoothness penalty weight for non-parametric (type 2/9) and LogisticPM (11) selectivity (the intuitive alternative is Sel_shape_sd). The 2DAR1/3DAR1 forms (6/7) reuse this column as a logit-scale AR1 correlation.</t>
         </is>
       </c>
     </row>
@@ -854,7 +855,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>If selectivity is set to type = 2 or 7 (non-parametric) this value will be the 2nd penalty on selectivity.</t>
+          <t>2nd-difference curvature penalty weight for non-parametric (type 2/9) selectivity (the intuitive alternative is Sel_curvature_sd). The 2DAR1/3DAR1 forms (6/7) reuse this column as a logit-scale AR1 correlation.</t>
         </is>
       </c>
     </row>
@@ -888,12 +889,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity,  descending logistic , or non-parametric (Selectivity = 5). _x000D_
+          <t>Whether to estimate time-varying selectivity for logistic, double logistic, descending logistic, or non-parametric forms._x000D_
 0 = no_x000D_
-1 = penalized deviates given sel_sd_prior (or random effects if "random_sel" is selected in "fit_mod"), _x000D_
-3 = time blocks with no penality _x000D_
+1 = penalized deviates given sel_sd_prior (or random effects if "random_sel" is selected in "fit_mod")_x000D_
+3 = time blocks with no penalty_x000D_
 4 = random walk following Dorn_x000D_
-5 = random walk on ascending portion of double logistic only.</t>
+5 = random walk on the ascending portion of double logistic only.</t>
         </is>
       </c>
     </row>
@@ -1682,9 +1683,9 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Integer: switch for which bioenergetics equation to use for each species for ft to scale max consumtion: _x000D_
+          <t>Integer: switch for which bioenergetics equation to use for each species for ft to scale max consumption: _x000D_
 1 = Exponential (Stewart et al 1983)_x000D_
-2 = Temperature-dependendence for warm-water species (Kitchell et al 1977; sensu Holsman et al 2015)_x000D_
+2 = Temperature-dependence for warm-water species (Kitchell et al 1977; sensu Holsman et al 2015)_x000D_
 3 = temperature dependence for cool and cold-water species (Thornton and Lessem 1979)_x000D_
 4 = for direct input of consumption in Pyrs  where consumption at age = Numbers * Pyrs (CA set to 1, fday set to 1, CB set to 0)</t>
         </is>
@@ -1919,7 +1920,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Environmental indices such as bottom temperature data to incorporate into ration equation specificed by Ceq and Cindex. Also used to drive catchability if Catchability = 5 or 6. Will use the mean for missing years. Temperature should be in celcius.</t>
+          <t>Environmental indices such as bottom temperature data to incorporate into ration equation specified by Ceq and Cindex. Also used to drive catchability if Catchability = 5 or 6. Will use the mean for missing years. Temperature should be in Celsius.</t>
         </is>
       </c>
     </row>
@@ -1966,14 +1967,14 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>NOTE: Lengths are index 1 through nlenths</t>
+          <t>NOTE: Lengths are index 1 through nlengths</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>NOTE: Columns for ages are index by 1 trhough nages, but are place holders.</t>
+          <t>NOTE: Columns for ages are index by 1 through nages, but are placeholders.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1891,7 +1891,9 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Diet composition likelihood distribution per predator species (0 = multinomial).</t>
+          <t>Diet composition likelihood distribution per predator species:_x000D_
+0 = multinomial_x000D_
+1 = dirichlet-multinomial</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1171,8 +1171,8 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Composition weights for composition likelihood. _x000D_
-After running model, these will update to McAllister &amp; Ianelli 1997 weights using the harmonic mean.</t>
+          <t>Starting composition weight, used when a model is built from scratch; a fit warm-started from `inits` carries the parameter forward instead. _x000D_
+A fitted model reports the implied McAllister &amp; Ianelli (1997) harmonic-mean weight separately, in `Comp_weights_mcallister`; `reweight_comps()` iterates on it.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1171,8 +1171,9 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Starting composition weight, used when a model is built from scratch; a fit warm-started from `inits` carries the parameter forward instead. _x000D_
-A fitted model reports the implied McAllister &amp; Ianelli (1997) harmonic-mean weight separately, in `Comp_weights_mcallister`; `reweight_comps()` iterates on it.</t>
+          <t>Composition weight. Multiplies the input sample size under a multinomial likelihood; starts the estimated weight under a Dirichlet-multinomial. _x000D_
+Read when a model is built from scratch -- a refit keeps the weight it is given. _x000D_
+See 'Comp_weights_mcallister' for the weight a fit implies, and reweight_comps() to tune towards it.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1171,7 +1171,9 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Composition weight. Multiplies the input sample size under a multinomial likelihood; starts the estimated weight under a Dirichlet-multinomial. _x000D_
+          <t>Composition weight, on a scale set by 'Comp_distribution'. _x000D_
+Under a multinomial it is the natural-scale multiplier on the input sample size. _x000D_
+Under a Dirichlet-multinomial the model uses exp(Comp_weights), so the column is the LOG of the starting weight -- the usual template value of 1 is a starting weight of e, not 1; use 0 for a weight of 1. _x000D_
 Read when a model is built from scratch -- a refit keeps the weight it is given. _x000D_
 See 'Comp_weights_mcallister' for the weight a fit implies, and reweight_comps() to tune towards it.</t>
         </is>
@@ -1209,7 +1211,10 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Composition weights for CAAL  likelihood.</t>
+          <t>Conditional age-at-length composition weight, on a scale set by 'CAAL_distribution' (as for 'Comp_weights'). _x000D_
+Under a multinomial it is the natural-scale multiplier on the input sample size. _x000D_
+Under a Dirichlet-multinomial the model uses exp(CAAL_weights), so the column is the LOG of the starting weight -- the default of 1 is a starting weight of e, not 1. _x000D_
+Read when a model is built from scratch -- a refit keeps the weight it is given.</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1916,10 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Diet composition weight (multinomial multiplier) per predator species.</t>
+          <t>Diet composition weight per predator species, on a scale set by 'Diet_distribution' (as for 'Comp_weights'). _x000D_
+Under a multinomial it is the natural-scale multiplier on the input sample size. _x000D_
+Under a Dirichlet-multinomial the model uses exp(Diet_comp_weights), so the column is the LOG of the starting weight. _x000D_
+Read when a model is built from scratch -- a refit keeps the weight it is given.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1962,7 +1962,7 @@
 3) If Pred_age &lt; 0 and Prey_age &lt; 0, data is assumed to be  mean diet proportion of prey-spp in predator-spp (sum across prey ages/sexes and take mean across predator ages/sexes)_x000D_
 4) If Pred_age &lt; -500 and Prey_age &lt; 0, data is assumed to be weighted mean diet proportion of prey-spp in predator-spp (sum across prey ages/sexes and take weighted mean across predator ages/sexes). Weights are estimated predators-at-age. _x000D_
 _x000D_
-If "Year = 0", the the diet will be assumed to be the average between "suit_styr" and "suit_endyr". _x000D_
+If "Year = 0", the diet will be assumed to be the average between "suit_styr" and "suit_endyr". _x000D_
 _x000D_
 Only diet-data type 1 can be used for MSVPA based suitability</t>
         </is>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C100"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1115,9 +1115,15 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Age/length bin at which selectivity = 1. _x000D_
+          <t>Age/length bin at which selectivity = 1. An absolute AGE for an age-based fleet (6 means age 6, not the 6th bin) or a 1-based LENGTH-BIN ordinal for a length-based one, per 'Selectivity_dimension'. _x000D_
 If NA, it will not normalize selectivity. _x000D_
-If &lt; 0, will normalize selectivity by the max.</t>
+If &lt; 0, will normalize selectivity by the max. _x000D_
+_x000D_
+In a two-sex model this column also sets how the sexes are scaled RELATIVE to each other, which is what decides whether relative sex-specific selectivity is estimated: _x000D_
+&lt; 0 normalizes by the maximum taken jointly across bins AND sexes, so one sex peaks at 1 and the other keeps its relative level (relative selectivity retained); _x000D_
+&gt;= 0 normalizes each sex separately at that bin, forcing both to 1 there, so only the SHAPE differs by sex (relative selectivity removed); _x000D_
+NA does not normalize, leaving the relative scale free. _x000D_
+Relative sex selectivity is only informed by the data where the composition is joint (comp_data Sex = 3); sex-specific rows (Sex = 1 or 2) each sum to 1 and carry no sex-ratio information. Selectivity = 'Hake' always normalizes within sex regardless of this column.</t>
         </is>
       </c>
     </row>
@@ -1146,10 +1152,31 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>Sel_norm_scope</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Whether selectivity normalization pools its reference across sexes. Orthogonal to 'Sel_norm_bin', which says WHERE the reference is taken (a named bin, or the max). _x000D_
+"WithinSex" = each sex is divided by its own reference, so both reach 1 and only the SHAPE differs by sex (relative sex-specific selectivity removed). _x000D_
+"AcrossSexes" (default) = one reference pooled over both sexes, so the less-selected sex stays below 1 (relative sex-specific selectivity retained). _x000D_
+No effect on a one-sex species, or where 'Sel_norm_bin' is NA (nothing is normalized). _x000D_
+NOTE: before v5.8.0 a named bin always implied "WithinSex"; max-normalization always implied "AcrossSexes". Set this column explicitly to "WithinSex" to restore the old behaviour of a two-sex fleet that normalizes at a named bin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>Comp_distribution</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Composition data distribution:_x000D_
 -1 = AFSC multinomial_x000D_
@@ -1158,18 +1185,18 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>Comp_weights</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Composition weight, on a scale set by 'Comp_distribution'. _x000D_
 Under a multinomial it is the natural-scale multiplier on the input sample size. _x000D_
@@ -1179,18 +1206,18 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>CAAL_distribution</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Composition data distribution:_x000D_
 0 = full multinomial_x000D_
@@ -1198,18 +1225,18 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>CAAL_weights</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Conditional age-at-length composition weight, on a scale set by 'CAAL_distribution' (as for 'Comp_weights'). _x000D_
 Under a multinomial it is the natural-scale multiplier on the input sample size. _x000D_
@@ -1218,23 +1245,6 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Comp_accum_young</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Age/length composition young-tail accumulation bin (AFSC ac_yng): a 1-based ordinal on the fleet's composition dimension; bins below it are folded into it before the likelihood. NA or 1 = no young accumulation.</t>
-        </is>
-      </c>
-    </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
@@ -1243,12 +1253,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Comp_accum_old</t>
+          <t>Comp_accum_young</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Age/length composition old-tail accumulation bin (AFSC ac_old): a 1-based ordinal on the fleet's composition dimension; bins above it are folded into it before the likelihood. NA, 0, or a value &gt;= the number of bins = no old accumulation.</t>
+          <t>Age/length composition young-tail accumulation bin (AFSC ac_yng): a 1-based ordinal on the fleet's composition dimension; bins below it are folded into it before the likelihood. NA or 1 = no young accumulation.</t>
         </is>
       </c>
     </row>
@@ -1260,33 +1270,33 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>Comp_accum_old</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Age/length composition old-tail accumulation bin (AFSC ac_old): a 1-based ordinal on the fleet's composition dimension; bins above it are folded into it before the likelihood. NA, 0, or a value &gt;= the number of bins = no old accumulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>Observation_units</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>1 = catch/index is weight (kg) the observation _x000D_
 2 = catch/index is in numbers</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Weight_index</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Weight index to use for calculation of derived quantities</t>
-        </is>
-      </c>
-    </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
@@ -1295,12 +1305,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Age_transition_index</t>
+          <t>Weight_index</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Age transition matrix (e.g. growth trajectory) index to used convert age to length</t>
+          <t>Weight index to use for calculation of derived quantities</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1322,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Catchability_index</t>
+          <t>Age_transition_index</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>index to use if catchability coefficients are to be set the same</t>
+          <t>Age transition matrix (e.g. growth trajectory) index to used convert age to length</t>
         </is>
       </c>
     </row>
@@ -1329,10 +1339,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>Catchability_index</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>index to use if catchability coefficients are to be set the same</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>Catchability</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Catchability form. Accepts integer codes or readable strings:_x000D_
 0 or "Fixed" = fixed at Catchability_init_x000D_
@@ -1346,23 +1373,6 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Catchability_init</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Starting value or fixed value for catchability</t>
-        </is>
-      </c>
-    </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
@@ -1371,12 +1381,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Catchability_prior_sd</t>
+          <t>Catchability_init</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Standard deviation for q prior</t>
+          <t>Starting value or fixed value for catchability</t>
         </is>
       </c>
     </row>
@@ -1388,10 +1398,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>Catchability_prior_sd</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Standard deviation for q prior</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>Time_varying_q</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>0 = no_x000D_
 1 = penalized deviate or random effect _x000D_
@@ -1402,23 +1429,6 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Time_varying_q_sd</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>starting or fixed sd to use for the random walk of time varying q if set to 1</t>
-        </is>
-      </c>
-    </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
@@ -1427,10 +1437,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>Time_varying_q_sd</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>starting or fixed sd to use for the random walk of time varying q if set to 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>Estimate_index_sd</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>0 = use input "Log_sd" from index_data_x000D_
 1 = estimate as free parameter_x000D_
@@ -1438,23 +1465,6 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Index_sd</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Starting value to be used if "Estimate_index_sd" = 1</t>
-        </is>
-      </c>
-    </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
@@ -1463,10 +1473,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>Index_sd</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Starting value to be used if "Estimate_index_sd" = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>Estimate_catch_sd</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>0 = use input "Log_sd" from catch_data_x000D_
 1 = estimate as free parameter_x000D_
@@ -1474,23 +1501,6 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Catch_sd</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Starting value to be used if Estimate_catch_sd = 1</t>
-        </is>
-      </c>
-    </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
@@ -1499,12 +1509,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Index_distribution</t>
+          <t>Catch_sd</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Survey/index biomass observation likelihood family. 0 or "Lognormal" (default) = independent lognormal; "MVN"/"MVNORM" use a multivariate normal with a user-supplied covariance in index_cov.</t>
+          <t>Starting value to be used if Estimate_catch_sd = 1</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1526,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Index_distribution</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Observation month for the fleet (0 = not specified).</t>
+          <t>Survey/index biomass observation likelihood family. 0 or "Lognormal" (default) = independent lognormal; "MVN"/"MVNORM" use a multivariate normal with a user-supplied covariance in index_cov.</t>
         </is>
       </c>
     </row>
@@ -1533,161 +1543,178 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Proj_F_proportion</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>The proportion of future fishing mortality assigned to this fleet</t>
+          <t>Observation month for the fleet (0 = not specified).</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>index_data</t>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Proj_F_proportion</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Survey index or fishery indices in weight (kg) or numbers.</t>
+          <t>The proportion of future fishing mortality assigned to this fleet</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>catch_data</t>
+          <t>index_data</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Total catch in weight (mt) or numbers data</t>
+          <t>Survey index or fishery indices in weight (kg) or numbers.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comp_data</t>
+          <t>catch_data</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Survey/fishery age or length composition data. Note if sex is 3, put female composition data then male composition data (similar to SS).</t>
+          <t>Total catch in weight (mt) or numbers data</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>caal_data</t>
+          <t>comp_data</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Survey/fishery CAAL data. Note if sex is 3, put female CAAL data then male CAAL data (similar to SS).</t>
+          <t>Survey/fishery age or length composition data. Note if sex is 3, put female composition data then male composition data (similar to SS).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>emp_sel</t>
+          <t>caal_data</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Empirical/fixed selectivity for surveys and fisheries (leave empty if not used)</t>
+          <t>Survey/fishery CAAL data. Note if sex is 3, put female CAAL data then male CAAL data (similar to SS).</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>emp_sel</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Empirical/fixed selectivity for surveys and fisheries (leave empty if not used)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>age_trans_matrix</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Age transition matrix (e.g. growth trajectory) used to convert age to length for length comp data. _x000D_
 Can have multiple matrices for a species specified by Age_transition_index.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>age_error</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Aging error matrices. Can have only one per species.</t>
-        </is>
-      </c>
-    </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>age_error</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Aging error matrices. Can have only one per species.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Time-invariant or -varying empirical weight-at-age for calculation of derived quantities (SSB, Consumption/Ration, Suitability, Total Catch, Survey Biomass, etc). _x000D_
 Can have multiple weight-at-age data-sets for each species.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>maturity</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Maturity-at-age for each species</t>
-        </is>
-      </c>
-    </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>sex_ratio</t>
+          <t>maturity</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Percent female at age for each species</t>
+          <t>Maturity-at-age for each species</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>M1_base</t>
+          <t>sex_ratio</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Residual natural mortality for each species</t>
+          <t>Percent female at age for each species</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>M1_base</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Residual natural mortality for each species</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>Ceq</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Integer: switch for which bioenergetics equation to use for each species for ft to scale max consumption: _x000D_
 1 = Exponential (Stewart et al 1983)_x000D_
@@ -1697,23 +1724,6 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>bioenergetics_control</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Cindex</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Integer: which environmental index in env_data to use to drive bioenergetics</t>
-        </is>
-      </c>
-    </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -1722,12 +1732,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pvalue</t>
+          <t>Cindex</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Numeric: this scales the maximum consumption used for ration for each species; Pvalue is in Cmax*fT*Pvalue*Pyrs</t>
+          <t>Integer: which environmental index in env_data to use to drive bioenergetics</t>
         </is>
       </c>
     </row>
@@ -1739,12 +1749,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>fday</t>
+          <t>Pvalue</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Numeric: number of foraging days per year for each species</t>
+          <t>Numeric: this scales the maximum consumption used for ration for each species; Pvalue is in Cmax*fT*Pvalue*Pyrs</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1766,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>fday</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Intercept of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
+          <t>Numeric: number of foraging days per year for each species</t>
         </is>
       </c>
     </row>
@@ -1773,12 +1783,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Slope of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
+          <t>Intercept of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1800,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Qc</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
+          <t>Slope of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1817,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tco</t>
+          <t>Qc</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -1824,7 +1834,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tcm</t>
+          <t>Tco</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -1841,7 +1851,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tcl</t>
+          <t>Tcm</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -1858,7 +1868,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CK1</t>
+          <t>Tcl</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -1875,7 +1885,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CK4</t>
+          <t>CK1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -1892,10 +1902,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
+          <t>CK4</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>Diet_distribution</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Diet composition likelihood distribution per predator species:_x000D_
 0 = multinomial_x000D_
@@ -1903,18 +1930,18 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>Diet_comp_weights</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Diet composition weight per predator species, on a scale set by 'Diet_distribution' (as for 'Comp_weights'). _x000D_
 Under a multinomial it is the natural-scale multiplier on the input sample size. _x000D_
@@ -1923,37 +1950,37 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>env_data</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Environmental indices such as bottom temperature data to incorporate into ration equation specified by Ceq and Cindex. Also used to drive catchability if Catchability = 5 or 6. Will use the mean for missing years. Temperature should be in Celsius.</t>
-        </is>
-      </c>
-    </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ration_data</t>
+          <t>env_data</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Annual relative foraging rate by age. Multiplied by pvalue and fday to scale maximum consumption to the number of days in a year that foraging occurs.</t>
+          <t>Environmental indices such as bottom temperature data to incorporate into ration equation specified by Ceq and Cindex. Also used to drive catchability if Catchability = 5 or 6. Will use the mean for missing years. Temperature should be in Celsius.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>ration_data</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Annual relative foraging rate by age. Multiplied by pvalue and fday to scale maximum consumption to the number of days in a year that foraging occurs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
           <t>diet_data</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Stomach proportion by weight for each predator, prey, predator age, prey age combination. Multiple diet-data formats can be included:_x000D_
 _x000D_
@@ -1968,36 +1995,36 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>NOTE: Most objects are ordered by species code if not specified</t>
-        </is>
-      </c>
-    </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>NOTE: Lengths are index 1 through nlengths</t>
+          <t>NOTE: Most objects are ordered by species code if not specified</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>NOTE: Columns for ages are index by 1 through nages, but are placeholders.</t>
+          <t>NOTE: Lengths are index 1 through nlengths</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NOTE: For catch, index, and comp data, if "Year" is negative, it will predict for that year, but not include the data in the likelihood.</t>
+          <t>NOTE: Columns for ages are index by 1 through nages, but are placeholders.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
+        <is>
+          <t>NOTE: For catch, index, and comp data, if "Year" is negative, it will predict for that year, but not include the data in the likelihood.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>NOTE: For emp_sel, weight, and ration_data, if "Year" == 0, those data will be used for all years</t>
         </is>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1119,11 +1119,8 @@
 If NA, it will not normalize selectivity. _x000D_
 If &lt; 0, will normalize selectivity by the max. _x000D_
 _x000D_
-In a two-sex model this column also sets how the sexes are scaled RELATIVE to each other, which is what decides whether relative sex-specific selectivity is estimated: _x000D_
-&lt; 0 normalizes by the maximum taken jointly across bins AND sexes, so one sex peaks at 1 and the other keeps its relative level (relative selectivity retained); _x000D_
-&gt;= 0 normalizes each sex separately at that bin, forcing both to 1 there, so only the SHAPE differs by sex (relative selectivity removed); _x000D_
-NA does not normalize, leaving the relative scale free. _x000D_
-Relative sex selectivity is only informed by the data where the composition is joint (comp_data Sex = 3); sex-specific rows (Sex = 1 or 2) each sum to 1 and carry no sex-ratio information. Selectivity = 'Hake' always normalizes within sex regardless of this column.</t>
+In a two-sex model this column says only WHERE the reference is taken; whether it is pooled across the sexes -- and so whether relative sex-specific selectivity survives -- is 'Sel_norm_scope'. NA does not normalize either way, leaving the relative scale free. _x000D_
+Relative sex selectivity is only informed by the data where the composition is joint (comp_data Sex = 3); sex-specific rows (Sex = 1 or 2) each sum to 1 and carry no sex-ratio information. Selectivity = 'Hake' always normalizes within sex regardless of either column.</t>
         </is>
       </c>
     </row>
@@ -1292,8 +1289,9 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1 = catch/index is weight (kg) the observation _x000D_
-2 = catch/index is in numbers</t>
+          <t>1 = catch/index is weight (mt) _x000D_
+2 = catch/index is in numbers (thousands of fish) _x000D_
+The model works in mt and thousands of fish throughout: numbers-at-age are thousands and weight-at-age is kg, so their product is mt.</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1575,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Survey index or fishery indices in weight (kg) or numbers.</t>
+          <t>Survey index or fishery indices in weight (mt) or numbers (thousands of fish).</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>index to use if catchability coefficients are to be set the same</t>
+          <t>Index used to give fleets the SAME catchability. Fleets sharing a value share one q parameter, so the group can carry only one answer to whether q is estimated: the LEAD fleet -- the group's first non-Off fleet -- decides for all of them, regardless of fleet type, and the others' Catchability settings are not used. A fleet with no index_data of its own is therefore still estimated if its group's lead is. Give a fleet its own value when it should be estimated independently.</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,8 @@
 4 or "PowerEquation" = power equation (NOT YET IMPLEMENTED)_x000D_
 5 or "Environmental" = linear equation log(q_y) = q_mu + beta * index_y; the environmental index is specified by Time_varying_q_x000D_
 6 or "AR1" = AR1 random deviates fit to an environmental index (sensu Rogers et al 2024; 10.1093/icesjms/fsae005), index specified by Time_varying_q_x000D_
-7 or "AnalyticalArith" = arithmetic-mean analytical q (AMAK/ebswp form, pair with the MVN survey likelihood)</t>
+7 or "AnalyticalArith" = arithmetic-mean analytical q (AMAK/ebswp form, pair with the MVN survey likelihood)_x000D_
+Applies to any fleet carrying index_data, a fishery with a CPUE series included; such a fleet's index uses that fleet's own selectivity. A fleet with NO fitted index rows gets no catchability whatever this says, since a q with no index to inform it is a flat direction -- unless it follows the lead of a shared Catchability_index group.</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1385,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Starting value or fixed value for catchability</t>
+          <t>Starting value or fixed value for catchability. Required on any fleet that carries index_data, whatever its Fleet_type -- it has no default, and data_check() rejects a fitted index without it.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -759,7 +759,9 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Index to mirror selectivities (otherwise, same as fleet_code)</t>
+          <t>Index used to give fleets the SAME selectivity (otherwise, same as Fleet_code). Fleets sharing a value share one selectivity parameter block, and the penalties and priors on it are accumulated once, on the LEAD fleet -- the group's first non-Off fleet._x000D_
+Sharing the parameters is not sufficient on its own: the columns that shape the curve are read per fleet, so they must match across the group or the fleets end up with different selectivities. Those are 'Selectivity', 'Selectivity_dimension', 'Bin_first_selected', 'N_sel_bins', 'Sel_norm_bin' and 'Sel_norm_bin_upper'; a blank counts as a value (a blank 'Sel_norm_bin' means 'do not normalize'). 'Time_varying_sel' and 'Sel_start_year' are instead resolved to the group's lead / earliest value, so a difference there is ignored rather than divergent. data_check() reports both cases._x000D_
+To mirror a fleet, copy its fleet_control row and change only the identity and catchability columns.</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1344,8 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Index used to give fleets the SAME catchability. Fleets sharing a value share one q parameter, so the group can carry only one answer to whether q is estimated: the LEAD fleet -- the group's first non-Off fleet -- decides for all of them, regardless of fleet type, and the others' Catchability settings are not used. A fleet with no index_data of its own is therefore still estimated if its group's lead is. Give a fleet its own value when it should be estimated independently.</t>
+          <t>Index used to give fleets the SAME catchability. Fleets sharing a value share one q parameter, so the group can carry only one answer to whether q is estimated: the LEAD fleet -- the group's first non-Off fleet -- decides for all of them, regardless of fleet type, and the others' Catchability settings are not used. A fleet with no index_data of its own is therefore still estimated if its group's lead is. Give a fleet its own value when it should be estimated independently._x000D_
+This applies to 'Fixed', 'Estimated' and 'Estimated-with-prior'. The solved forms -- 'Analytical', 'AnalyticalArith', 'Environmental' and 'AR1' -- compute catchability per fleet, from that fleet's own residuals or covariate, so a group containing one does NOT share a catchability even when every fleet in it carries the same setting. data_check() reports that case, and a differing 'Catchability' or 'Time_varying_q' within a group.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -760,7 +760,7 @@
       <c r="C24" t="inlineStr">
         <is>
           <t>Index used to give fleets the SAME selectivity (otherwise, same as Fleet_code). Fleets sharing a value share one selectivity parameter block, and the penalties and priors on it are accumulated once, on the LEAD fleet -- the group's first non-Off fleet._x000D_
-Sharing the parameters is not sufficient on its own: the columns that shape the curve are read per fleet, so they must match across the group or the fleets end up with different selectivities. Those are 'Selectivity', 'Selectivity_dimension', 'Bin_first_selected', 'N_sel_bins', 'Sel_norm_bin' and 'Sel_norm_bin_upper'; a blank counts as a value (a blank 'Sel_norm_bin' means 'do not normalize'). 'Time_varying_sel' and 'Sel_start_year' are instead resolved to the group's lead / earliest value, so a difference there is ignored rather than divergent. data_check() reports both cases._x000D_
+Sharing the parameters is not sufficient on its own: the columns that shape the curve are read per fleet, so they must match across the group or the fleets end up with different selectivities. Those are 'Selectivity', 'Selectivity_dimension', 'Bin_first_selected', 'N_sel_bins', 'Sel_norm_bin', 'Sel_norm_bin_upper', 'Sel_norm_scope' and 'Sel_cap_bin'; a blank counts as a value (a blank 'Sel_norm_bin' means 'do not normalize'). 'Time_varying_sel' and 'Sel_start_year' are instead resolved to the group's lead / earliest value, so a difference there is ignored rather than divergent. data_check() reports both cases._x000D_
 To mirror a fleet, copy its fleet_control row and change only the identity and catchability columns.</t>
         </is>
       </c>
@@ -1345,7 +1345,7 @@
       <c r="C56" t="inlineStr">
         <is>
           <t>Index used to give fleets the SAME catchability. Fleets sharing a value share one q parameter, so the group can carry only one answer to whether q is estimated: the LEAD fleet -- the group's first non-Off fleet -- decides for all of them, regardless of fleet type, and the others' Catchability settings are not used. A fleet with no index_data of its own is therefore still estimated if its group's lead is. Give a fleet its own value when it should be estimated independently._x000D_
-This applies to 'Fixed', 'Estimated' and 'Estimated-with-prior'. The solved forms -- 'Analytical', 'AnalyticalArith', 'Environmental' and 'AR1' -- compute catchability per fleet, from that fleet's own residuals or covariate, so a group containing one does NOT share a catchability even when every fleet in it carries the same setting. data_check() reports that case, and a differing 'Catchability' or 'Time_varying_q' within a group.</t>
+The exception is 'Analytical' and 'AnalyticalArith', which solve catchability from each fleet's own index observations rather than from the shared parameter, so a group containing one does NOT share a catchability even when every fleet in it carries the same setting. 'Environmental' and 'AR1' do share: they rebuild q from the group's shared parameters, including when the fleets name different environmental series (the lead fleet's is used). If the lead is 'Fixed' the group shares nothing at all: no catchability is estimated and each fleet sits at its own 'Catchability_init'. Where a q IS estimated for the group, its STARTING value is the mean of the group's log 'Catchability_init' (TMB averages the initial values of parameters mapped together), not the lead's; the prior centre does use the lead's. data_check() reports the analytical case, a Fixed lead that leaves fleets on different inits, and a differing 'Catchability' or 'Time_varying_q' within a group.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Starting value or fixed value for catchability. Required on any fleet that carries index_data, whatever its Fleet_type -- it has no default, and data_check() rejects a fitted index without it.</t>
+          <t>Starting value or fixed value for catchability. Must be positive on any fleet that carries index_data, whatever its Fleet_type -- it has no default, and it is logged to seed index_log_q, so a blank or zero gives a non-finite starting value. Not read under Analytical or AnalyticalArith, which solve q from the data.</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Standard deviation for q prior</t>
+          <t>Standard deviation for the q prior. Must be positive under Estimated-with-prior, where the prior is scored at it, and under AR1, where the estimated sd starts from it.</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>starting or fixed sd to use for the random walk of time varying q if set to 1</t>
+          <t>Starting or fixed sd for the time-varying q deviations. Must be positive when Time_varying_q is IID, AR1 or RandomWalk, which penalize the deviations at it; Block needs none.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -754,10 +754,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Observation month for the fleet (0 = not specified).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>Selectivity_index</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Index used to give fleets the SAME selectivity (otherwise, same as Fleet_code). Fleets sharing a value share one selectivity parameter block, and the penalties and priors on it are accumulated once, on the LEAD fleet -- the group's first non-Off fleet._x000D_
 Sharing the parameters is not sufficient on its own: the columns that shape the curve are read per fleet, so they must match across the group or the fleets end up with different selectivities. Those are 'Selectivity', 'Selectivity_dimension', 'Bin_first_selected', 'N_sel_bins', 'Sel_norm_bin', 'Sel_norm_bin_upper', 'Sel_norm_scope' and 'Sel_cap_bin'; a blank counts as a value (a blank 'Sel_norm_bin' means 'do not normalize'). 'Time_varying_sel' and 'Sel_start_year' are instead resolved to the group's lead / earliest value, so a difference there is ignored rather than divergent. data_check() reports both cases._x000D_
@@ -765,18 +782,18 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>Selectivity</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>0 = fixed (empirical selectivity from srv_emp_sel)_x000D_
 1 = logistic_x000D_
@@ -793,23 +810,6 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Selectivity_dimension</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>"Age" or "Length".</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
@@ -818,12 +818,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>N_sel_bins</t>
+          <t>Selectivity_dimension</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Number of age or length bins to estimate for non-parametric and AR1 selectivity (Selectivity = 2, 5, 6, 7, or 9).</t>
+          <t>"Age" or "Length".</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sel_curve_pen1</t>
+          <t>N_sel_bins</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Shape/smoothness penalty weight for non-parametric (type 2/9) and LogisticPM (11) selectivity (the intuitive alternative is Sel_shape_sd). The 2DAR1/3DAR1 forms (6/7) reuse this column as a logit-scale AR1 correlation, across selectivity BINS (ages or length bins, per Selectivity_dimension).</t>
+          <t>Number of age or length bins to estimate for non-parametric and AR1 selectivity (Selectivity = 2, 5, 6, 7, or 9).</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sel_curve_pen2</t>
+          <t>Sel_curve_pen1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2nd-difference curvature penalty weight for non-parametric (type 2/9) selectivity (the intuitive alternative is Sel_curvature_sd). The 2DAR1/3DAR1 forms (6/7) reuse this column as a logit-scale AR1 correlation, across YEARS.</t>
+          <t>Shape/smoothness penalty weight for non-parametric (type 2/9) and LogisticPM (11) selectivity (the intuitive alternative is Sel_shape_sd). The 2DAR1/3DAR1 forms (6/7) reuse this column as a logit-scale AR1 correlation, across selectivity BINS (ages or length bins, per Selectivity_dimension).</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sel_curve_pen3</t>
+          <t>Sel_curve_pen2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Deviation-magnitude penalty weight (Sel_curve_pen3) for non-parametric / LogisticPM selectivity. The 3DAR1 form (7) reuses this column as a logit-scale AR1 correlation, across COHORTS.</t>
+          <t>2nd-difference curvature penalty weight for non-parametric (type 2/9) selectivity (the intuitive alternative is Sel_curvature_sd). The 2DAR1/3DAR1 forms (6/7) reuse this column as a logit-scale AR1 correlation, across YEARS.</t>
         </is>
       </c>
     </row>
@@ -886,10 +886,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>Sel_curve_pen3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Deviation-magnitude penalty weight (Sel_curve_pen3) for non-parametric / LogisticPM selectivity. The 3DAR1 form (7) reuses this column as a logit-scale AR1 correlation, across COHORTS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>Time_varying_sel</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Whether to estimate time-varying selectivity for logistic, double logistic, descending logistic, or non-parametric forms._x000D_
 0 = no_x000D_
@@ -900,23 +917,6 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Time_varying_sel_sd</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>The fixed or initial sd to use for time varying selectivity if set to 1, 4, or 5.</t>
-        </is>
-      </c>
-    </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -925,12 +925,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sel_start_year</t>
+          <t>Time_varying_sel_sd</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>First year the fleet's time-varying selectivity deviations are estimated and penalized (NA -&gt; earliest year of data across fleets sharing the Selectivity_index, bounded below by styr).</t>
+          <t>The fixed or initial sd to use for time varying selectivity if set to 1, 4, or 5.</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bin_first_selected</t>
+          <t>Sel_start_year</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Age/length bin at which selectivity becomes non-zero</t>
+          <t>First year the fleet's time-varying selectivity deviations are estimated and penalized (NA -&gt; earliest year of data across fleets sharing the Selectivity_index, bounded below by styr).</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sel_shape_sd</t>
+          <t>Bin_first_selected</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Shape/smoothness selectivity penalty expressed as a standard deviation (an intuitive alternative to Sel_curve_pen1); weight = 1/(2*sd^2). NonParametric (2/9) and LogisticPM (11).</t>
+          <t>Age/length bin at which selectivity becomes non-zero</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sel_curvature_sd</t>
+          <t>Sel_shape_sd</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2nd-difference curvature selectivity penalty expressed as a standard deviation (Sel_curve_pen2); NonParametric-only.</t>
+          <t>Shape/smoothness selectivity penalty expressed as a standard deviation (an intuitive alternative to Sel_curve_pen1); weight = 1/(2*sd^2). NonParametric (2/9) and LogisticPM (11).</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sel_devmag_sd</t>
+          <t>Sel_curvature_sd</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Deviation-magnitude selectivity penalty expressed as a standard deviation (Sel_curve_pen3). NonParametric (2/9) and LogisticPM (11).</t>
+          <t>2nd-difference curvature selectivity penalty expressed as a standard deviation (Sel_curve_pen2); NonParametric-only.</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sel_shape_dir</t>
+          <t>Sel_devmag_sd</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Direction of the (directional-mode) NonParametric shape penalty when Sel_shape_sd is used: "Decreasing" (default) or "Increasing".</t>
+          <t>Deviation-magnitude selectivity penalty expressed as a standard deviation (Sel_curve_pen3). NonParametric (2/9) and LogisticPM (11).</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sel_pen_first_bin</t>
+          <t>Sel_shape_dir</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>First bin (age or length) for the non-parametric shape penalty (NA -&gt; Bin_first_selected).</t>
+          <t>Direction of the (directional-mode) NonParametric shape penalty when Sel_shape_sd is used: "Decreasing" (default) or "Increasing".</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sel_pen_last_bin</t>
+          <t>Sel_pen_first_bin</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Last (left) bin of the shape-penalty pairs (NA -&gt; nbins-2).</t>
+          <t>First bin (age or length) for the non-parametric shape penalty (NA -&gt; Bin_first_selected).</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sel_shape_mode</t>
+          <t>Sel_pen_last_bin</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Shape-penalty mode: "Directional" (default) or "Smooth" (two-sided d^2, RTMB).</t>
+          <t>Last (left) bin of the shape-penalty pairs (NA -&gt; nbins-2).</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sel_avgsel_pen</t>
+          <t>Sel_shape_mode</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Weight on the AMAK avgsel base-level penalty (type 9); 0 = off (default), 10 matches AMAK.</t>
+          <t>Shape-penalty mode: "Directional" (default) or "Smooth" (two-sided d^2, RTMB).</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sel_cap_bin</t>
+          <t>Sel_avgsel_pen</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NonParametricRPM bin cap (NA -&gt; no cap).</t>
+          <t>Weight on the AMAK avgsel base-level penalty (type 9); 0 = off (default), 10 matches AMAK.</t>
         </is>
       </c>
     </row>
@@ -1112,10 +1112,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>Sel_cap_bin</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NonParametricRPM bin cap (NA -&gt; no cap).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>Sel_norm_bin</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Age/length bin at which selectivity = 1. An absolute AGE for an age-based fleet (6 means age 6, not the 6th bin) or a 1-based LENGTH-BIN ordinal for a length-based one, per 'Selectivity_dimension'. _x000D_
 If NA, it will not normalize selectivity. _x000D_
@@ -1126,23 +1143,6 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Sel_norm_bin_upper</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Upper age/length bin for selectivity normalization (default = NA). If NA, does not use the age range, If not NA, uses mean selectivity between `Sel_norm_bin` and `Sel_norm_bin_upper`</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
@@ -1151,10 +1151,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>Sel_norm_bin_upper</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Upper age/length bin for selectivity normalization (default = NA). If NA, does not use the age range, If not NA, uses mean selectivity between `Sel_norm_bin` and `Sel_norm_bin_upper`</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>Sel_norm_scope</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Whether selectivity normalization pools its reference across sexes. Orthogonal to 'Sel_norm_bin', which says WHERE the reference is taken (a named bin, or the max). _x000D_
 "WithinSex" = each sex is divided by its own reference, so both reach 1 and only the SHAPE differs by sex (relative sex-specific selectivity removed). _x000D_
@@ -1164,18 +1181,18 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>Comp_distribution</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Composition data distribution:_x000D_
 -1 = AFSC multinomial_x000D_
@@ -1184,18 +1201,18 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>Comp_weights</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Composition weight, on a scale set by 'Comp_distribution'. _x000D_
 Under a multinomial it is the natural-scale multiplier on the input sample size. _x000D_
@@ -1205,18 +1222,18 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>CAAL_distribution</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Composition data distribution:_x000D_
 0 = full multinomial_x000D_
@@ -1224,18 +1241,18 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>CAAL_weights</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Conditional age-at-length composition weight, on a scale set by 'CAAL_distribution' (as for 'Comp_weights'). _x000D_
 Under a multinomial it is the natural-scale multiplier on the input sample size. _x000D_
@@ -1244,23 +1261,6 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Comp_accum_young</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Age/length composition young-tail accumulation bin (AFSC ac_yng): a 1-based ordinal on the fleet's composition dimension; bins below it are folded into it before the likelihood. NA or 1 = no young accumulation.</t>
-        </is>
-      </c>
-    </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Comp_accum_old</t>
+          <t>Comp_accum_young</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Age/length composition old-tail accumulation bin (AFSC ac_old): a 1-based ordinal on the fleet's composition dimension; bins above it are folded into it before the likelihood. NA, 0, or a value &gt;= the number of bins = no old accumulation.</t>
+          <t>Age/length composition young-tail accumulation bin (AFSC ac_yng): a 1-based ordinal on the fleet's composition dimension; bins below it are folded into it before the likelihood. NA or 1 = no young accumulation.</t>
         </is>
       </c>
     </row>
@@ -1286,10 +1286,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>Comp_accum_old</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Age/length composition old-tail accumulation bin (AFSC ac_old): a 1-based ordinal on the fleet's composition dimension; bins above it are folded into it before the likelihood. NA, 0, or a value &gt;= the number of bins = no old accumulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>Observation_units</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>1 = catch/index is weight (mt) _x000D_
 2 = catch/index is in numbers (thousands of fish) _x000D_
@@ -1297,23 +1314,6 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Weight_index</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Weight index to use for calculation of derived quantities</t>
-        </is>
-      </c>
-    </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Age_transition_index</t>
+          <t>Weight_index</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Age transition matrix (e.g. growth trajectory) index to used convert age to length</t>
+          <t>Weight index to use for calculation of derived quantities</t>
         </is>
       </c>
     </row>
@@ -1339,28 +1339,45 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>Age_transition_index</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Age transition matrix (e.g. growth trajectory) index to used convert age to length</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>Catchability_index</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Index used to give fleets the SAME catchability. Fleets sharing a value share one q parameter, so the group can carry only one answer to whether q is estimated: the LEAD fleet -- the group's first non-Off fleet -- decides for all of them, regardless of fleet type, and the others' Catchability settings are not used. A fleet with no index_data of its own is therefore still estimated if its group's lead is. Give a fleet its own value when it should be estimated independently._x000D_
 The exception is 'Analytical' and 'AnalyticalArith', which solve catchability from each fleet's own index observations rather than from the shared parameter, so a group containing one does NOT share a catchability even when every fleet in it carries the same setting. 'Environmental' and 'AR1' do share: they rebuild q from the group's shared parameters, including when the fleets name different environmental series (the lead fleet's is used). If the lead is 'Fixed' the group shares nothing at all: no catchability is estimated and each fleet sits at its own 'Catchability_init'. Where a q IS estimated for the group, its STARTING value is the mean of the group's log 'Catchability_init' (TMB averages the initial values of parameters mapped together), not the lead's; the prior centre does use the lead's. data_check() reports the analytical case, a Fixed lead that leaves fleets on different inits, and a differing 'Catchability' or 'Time_varying_q' within a group.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>Catchability</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Catchability form. Accepts integer codes or readable strings:_x000D_
 0 or "Fixed" = fixed at Catchability_init_x000D_
@@ -1375,23 +1392,6 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Catchability_init</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Starting value or fixed value for catchability. Must be positive on any fleet that carries index_data, whatever its Fleet_type -- it has no default, and it is logged to seed index_log_q, so a blank or zero gives a non-finite starting value. Not read under Analytical or AnalyticalArith, which solve q from the data.</t>
-        </is>
-      </c>
-    </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Catchability_prior_sd</t>
+          <t>Catchability_init</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Standard deviation for the q prior. Must be positive under Estimated-with-prior, where the prior is scored at it, and under AR1, where the estimated sd starts from it.</t>
+          <t>Starting value or fixed value for catchability. Must be positive on any fleet that carries index_data, whatever its Fleet_type -- it has no default, and it is logged to seed index_log_q, so a blank or zero gives a non-finite starting value. Not read under Analytical or AnalyticalArith, which solve q from the data.</t>
         </is>
       </c>
     </row>
@@ -1417,10 +1417,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>Catchability_prior_sd</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Standard deviation for the q prior. Must be positive under Estimated-with-prior, where the prior is scored at it, and under AR1, where the estimated sd starts from it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>Time_varying_q</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>0 = no_x000D_
 1 = penalized deviate or random effect _x000D_
@@ -1431,23 +1448,6 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Time_varying_q_sd</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Starting or fixed sd for the time-varying q deviations. Must be positive when Time_varying_q is IID, AR1 or RandomWalk, which penalize the deviations at it; Block needs none.</t>
-        </is>
-      </c>
-    </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
@@ -1456,14 +1456,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Estimate_index_sd</t>
+          <t>Time_varying_q_sd</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>0 = use input "Log_sd" from index_data_x000D_
-1 = estimate as free parameter_x000D_
-2 = estimate analytically following Ludwig and Walters (1994)</t>
+          <t>Starting or fixed sd for the time-varying q deviations. Must be positive when Time_varying_q is IID, AR1 or RandomWalk, which penalize the deviations at it; Block needs none.</t>
         </is>
       </c>
     </row>
@@ -1475,63 +1473,10 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Index_sd</t>
+          <t>Index_distribution</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
-        <is>
-          <t>Starting value to be used if "Estimate_index_sd" = 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Estimate_catch_sd</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>0 = use input "Log_sd" from catch_data_x000D_
-1 = estimate as free parameter_x000D_
-2 = estimate analytically following Ludwig and Walters (1994)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Catch_sd</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Starting value to be used if Estimate_catch_sd = 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Index_distribution</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
         <is>
           <t>Survey/index biomass observation likelihood family._x000D_
 0 or "Lognormal" (default) = independent lognormal on the log observation, with the bias correction._x000D_
@@ -1541,6 +1486,61 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Estimate_index_sd</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0 = use input "Log_sd" from index_data_x000D_
+1 = estimate as free parameter_x000D_
+2 = estimate analytically following Ludwig and Walters (1994)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Index_sd</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Starting value to be used if "Estimate_index_sd" = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Estimate_catch_sd</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0 = use input "Log_sd" from catch_data_x000D_
+1 = estimate as free parameter_x000D_
+2 = estimate analytically following Ludwig and Walters (1994)</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
@@ -1549,12 +1549,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Catch_sd</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Observation month for the fleet (0 = not specified).</t>
+          <t>Starting value to be used if Estimate_catch_sd = 1</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1386,7 +1386,7 @@
 3 or "Analytical" = geometric-mean analytical q following Ludwig and Walters 1994_x000D_
 4 or "PowerEquation" = power equation (NOT YET IMPLEMENTED)_x000D_
 5 or "Environmental" = linear equation log(q_y) = q_mu + beta * index_y; the environmental index is specified by Time_varying_q_x000D_
-6 or "AR1" = AR1 random deviates fit to an environmental index (sensu Rogers et al 2024; 10.1093/icesjms/fsae005), index specified by Time_varying_q_x000D_
+6 or "AR1" = REMOVED; data_check() errors. AR1 random deviates fit to an environmental index (sensu Rogers et al 2024; 10.1093/icesjms/fsae005), index specified by Time_varying_q -- but the deviates were never estimated, so q came back constant and the objective was not comparable with another model's. Express it as a q linkage with ar1(1 | Year) and 'observe', passed to fit_mod(qFun = ); the error gives the call._x000D_
 7 or "AnalyticalArith" = arithmetic-mean analytical q (AMAK/ebswp form, pair with the MVN survey likelihood)_x000D_
 Applies to any fleet carrying index_data, a fishery with a CPUE series included; such a fleet's index uses that fleet's own selectivity. A fleet with NO fitted index rows gets no catchability whatever this says, since a q with no index to inform it is a flat direction -- unless it follows the lead of a shared Catchability_index group.</t>
         </is>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1236,6 +1236,7 @@
       <c r="C50" t="inlineStr">
         <is>
           <t>Composition data distribution:_x000D_
+-1 = AFSC multinomial_x000D_
 0 = full multinomial_x000D_
 1 = dirichlet-multinomial</t>
         </is>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -909,11 +909,13 @@
       <c r="C32" t="inlineStr">
         <is>
           <t>Whether to estimate time-varying selectivity for logistic, double logistic, descending logistic, or non-parametric forms._x000D_
-0 = no_x000D_
-1 = penalized deviates given sel_sd_prior (or random effects if "random_sel" is selected in "fit_mod")_x000D_
-3 = time blocks with no penalty_x000D_
-4 = random walk following Dorn_x000D_
-5 = random walk on the ascending portion of double logistic only.</t>
+0 or "Off" = no_x000D_
+1 or "IID" = penalized deviates given Time_varying_sel_sd (or random effects if "random_sel" is selected in "fit_mod")_x000D_
+2 or "AR1" = REMOVED in 5.16.0; data_check() errors on it. It was never an AR1 -- the template scored it with the same independent normal penalty as "IID", and the selectivity deviations have no correlation parameter. Use "IID" for the fit it actually gave, or express the autocorrelation as a selectivity linkage: build_selectivity(linkages = list(inf_asc = linkage_spec(~ ar1(1 | Year), by = ~ fleet)))._x000D_
+3 or "Block" = time blocks with no penalty_x000D_
+4 or "RandomWalk" = random walk following Dorn_x000D_
+5 or "RandomWalkAscending" = random walk on the ascending portion of double logistic only._x000D_
+Soft-deprecated as a whole: the linkage grammar expresses the same deviations per selectivity parameter, with the deviation sd estimated or fixed.</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1442,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0 = no_x000D_
-1 = penalized deviate or random effect _x000D_
-3 = time blocks with no penalty_x000D_
-4 = random walk from mean following Dorn 2018 (dnorm(q_y - q_y-1, 0, sigma)_x000D_
+          <t>0 or "Off" = no_x000D_
+1 or "IID" = penalized deviate or random effect_x000D_
+2 or "AR1" = REMOVED in 5.16.0; data_check() errors on it. It was never an AR1 -- the template scored it with the same independent normal penalty as "IID", and index_q_rho belongs to the removed Catchability = "AR1" (QAR1) path, not to this switch. Use "IID" for the fit it actually gave, or express the autocorrelation as a q linkage: build_catchability(linkages = list(q = linkage_spec(~ ar1(1 | Year), by = ~ fleet)))._x000D_
+3 or "Block" = time blocks with no penalty_x000D_
+4 or "RandomWalk" = random walk from mean following Dorn 2018 (dnorm(q_y - q_y-1, 0, sigma)_x000D_
 If Catchability = 5, this determines the environmental index to be used in the equation log(q_y) = q_mu + beta * index_y_x000D_
-If "random_q" is selected in fit_mod, penalized deviates (1) and random walk parameters (4) will be treated as random effects</t>
+If "random_q" is selected in fit_mod, penalized deviates (1) and random walk parameters (4) will be treated as random effects._x000D_
+Soft-deprecated as a whole: the linkage grammar expresses the same deviations, with the deviation sd estimated or fixed.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -776,9 +776,9 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Index used to give fleets the SAME selectivity (otherwise, same as Fleet_code). Fleets sharing a value share one selectivity parameter block, and the penalties and priors on it are accumulated once, on the LEAD fleet -- the group's first non-Off fleet._x000D_
-Sharing the parameters is not sufficient on its own: the columns that shape the curve are read per fleet, so they must match across the group or the fleets end up with different selectivities. Those are 'Selectivity', 'Selectivity_dimension', 'Bin_first_selected', 'N_sel_bins', 'Sel_norm_bin', 'Sel_norm_bin_upper', 'Sel_norm_scope' and 'Sel_cap_bin'; a blank counts as a value (a blank 'Sel_norm_bin' means 'do not normalize'). 'Time_varying_sel' and 'Sel_start_year' are instead resolved to the group's lead / earliest value, so a difference there is ignored rather than divergent. data_check() reports both cases._x000D_
-To mirror a fleet, copy its fleet_control row and change only the identity and catchability columns.</t>
+          <t>Index used to give fleets the SAME selectivity (otherwise, same as Fleet_code). Fleets sharing a value share one selectivity parameter block, with its penalties and priors accumulated once on the group's first non-Off fleet._x000D_
+Sharing the parameters is not enough on its own: the columns that shape the curve are read per fleet and must agree across the group, or the fleets end up with different selectivities. data_check() reports any that differ. To mirror a fleet, copy its fleet_control row and change only the identity and catchability columns._x000D_
+See vignette('model-options-and-functionality'), 'Sharing a selectivity between fleets'.</t>
         </is>
       </c>
     </row>
@@ -911,11 +911,11 @@
           <t>Whether to estimate time-varying selectivity for logistic, double logistic, descending logistic, or non-parametric forms._x000D_
 0 or "Off" = no_x000D_
 1 or "IID" = penalized deviates given Time_varying_sel_sd (or random effects if "random_sel" is selected in "fit_mod")_x000D_
-2 or "AR1" = REMOVED in 5.16.0; data_check() errors on it. It was never an AR1 -- the template scored it with the same independent normal penalty as "IID", and the selectivity deviations have no correlation parameter. Use "IID" for the fit it actually gave, or express the autocorrelation as a selectivity linkage: build_selectivity(linkages = list(inf_asc = linkage_spec(~ ar1(1 | Year), by = ~ fleet)))._x000D_
+2 or "AR1" = REMOVED in 5.16.0; data_check() errors on it. It was never an AR1 -- it was scored as "IID" -- so use "IID" for the same fit, or a selectivity linkage with ar1(1 | Year) for a real one._x000D_
 3 or "Block" = time blocks with no penalty_x000D_
 4 or "RandomWalk" = random walk following Dorn_x000D_
 5 or "RandomWalkAscending" = random walk on the ascending portion of double logistic only._x000D_
-Soft-deprecated as a whole: the linkage grammar expresses the same deviations per selectivity parameter, with the deviation sd estimated or fixed.</t>
+Soft-deprecated as a whole: the linkage grammar expresses the same deviations per selectivity parameter, with the deviation sd estimated or fixed. See vignette('model-options-and-functionality').</t>
         </is>
       </c>
     </row>
@@ -1139,9 +1139,7 @@
           <t>Age/length bin at which selectivity = 1. An absolute AGE for an age-based fleet (6 means age 6, not the 6th bin) or a 1-based LENGTH-BIN ordinal for a length-based one, per 'Selectivity_dimension'. _x000D_
 If NA, it will not normalize selectivity. _x000D_
 If &lt; 0, will normalize selectivity by the max. _x000D_
-_x000D_
-In a two-sex model this column says only WHERE the reference is taken; whether it is pooled across the sexes -- and so whether relative sex-specific selectivity survives -- is 'Sel_norm_scope'. NA does not normalize either way, leaving the relative scale free. _x000D_
-Relative sex selectivity is only informed by the data where the composition is joint (comp_data Sex = 3); sex-specific rows (Sex = 1 or 2) each sum to 1 and carry no sex-ratio information. Selectivity = 'Hake' always normalizes within sex regardless of either column.</t>
+In a two-sex model this column says only WHERE the reference is taken; whether it is pooled across the sexes is 'Sel_norm_scope'. See vignette('model-options-and-functionality'), 'Sex structure and relative selectivity'.</t>
         </is>
       </c>
     </row>
@@ -1178,8 +1176,7 @@
           <t>Whether selectivity normalization pools its reference across sexes. Orthogonal to 'Sel_norm_bin', which says WHERE the reference is taken (a named bin, or the max). _x000D_
 "WithinSex" = each sex is divided by its own reference, so both reach 1 and only the SHAPE differs by sex (relative sex-specific selectivity removed). _x000D_
 "AcrossSexes" (default) = one reference pooled over both sexes, so the less-selected sex stays below 1 (relative sex-specific selectivity retained). _x000D_
-No effect on a one-sex species, or where 'Sel_norm_bin' is NA (nothing is normalized). _x000D_
-NOTE: before v5.8.0 a named bin always implied "WithinSex"; max-normalization always implied "AcrossSexes". Set this column explicitly to "WithinSex" to restore the old behaviour of a two-sex fleet that normalizes at a named bin.</t>
+No effect on a one-sex species, or where 'Sel_norm_bin' is NA (nothing is normalized).</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1215,7 @@
         <is>
           <t>Composition weight, on a scale set by 'Comp_distribution'. _x000D_
 Under a multinomial it is the natural-scale multiplier on the input sample size. _x000D_
-Under a Dirichlet-multinomial the model uses exp(Comp_weights), so the column is the LOG of the starting weight -- the usual template value of 1 is a starting weight of e, not 1; use 0 for a weight of 1. _x000D_
+Under a Dirichlet-multinomial the model uses exp(Comp_weights), so the column is the LOG of the starting weight -- a value of 1 is a starting weight of e; use 0 for a weight of 1. _x000D_
 Read when a model is built from scratch -- a refit keeps the weight it is given. _x000D_
 See 'Comp_weights_mcallister' for the weight a fit implies, and reweight_comps() to tune towards it.</t>
         </is>
@@ -1257,10 +1254,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Conditional age-at-length composition weight, on a scale set by 'CAAL_distribution' (as for 'Comp_weights'). _x000D_
-Under a multinomial it is the natural-scale multiplier on the input sample size. _x000D_
-Under a Dirichlet-multinomial the model uses exp(CAAL_weights), so the column is the LOG of the starting weight -- the default of 1 is a starting weight of e, not 1. _x000D_
-Read when a model is built from scratch -- a refit keeps the weight it is given.</t>
+          <t>Conditional age-at-length composition weight, on a scale set by 'CAAL_distribution', exactly as 'Comp_weights' is. Under a Dirichlet-multinomial the column is the LOG of the starting weight, so the default of 1 is a starting weight of e.</t>
         </is>
       </c>
     </row>
@@ -1364,8 +1358,9 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Index used to give fleets the SAME catchability. Fleets sharing a value share one q parameter, so the group can carry only one answer to whether q is estimated: the LEAD fleet -- the group's first non-Off fleet -- decides for all of them, regardless of fleet type, and the others' Catchability settings are not used. A fleet with no index_data of its own is therefore still estimated if its group's lead is. Give a fleet its own value when it should be estimated independently._x000D_
-The exception is 'Analytical' and 'AnalyticalArith', which solve catchability from each fleet's own index observations rather than from the shared parameter, so a group containing one does NOT share a catchability even when every fleet in it carries the same setting. 'Environmental' and 'AR1' do share: they rebuild q from the group's shared parameters, including when the fleets name different environmental series (the lead fleet's is used). If the lead is 'Fixed' the group shares nothing at all: no catchability is estimated and each fleet sits at its own 'Catchability_init'. Where a q IS estimated for the group, its STARTING value is the mean of the group's log 'Catchability_init' (TMB averages the initial values of parameters mapped together), not the lead's; the prior centre does use the lead's. data_check() reports the analytical case, a Fixed lead that leaves fleets on different inits, and a differing 'Catchability' or 'Time_varying_q' within a group.</t>
+          <t>Index used to give fleets the SAME catchability (otherwise, same as Fleet_code). Fleets sharing a value share one q parameter, so the group carries only one answer to whether q is estimated: the group's first non-Off fleet decides for all of them, regardless of fleet type. Give a fleet its own value when it should be estimated independently._x000D_
+'Analytical' and 'AnalyticalArith' are the exception -- they solve q from each fleet's own index observations, so a group containing one does NOT share a catchability. data_check() reports that case, a Fixed lead that leaves fleets on different inits, and a Catchability or Time_varying_q that differs within a group._x000D_
+See vignette('model-options-and-functionality'), 'Which fleets get a catchability'.</t>
         </is>
       </c>
     </row>
@@ -1389,9 +1384,9 @@
 3 or "Analytical" = geometric-mean analytical q following Ludwig and Walters 1994_x000D_
 4 or "PowerEquation" = power equation (NOT YET IMPLEMENTED)_x000D_
 5 or "Environmental" = linear equation log(q_y) = q_mu + beta * index_y; the environmental index is specified by Time_varying_q_x000D_
-6 or "AR1" = REMOVED; data_check() errors. AR1 random deviates fit to an environmental index (sensu Rogers et al 2024; 10.1093/icesjms/fsae005), index specified by Time_varying_q -- but the deviates were never estimated, so q came back constant and the objective was not comparable with another model's. Express it as a q linkage with ar1(1 | Year) and 'observe', passed to fit_mod(qFun = ); the error gives the call._x000D_
+6 or "AR1" = REMOVED; data_check() errors. The deviates were never estimated, so q came back constant. Express the Rogers et al. (2024) form as a q linkage with ar1(1 | Year) and 'observe'; the error gives the call._x000D_
 7 or "AnalyticalArith" = arithmetic-mean analytical q (AMAK/ebswp form, pair with the MVN survey likelihood)_x000D_
-Applies to any fleet carrying index_data, a fishery with a CPUE series included; such a fleet's index uses that fleet's own selectivity. A fleet with NO fitted index rows gets no catchability whatever this says, since a q with no index to inform it is a flat direction -- unless it follows the lead of a shared Catchability_index group.</t>
+Applies to any fleet carrying index_data, a fishery with a CPUE series included. A fleet with NO fitted index rows gets no catchability whatever this says, unless it follows the lead of a shared Catchability_index group. See vignette('model-options-and-functionality').</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1439,12 @@
         <is>
           <t>0 or "Off" = no_x000D_
 1 or "IID" = penalized deviate or random effect_x000D_
-2 or "AR1" = REMOVED in 5.16.0; data_check() errors on it. It was never an AR1 -- the template scored it with the same independent normal penalty as "IID", and index_q_rho belongs to the removed Catchability = "AR1" (QAR1) path, not to this switch. Use "IID" for the fit it actually gave, or express the autocorrelation as a q linkage: build_catchability(linkages = list(q = linkage_spec(~ ar1(1 | Year), by = ~ fleet)))._x000D_
+2 or "AR1" = REMOVED in 5.16.0; data_check() errors on it. It was never an AR1 -- it was scored as "IID" -- so use "IID" for the same fit, or a q linkage with ar1(1 | Year) for a real one._x000D_
 3 or "Block" = time blocks with no penalty_x000D_
 4 or "RandomWalk" = random walk from mean following Dorn 2018 (dnorm(q_y - q_y-1, 0, sigma)_x000D_
-If Catchability = 5, this determines the environmental index to be used in the equation log(q_y) = q_mu + beta * index_y_x000D_
-If "random_q" is selected in fit_mod, penalized deviates (1) and random walk parameters (4) will be treated as random effects._x000D_
-Soft-deprecated as a whole: the linkage grammar expresses the same deviations, with the deviation sd estimated or fixed.</t>
+If Catchability = 5, this holds the env_data column index for log(q_y) = q_mu + beta * index_y, not a mode._x000D_
+Under fit_mod(random_q = TRUE), IID (1) and RandomWalk (4) deviations become random effects._x000D_
+Soft-deprecated as a whole: the linkage grammar expresses the same deviations, with the deviation sd estimated or fixed. See vignette('model-options-and-functionality').</t>
         </is>
       </c>
     </row>
@@ -1486,8 +1481,8 @@
           <t>Survey/index biomass observation likelihood family._x000D_
 0 or "Lognormal" (default) = independent lognormal on the log observation, with the bias correction._x000D_
 1 "MVN" / 2 "MVNORM" = multivariate normal on the natural-scale residual, with a user-supplied covariance in index_cov; they differ only by a constant._x000D_
-3 "Normal" = independent normal on the natural-scale residual with an ABSOLUTE sd from Log_sd (not a log-scale CV). Matches the AMAK avo_like/cpue_like term for term, so it is what the ADMB bridges compare against._x000D_
-4 "TruncatedNormal" = the same normal, left-truncated at zero. An index cannot be negative, so over the values the data can take the density is renormalized by log Phi(mu/sd). Prefer this to 3 unless an exact ADMB comparison is needed: it is the only natural-scale family sim_mod() can draw from exactly, since 3 has to reject the non-positive draws data_check() would refuse.</t>
+3 "Normal" = independent normal on the natural-scale residual with an ABSOLUTE sd from Log_sd (not a log-scale CV). Matches AMAK avo_like/cpue_like term for term, so it is what the ADMB bridges compare against._x000D_
+4 "TruncatedNormal" = the same normal, left-truncated at zero. Prefer it to 3 unless an exact ADMB comparison is needed: an index cannot be negative, so this is the only natural-scale family whose likelihood and simulator are the same distribution.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1726,7 +1726,7 @@
 1 = Exponential (Stewart et al 1983)_x000D_
 2 = Temperature-dependence for warm-water species (Kitchell et al 1977; sensu Holsman et al 2015)_x000D_
 3 = temperature dependence for cool and cold-water species (Thornton and Lessem 1979)_x000D_
-4 = for direct input of consumption in Pyrs  where consumption at age = Numbers * Pyrs (CA set to 1, fday set to 1, CB set to 0)</t>
+4 = for direct input of consumption in Pyrs  where consumption at age = Numbers * Pyrs (CA set to 1, fday set to 1, CB set to 0). Equations 1-3 read the Cindex column of env_data; 4 does not, and is the default.</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Integer: which environmental index in env_data to use to drive bioenergetics</t>
+          <t>Integer: which environmental index in env_data drives bioenergetics, counting the covariate columns from 1 (the Year column is not one). Read only when Ceq is 1, 2 or 3.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="meta_data" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1080,12 +1080,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sel_shape_mode</t>
+          <t>Sel_penalty_form</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Shape-penalty mode: "Directional" (default) or "Smooth" (two-sided d^2, RTMB).</t>
+          <t>Which form the NonParametric (type 2) selectivity penalties take:_x000D_
+0 or "Rceattle" (default)_x000D_
+1 or "AMAK" = the ADMB atka mackerel forms: a bare sum of squares on the random walk in place of a normalized density, and the level weight read from Sel_avgsel_pen (which must then be &gt; 0) rather than fixed at 2. Read only for Selectivity = 2, and not available with Time_varying_sel = "IID".</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1099,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sel_avgsel_pen</t>
+          <t>Sel_shape_mode</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Weight on the AMAK avgsel base-level penalty (type 9); 0 = off (default), 10 matches AMAK.</t>
+          <t>Shape-penalty mode: "Directional" (default) or "Smooth" (two-sided d^2, RTMB).</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1116,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sel_cap_bin</t>
+          <t>Sel_avgsel_pen</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NonParametricRPM bin cap (NA -&gt; no cap).</t>
+          <t>Weight on the AMAK avgsel base-level penalty: type 9, and type 2 under Sel_penalty_form = "AMAK", where it must be &gt; 0. 0 = off (default); 10 matches the type-9 AMAK model, 20 the type-2 atka mackerel one.</t>
         </is>
       </c>
     </row>
@@ -1131,10 +1133,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>Sel_cap_bin</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>NonParametricRPM bin cap (NA -&gt; no cap).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>Sel_norm_bin</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Age/length bin at which selectivity = 1. An absolute AGE for an age-based fleet (6 means age 6, not the 6th bin) or a 1-based LENGTH-BIN ordinal for a length-based one, per 'Selectivity_dimension'. _x000D_
 If NA, it will not normalize selectivity. _x000D_
@@ -1143,23 +1162,6 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Sel_norm_bin_upper</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Upper age/length bin for selectivity normalization (default = NA). If NA, does not use the age range, If not NA, uses mean selectivity between `Sel_norm_bin` and `Sel_norm_bin_upper`</t>
-        </is>
-      </c>
-    </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
@@ -1168,10 +1170,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>Sel_norm_bin_upper</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Upper age/length bin for selectivity normalization (default = NA). If NA, does not use the age range, If not NA, uses mean selectivity between `Sel_norm_bin` and `Sel_norm_bin_upper`</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>Sel_norm_scope</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Whether selectivity normalization pools its reference across sexes. Orthogonal to 'Sel_norm_bin', which says WHERE the reference is taken (a named bin, or the max). _x000D_
 "WithinSex" = each sex is divided by its own reference, so both reach 1 and only the SHAPE differs by sex (relative sex-specific selectivity removed). _x000D_
@@ -1180,18 +1199,18 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>Comp_distribution</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Composition data distribution:_x000D_
 -1 = AFSC multinomial_x000D_
@@ -1200,18 +1219,18 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>Comp_weights</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Composition weight, on a scale set by 'Comp_distribution'. _x000D_
 Under a multinomial it is the natural-scale multiplier on the input sample size. _x000D_
@@ -1221,18 +1240,18 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>CAAL_distribution</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Composition data distribution:_x000D_
 -1 = AFSC multinomial_x000D_
@@ -1241,23 +1260,6 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>CAAL_weights</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Conditional age-at-length composition weight, on a scale set by 'CAAL_distribution', exactly as 'Comp_weights' is. Under a Dirichlet-multinomial the column is the LOG of the starting weight, so the default of 1 is a starting weight of e.</t>
-        </is>
-      </c>
-    </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -1266,12 +1268,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Comp_accum_young</t>
+          <t>CAAL_weights</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Age/length composition young-tail accumulation bin (AFSC ac_yng): a 1-based ordinal on the fleet's composition dimension; bins below it are folded into it before the likelihood. NA or 1 = no young accumulation.</t>
+          <t>Conditional age-at-length composition weight, on a scale set by 'CAAL_distribution', exactly as 'Comp_weights' is. Under a Dirichlet-multinomial the column is the LOG of the starting weight, so the default of 1 is a starting weight of e.</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1285,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Comp_accum_old</t>
+          <t>Comp_accum_young</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Age/length composition old-tail accumulation bin (AFSC ac_old): a 1-based ordinal on the fleet's composition dimension; bins above it are folded into it before the likelihood. NA, 0, or a value &gt;= the number of bins = no old accumulation.</t>
+          <t>Age/length composition young-tail accumulation bin (AFSC ac_yng): a 1-based ordinal on the fleet's composition dimension; bins below it are folded into it before the likelihood. NA or 1 = no young accumulation.</t>
         </is>
       </c>
     </row>
@@ -1300,10 +1302,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>Comp_accum_old</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Age/length composition old-tail accumulation bin (AFSC ac_old): a 1-based ordinal on the fleet's composition dimension; bins above it are folded into it before the likelihood. NA, 0, or a value &gt;= the number of bins = no old accumulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>Observation_units</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>1 = catch/index is weight (mt) _x000D_
 2 = catch/index is in numbers (thousands of fish) _x000D_
@@ -1311,23 +1330,6 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Weight_index</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Weight index to use for calculation of derived quantities</t>
-        </is>
-      </c>
-    </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
@@ -1336,12 +1338,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Age_transition_index</t>
+          <t>Weight_index</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Age transition matrix (e.g. growth trajectory) index to used convert age to length</t>
+          <t>Weight index to use for calculation of derived quantities</t>
         </is>
       </c>
     </row>
@@ -1353,10 +1355,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>Age_transition_index</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Age transition matrix (e.g. growth trajectory) index to used convert age to length</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>Catchability_index</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Index used to give fleets the SAME catchability (otherwise, same as Fleet_code). Fleets sharing a value share one q parameter, so the group carries only one answer to whether q is estimated: the group's first non-Off fleet decides for all of them, regardless of fleet type. Give a fleet its own value when it should be estimated independently._x000D_
 'Analytical' and 'AnalyticalArith' are the exception -- they solve q from each fleet's own index observations, so a group containing one does NOT share a catchability. data_check() reports that case, a Fixed lead that leaves fleets on different inits, and a Catchability or Time_varying_q that differs within a group._x000D_
@@ -1364,18 +1383,18 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>Catchability</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Catchability form. Accepts integer codes or readable strings:_x000D_
 0 or "Fixed" = fixed at Catchability_init_x000D_
@@ -1390,23 +1409,6 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Catchability_init</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Starting value or fixed value for catchability. Must be positive on any fleet that carries index_data, whatever its Fleet_type -- it has no default, and it is logged to seed index_log_q, so a blank or zero gives a non-finite starting value. Not read under Analytical or AnalyticalArith, which solve q from the data.</t>
-        </is>
-      </c>
-    </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -1415,12 +1417,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Catchability_prior_sd</t>
+          <t>Catchability_init</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Standard deviation for the q prior. Must be positive under Estimated-with-prior, where the prior is scored at it, and under AR1, where the estimated sd starts from it.</t>
+          <t>Starting value or fixed value for catchability. Must be positive on any fleet that carries index_data, whatever its Fleet_type -- it has no default, and it is logged to seed index_log_q, so a blank or zero gives a non-finite starting value. Not read under Analytical or AnalyticalArith, which solve q from the data.</t>
         </is>
       </c>
     </row>
@@ -1432,10 +1434,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>Catchability_prior_sd</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Standard deviation for the q prior. Must be positive under Estimated-with-prior, where the prior is scored at it, and under AR1, where the estimated sd starts from it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>Time_varying_q</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>0 or "Off" = no_x000D_
 1 or "IID" = penalized deviate or random effect_x000D_
@@ -1448,23 +1467,6 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Time_varying_q_sd</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Starting or fixed sd for the time-varying q deviations. Must be positive when Time_varying_q is IID, AR1 or RandomWalk, which penalize the deviations at it; Block needs none.</t>
-        </is>
-      </c>
-    </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
@@ -1473,10 +1475,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>Time_varying_q_sd</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Starting or fixed sd for the time-varying q deviations. Must be positive when Time_varying_q is IID, AR1 or RandomWalk, which penalize the deviations at it; Block needs none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>Index_distribution</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Survey/index biomass observation likelihood family._x000D_
 0 or "Lognormal" (default) = independent lognormal on the log observation, with the bias correction._x000D_
@@ -1486,18 +1505,18 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
         <is>
           <t>Estimate_index_sd</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>0 = use input "Log_sd" from index_data_x000D_
 1 = estimate as free parameter_x000D_
@@ -1505,23 +1524,6 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Index_sd</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Starting value to be used if "Estimate_index_sd" = 1</t>
-        </is>
-      </c>
-    </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
@@ -1530,10 +1532,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>Index_sd</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Starting value to be used if "Estimate_index_sd" = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>Estimate_catch_sd</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>0 = use input "Log_sd" from catch_data_x000D_
 1 = estimate as free parameter_x000D_
@@ -1541,23 +1560,6 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Catch_sd</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Starting value to be used if Estimate_catch_sd = 1</t>
-        </is>
-      </c>
-    </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
@@ -1566,161 +1568,178 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Proj_F_proportion</t>
+          <t>Catch_sd</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>The proportion of future fishing mortality assigned to this fleet</t>
+          <t>Starting value to be used if Estimate_catch_sd = 1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>index_data</t>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Proj_F_proportion</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Survey index or fishery indices in weight (mt) or numbers (thousands of fish).</t>
+          <t>The proportion of future fishing mortality assigned to this fleet</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>catch_data</t>
+          <t>index_data</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Total catch in weight (mt) or numbers data</t>
+          <t>Survey index or fishery indices in weight (mt) or numbers (thousands of fish).</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comp_data</t>
+          <t>catch_data</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Survey/fishery age or length composition data. Note if sex is 3, put female composition data then male composition data (similar to SS).</t>
+          <t>Total catch in weight (mt) or numbers data</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>caal_data</t>
+          <t>comp_data</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Survey/fishery CAAL data. Note if sex is 3, put female CAAL data then male CAAL data (similar to SS).</t>
+          <t>Survey/fishery age or length composition data. Note if sex is 3, put female composition data then male composition data (similar to SS).</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>emp_sel</t>
+          <t>caal_data</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Empirical/fixed selectivity for surveys and fisheries (leave empty if not used)</t>
+          <t>Survey/fishery CAAL data. Note if sex is 3, put female CAAL data then male CAAL data (similar to SS).</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>emp_sel</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Empirical/fixed selectivity for surveys and fisheries (leave empty if not used)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>age_trans_matrix</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Age transition matrix (e.g. growth trajectory) used to convert age to length for length comp data. _x000D_
 Can have multiple matrices for a species specified by Age_transition_index.</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>age_error</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Aging error matrices. Can have only one per species.</t>
-        </is>
-      </c>
-    </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>age_error</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Aging error matrices. Can have only one per species.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Time-invariant or -varying empirical weight-at-age for calculation of derived quantities (SSB, Consumption/Ration, Suitability, Total Catch, Survey Biomass, etc). _x000D_
 Can have multiple weight-at-age data-sets for each species.</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>maturity</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Maturity-at-age for each species</t>
-        </is>
-      </c>
-    </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>sex_ratio</t>
+          <t>maturity</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Percent female at age for each species</t>
+          <t>Maturity-at-age for each species</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>M1_base</t>
+          <t>sex_ratio</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Residual natural mortality for each species</t>
+          <t>Percent female at age for each species</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>M1_base</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Residual natural mortality for each species</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>Ceq</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Integer: switch for which bioenergetics equation to use for each species for ft to scale max consumption: _x000D_
 1 = Exponential (Stewart et al 1983)_x000D_
@@ -1730,23 +1749,6 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>bioenergetics_control</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Cindex</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Integer: which environmental index in env_data drives bioenergetics, counting the covariate columns from 1 (the Year column is not one). Read only when Ceq is 1, 2 or 3.</t>
-        </is>
-      </c>
-    </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
@@ -1755,12 +1757,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Pvalue</t>
+          <t>Cindex</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Numeric: this scales the maximum consumption used for ration for each species; Pvalue is in Cmax*fT*Pvalue*Pyrs</t>
+          <t>Integer: which environmental index in env_data drives bioenergetics, counting the covariate columns from 1 (the Year column is not one). Read only when Ceq is 1, 2 or 3.</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1774,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>fday</t>
+          <t>Pvalue</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Numeric: number of foraging days per year for each species</t>
+          <t>Numeric: this scales the maximum consumption used for ration for each species; Pvalue is in Cmax*fT*Pvalue*Pyrs</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1791,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>fday</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Intercept of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
+          <t>Numeric: number of foraging days per year for each species</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1808,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Slope of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
+          <t>Intercept of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1825,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Qc</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
+          <t>Slope of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1842,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tco</t>
+          <t>Qc</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -1857,7 +1859,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tcm</t>
+          <t>Tco</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -1874,7 +1876,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tcl</t>
+          <t>Tcm</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -1891,7 +1893,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CK1</t>
+          <t>Tcl</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -1908,7 +1910,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CK4</t>
+          <t>CK1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -1925,10 +1927,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
+          <t>CK4</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>Diet_distribution</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Diet composition likelihood distribution per predator species:_x000D_
 0 = multinomial_x000D_
@@ -1936,18 +1955,18 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>Diet_comp_weights</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Diet composition weight per predator species, on a scale set by 'Diet_distribution' (as for 'Comp_weights'). _x000D_
 Under a multinomial it is the natural-scale multiplier on the input sample size. _x000D_
@@ -1956,37 +1975,37 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>env_data</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Environmental indices such as bottom temperature data to incorporate into ration equation specified by Ceq and Cindex. Also used to drive catchability if Catchability = 5 or 6. Will use the mean for missing years. Temperature should be in Celsius.</t>
-        </is>
-      </c>
-    </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ration_data</t>
+          <t>env_data</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Annual relative foraging rate by age. Multiplied by pvalue and fday to scale maximum consumption to the number of days in a year that foraging occurs.</t>
+          <t>Environmental indices such as bottom temperature data to incorporate into ration equation specified by Ceq and Cindex. Also used to drive catchability if Catchability = 5 or 6. Will use the mean for missing years. Temperature should be in Celsius.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
+          <t>ration_data</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Annual relative foraging rate by age. Multiplied by pvalue and fday to scale maximum consumption to the number of days in a year that foraging occurs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
           <t>diet_data</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Stomach proportion by weight for each predator, prey, predator age, prey age combination. Multiple diet-data formats can be included:_x000D_
 _x000D_
@@ -2001,36 +2020,36 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>NOTE: Most objects are ordered by species code if not specified</t>
-        </is>
-      </c>
-    </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>NOTE: Lengths are index 1 through nlengths</t>
+          <t>NOTE: Most objects are ordered by species code if not specified</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NOTE: Columns for ages are index by 1 through nages, but are placeholders.</t>
+          <t>NOTE: Lengths are index 1 through nlengths</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>NOTE: For catch, index, and comp data, if "Year" is negative, it will predict for that year, but not include the data in the likelihood.</t>
+          <t>NOTE: Columns for ages are index by 1 through nages, but are placeholders.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
+        <is>
+          <t>NOTE: For catch, index, and comp data, if "Year" is negative, it will predict for that year, but not include the data in the likelihood.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>NOTE: For emp_sel, weight, and ration_data, if "Year" == 0, those data will be used for all years</t>
         </is>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -966,7 +966,8 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Age/length bin at which selectivity becomes non-zero</t>
+          <t>First age/length bin selected; selectivity is 0 below it. _x000D_
+A 1-based BIN ORDINAL on the fleet's 'Selectivity_dimension' -- 3 means the third bin, so on a stock with 'minage' 3 it is age 5, not age 3. This is the opposite convention to 'Sel_norm_bin', which is an absolute age. The alias 'Age_first_selected' is the older name for the same column, not a second convention.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1137,9 +1137,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Age/length bin at which selectivity = 1. An absolute AGE for an age-based fleet (6 means age 6, not the 6th bin) or a 1-based LENGTH-BIN ordinal for a length-based one, per 'Selectivity_dimension'. _x000D_
-If NA, it will not normalize selectivity. _x000D_
-If &lt; 0, will normalize selectivity by the max. _x000D_
+          <t>Where selectivity is normalized to 1. Takes a word or a bin:_x000D_
+"Max" = normalize by the largest value._x000D_
+"Off" (or "None", or blank) = do not normalize._x000D_
+"All" = the whole selected range; LogisticPM only, where this column is a penalty range rather than a normalization reference. On that form the model reads any non-bin the same way, so a blank and "Off" give the whole range too -- "All" is simply the word that says so._x000D_
+A number = an absolute AGE for an age-based fleet (6 means age 6, not the 6th bin) or a 1-based LENGTH-BIN ordinal for a length-based one, per 'Selectivity_dimension'. Note 'Bin_first_selected' beside it uses the OPPOSITE convention and is always a bin ordinal._x000D_
+Must fall between the fleet's first selected bin and its last: below 'Bin_first_selected' the curve is zeroed, so a reference taken there divides by nothing. A value below the first selected bin is read as "Max", which is what a negative has always meant._x000D_
 In a two-sex model this column says only WHERE the reference is taken; whether it is pooled across the sexes is 'Sel_norm_scope'. See vignette('model-options-and-functionality'), 'Sex structure and relative selectivity'.</t>
         </is>
       </c>
@@ -1157,7 +1160,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Upper age/length bin for selectivity normalization (default = NA). If NA, does not use the age range, If not NA, uses mean selectivity between `Sel_norm_bin` and `Sel_norm_bin_upper`</t>
+          <t>Upper age/length bin for selectivity normalization. "Off" (or blank) uses a single bin rather than a range; a number takes mean selectivity between 'Sel_norm_bin' and this bin, on the same scale and with the same bounds as 'Sel_norm_bin'.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/meta_data_names.xlsx
+++ b/inst/extdata/meta_data_names.xlsx
@@ -1384,7 +1384,7 @@
           <t>Catchability form. Accepts integer codes or readable strings:_x000D_
 0 or "Fixed" = fixed at Catchability_init_x000D_
 1 or "Estimated" = estimate as a free parameter_x000D_
-2 or "Estimated-with-prior" = estimate with a normal prior N(Catchability_init, Catchability_prior_sd)_x000D_
+2 or "Estimated-with-prior" = estimate with a lognormal prior on q, mean Catchability_init (median when bias_adjust_proc = FALSE) and log-scale SD Catchability_prior_sd_x000D_
 3 or "Analytical" = geometric-mean analytical q following Ludwig and Walters 1994_x000D_
 4 or "PowerEquation" = power equation (NOT YET IMPLEMENTED)_x000D_
 5 or "Environmental" = linear equation log(q_y) = q_mu + beta * index_y; the environmental index is specified by Time_varying_q_x000D_
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Standard deviation for the q prior. Must be positive under Estimated-with-prior, where the prior is scored at it, and under AR1, where the estimated sd starts from it.</t>
+          <t>Standard deviation for the q prior, on the log scale. Must be positive under Estimated-with-prior, where the prior is scored at it.</t>
         </is>
       </c>
     </row>
